--- a/HAL Stock HQ - Daily 2026-09-14.xlsx
+++ b/HAL Stock HQ - Daily 2026-09-14.xlsx
@@ -18,23 +18,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="0;-0;;@"/>
+    <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="23">
     <font>
       <name val="Tahoma"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -85,12 +79,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
@@ -111,20 +99,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -190,7 +164,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -247,11 +221,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -284,17 +264,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -541,19 +510,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
       </right>
@@ -627,32 +583,6 @@
       </top>
       <bottom style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF808080"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF808080"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF808080"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,19 +727,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -880,17 +797,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -906,26 +812,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -938,17 +824,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -973,26 +848,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1026,6 +881,68 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF808080"/>
       </top>
@@ -1046,736 +963,646 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="10" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1784,17 +1611,7 @@
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1977,7 +1794,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2328,151 +2212,152 @@
   <dimension ref="A1:AS60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="16.9" customHeight="1"/>
   <cols>
-    <col width="10.75" customWidth="1" style="3" min="1" max="2"/>
-    <col width="4.25" customWidth="1" style="3" min="3" max="11"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="3" min="12" max="12"/>
-    <col width="4.25" customWidth="1" style="3" min="13" max="13"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="3" min="14" max="14"/>
-    <col width="4.25" customWidth="1" style="3" min="15" max="20"/>
-    <col hidden="1" width="3" customWidth="1" style="3" min="21" max="21"/>
-    <col width="10.75" customWidth="1" style="3" min="22" max="23"/>
-    <col width="4.25" customWidth="1" style="3" min="24" max="32"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="3" min="33" max="33"/>
-    <col width="4.25" customWidth="1" style="3" min="34" max="41"/>
-    <col width="8.875" customWidth="1" style="3" min="42" max="42"/>
-    <col width="10.125" customWidth="1" style="3" min="43" max="43"/>
-    <col width="8.875" customWidth="1" style="3" min="44" max="16384"/>
+    <col width="10.75" customWidth="1" style="165" min="1" max="2"/>
+    <col width="4.25" customWidth="1" style="165" min="3" max="11"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="165" min="12" max="12"/>
+    <col width="4.25" customWidth="1" style="165" min="13" max="13"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="165" min="14" max="14"/>
+    <col width="4.25" customWidth="1" style="165" min="15" max="20"/>
+    <col hidden="1" width="3" customWidth="1" style="165" min="21" max="21"/>
+    <col width="10.75" customWidth="1" style="165" min="22" max="23"/>
+    <col width="4.25" customWidth="1" style="165" min="24" max="32"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="165" min="33" max="33"/>
+    <col width="4.25" customWidth="1" style="165" min="34" max="41"/>
+    <col width="8.875" customWidth="1" style="165" min="42" max="42"/>
+    <col width="10.125" customWidth="1" style="165" min="43" max="43"/>
+    <col width="8.875" customWidth="1" style="165" min="44" max="44"/>
+    <col width="8.875" customWidth="1" style="165" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="54.95" customFormat="1" customHeight="1" s="1" thickBot="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>DAILY CONTAINER STOCK</t>
         </is>
       </c>
-      <c r="B1" s="130" t="n"/>
-      <c r="C1" s="169" t="n"/>
-      <c r="D1" s="135" t="n"/>
-      <c r="E1" s="168" t="n"/>
-      <c r="F1" s="169" t="n"/>
-      <c r="G1" s="169" t="n"/>
-      <c r="H1" s="169" t="n"/>
-      <c r="I1" s="169" t="n"/>
-      <c r="J1" s="169" t="n"/>
-      <c r="K1" s="169" t="n"/>
-      <c r="L1" s="169" t="n"/>
-      <c r="M1" s="169" t="n"/>
-      <c r="N1" s="169" t="n"/>
-      <c r="O1" s="169" t="n"/>
-      <c r="P1" s="169" t="n"/>
-      <c r="Q1" s="169" t="n"/>
-      <c r="R1" s="169" t="n"/>
-      <c r="S1" s="135" t="n"/>
-      <c r="T1" s="169" t="n"/>
-      <c r="U1" s="169" t="n"/>
-      <c r="V1" s="132" t="n"/>
-      <c r="W1" s="132" t="n"/>
-      <c r="X1" s="169" t="n"/>
-      <c r="Y1" s="169" t="n"/>
-      <c r="Z1" s="169" t="n"/>
-      <c r="AA1" s="169" t="n"/>
-      <c r="AB1" s="169" t="n"/>
-      <c r="AC1" s="169" t="n"/>
-      <c r="AD1" s="169" t="n"/>
-      <c r="AE1" s="169" t="n"/>
-      <c r="AF1" s="169" t="n"/>
-      <c r="AG1" s="169" t="n"/>
-      <c r="AH1" s="169" t="n"/>
-      <c r="AI1" s="169" t="n"/>
-      <c r="AJ1" s="168" t="inlineStr">
+      <c r="B1" s="105" t="n"/>
+      <c r="C1" s="106" t="n"/>
+      <c r="D1" s="110" t="n"/>
+      <c r="E1" s="169" t="n"/>
+      <c r="F1" s="106" t="n"/>
+      <c r="G1" s="106" t="n"/>
+      <c r="H1" s="106" t="n"/>
+      <c r="I1" s="106" t="n"/>
+      <c r="J1" s="106" t="n"/>
+      <c r="K1" s="106" t="n"/>
+      <c r="L1" s="106" t="n"/>
+      <c r="M1" s="106" t="n"/>
+      <c r="N1" s="106" t="n"/>
+      <c r="O1" s="106" t="n"/>
+      <c r="P1" s="106" t="n"/>
+      <c r="Q1" s="106" t="n"/>
+      <c r="R1" s="106" t="n"/>
+      <c r="S1" s="110" t="n"/>
+      <c r="T1" s="106" t="n"/>
+      <c r="U1" s="106" t="n"/>
+      <c r="V1" s="107" t="n"/>
+      <c r="W1" s="107" t="n"/>
+      <c r="X1" s="106" t="n"/>
+      <c r="Y1" s="106" t="n"/>
+      <c r="Z1" s="106" t="n"/>
+      <c r="AA1" s="106" t="n"/>
+      <c r="AB1" s="106" t="n"/>
+      <c r="AC1" s="106" t="n"/>
+      <c r="AD1" s="106" t="n"/>
+      <c r="AE1" s="106" t="n"/>
+      <c r="AF1" s="106" t="n"/>
+      <c r="AG1" s="106" t="n"/>
+      <c r="AH1" s="106" t="n"/>
+      <c r="AI1" s="106" t="n"/>
+      <c r="AJ1" s="169" t="inlineStr">
         <is>
           <t>DATE:</t>
         </is>
       </c>
-      <c r="AK1" s="182" t="n"/>
-      <c r="AL1" s="183" t="n">
+      <c r="AK1" s="170" t="n"/>
+      <c r="AL1" s="202" t="n">
         <v>46279</v>
       </c>
-      <c r="AM1" s="182" t="n"/>
-      <c r="AN1" s="182" t="n"/>
-      <c r="AO1" s="184" t="n"/>
+      <c r="AM1" s="170" t="n"/>
+      <c r="AN1" s="170" t="n"/>
+      <c r="AO1" s="185" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="185" t="inlineStr">
+      <c r="A2" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="B2" s="186" t="n"/>
-      <c r="C2" s="162" t="inlineStr">
+      <c r="B2" s="178" t="n"/>
+      <c r="C2" s="188" t="inlineStr">
         <is>
           <t>FULL INBOUND (BKK)</t>
         </is>
       </c>
-      <c r="D2" s="187" t="n"/>
-      <c r="E2" s="187" t="n"/>
-      <c r="F2" s="187" t="n"/>
-      <c r="G2" s="187" t="n"/>
-      <c r="H2" s="187" t="n"/>
-      <c r="I2" s="187" t="n"/>
-      <c r="J2" s="187" t="n"/>
-      <c r="K2" s="188" t="n"/>
-      <c r="L2" s="143" t="inlineStr">
+      <c r="D2" s="167" t="n"/>
+      <c r="E2" s="167" t="n"/>
+      <c r="F2" s="167" t="n"/>
+      <c r="G2" s="167" t="n"/>
+      <c r="H2" s="167" t="n"/>
+      <c r="I2" s="167" t="n"/>
+      <c r="J2" s="167" t="n"/>
+      <c r="K2" s="175" t="n"/>
+      <c r="L2" s="176" t="inlineStr">
         <is>
           <t>CURRENT STOCK (BKK)</t>
         </is>
       </c>
-      <c r="M2" s="187" t="n"/>
-      <c r="N2" s="187" t="n"/>
-      <c r="O2" s="187" t="n"/>
-      <c r="P2" s="187" t="n"/>
-      <c r="Q2" s="188" t="n"/>
-      <c r="R2" s="189">
+      <c r="M2" s="167" t="n"/>
+      <c r="N2" s="167" t="n"/>
+      <c r="O2" s="167" t="n"/>
+      <c r="P2" s="167" t="n"/>
+      <c r="Q2" s="175" t="n"/>
+      <c r="R2" s="203">
         <f>AL1</f>
         <v/>
       </c>
-      <c r="S2" s="187" t="n"/>
-      <c r="T2" s="190" t="n"/>
+      <c r="S2" s="167" t="n"/>
+      <c r="T2" s="168" t="n"/>
       <c r="U2" s="2" t="n"/>
-      <c r="V2" s="185" t="inlineStr">
+      <c r="V2" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="W2" s="186" t="n"/>
-      <c r="X2" s="162" t="inlineStr">
+      <c r="W2" s="178" t="n"/>
+      <c r="X2" s="188" t="inlineStr">
         <is>
           <t>FULL INBOUND (LCH)</t>
         </is>
       </c>
-      <c r="Y2" s="187" t="n"/>
-      <c r="Z2" s="187" t="n"/>
-      <c r="AA2" s="187" t="n"/>
-      <c r="AB2" s="187" t="n"/>
-      <c r="AC2" s="187" t="n"/>
-      <c r="AD2" s="187" t="n"/>
-      <c r="AE2" s="187" t="n"/>
-      <c r="AF2" s="188" t="n"/>
-      <c r="AG2" s="143" t="inlineStr">
+      <c r="Y2" s="167" t="n"/>
+      <c r="Z2" s="167" t="n"/>
+      <c r="AA2" s="167" t="n"/>
+      <c r="AB2" s="167" t="n"/>
+      <c r="AC2" s="167" t="n"/>
+      <c r="AD2" s="167" t="n"/>
+      <c r="AE2" s="167" t="n"/>
+      <c r="AF2" s="175" t="n"/>
+      <c r="AG2" s="176" t="inlineStr">
         <is>
           <t>CURRENT STOCK (LCH)</t>
         </is>
       </c>
-      <c r="AH2" s="187" t="n"/>
-      <c r="AI2" s="187" t="n"/>
-      <c r="AJ2" s="187" t="n"/>
-      <c r="AK2" s="187" t="n"/>
-      <c r="AL2" s="188" t="n"/>
-      <c r="AM2" s="189">
+      <c r="AH2" s="167" t="n"/>
+      <c r="AI2" s="167" t="n"/>
+      <c r="AJ2" s="167" t="n"/>
+      <c r="AK2" s="167" t="n"/>
+      <c r="AL2" s="175" t="n"/>
+      <c r="AM2" s="203">
         <f>R2</f>
         <v/>
       </c>
-      <c r="AN2" s="187" t="n"/>
-      <c r="AO2" s="190" t="n"/>
+      <c r="AN2" s="167" t="n"/>
+      <c r="AO2" s="168" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="191" t="n"/>
-      <c r="B3" s="192" t="n"/>
+      <c r="A3" s="179" t="n"/>
+      <c r="B3" s="180" t="n"/>
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -2564,8 +2449,8 @@
         </is>
       </c>
       <c r="U3" s="9" t="n"/>
-      <c r="V3" s="191" t="n"/>
-      <c r="W3" s="192" t="n"/>
+      <c r="V3" s="179" t="n"/>
+      <c r="W3" s="180" t="n"/>
       <c r="X3" s="10" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -2657,7 +2542,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customFormat="1" customHeight="1" s="19">
+    <row r="4" ht="15" customFormat="1" customHeight="1" s="15">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>PAT</t>
@@ -2668,34 +2553,34 @@
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C4" s="193" t="n">
+      <c r="C4" s="113" t="n">
         <v>33</v>
       </c>
-      <c r="D4" s="194" t="n"/>
-      <c r="E4" s="194" t="n">
+      <c r="D4" s="114" t="n"/>
+      <c r="E4" s="114" t="n">
         <v>47</v>
       </c>
-      <c r="F4" s="194" t="n"/>
-      <c r="G4" s="194" t="n">
+      <c r="F4" s="114" t="n"/>
+      <c r="G4" s="114" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="194" t="n"/>
-      <c r="I4" s="194" t="n"/>
-      <c r="J4" s="194" t="n"/>
-      <c r="K4" s="195" t="n"/>
-      <c r="L4" s="196" t="n">
+      <c r="H4" s="114" t="n"/>
+      <c r="I4" s="114" t="n"/>
+      <c r="J4" s="114" t="n"/>
+      <c r="K4" s="115" t="n"/>
+      <c r="L4" s="116" t="n">
         <v>22</v>
       </c>
-      <c r="M4" s="197" t="n"/>
-      <c r="N4" s="197" t="n">
+      <c r="M4" s="117" t="n"/>
+      <c r="N4" s="117" t="n">
         <v>32</v>
       </c>
-      <c r="O4" s="197" t="n"/>
-      <c r="P4" s="197" t="n"/>
-      <c r="Q4" s="197" t="n"/>
-      <c r="R4" s="197" t="n"/>
-      <c r="S4" s="197" t="n"/>
-      <c r="T4" s="198" t="n"/>
+      <c r="O4" s="117" t="n"/>
+      <c r="P4" s="117" t="n"/>
+      <c r="Q4" s="117" t="n"/>
+      <c r="R4" s="117" t="n"/>
+      <c r="S4" s="117" t="n"/>
+      <c r="T4" s="118" t="n"/>
       <c r="V4" s="13" t="inlineStr">
         <is>
           <t>LCMT</t>
@@ -2706,1359 +2591,1363 @@
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X4" s="193" t="n">
+      <c r="X4" s="113" t="n">
         <v>8</v>
       </c>
-      <c r="Y4" s="194" t="n"/>
-      <c r="Z4" s="194" t="n">
+      <c r="Y4" s="114" t="n"/>
+      <c r="Z4" s="114" t="n">
         <v>10</v>
       </c>
-      <c r="AA4" s="194" t="n">
+      <c r="AA4" s="114" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="194" t="n"/>
-      <c r="AC4" s="194" t="n"/>
-      <c r="AD4" s="194" t="n"/>
-      <c r="AE4" s="194" t="n"/>
-      <c r="AF4" s="195" t="n"/>
-      <c r="AG4" s="199" t="n">
+      <c r="AB4" s="114" t="n"/>
+      <c r="AC4" s="114" t="n"/>
+      <c r="AD4" s="114" t="n"/>
+      <c r="AE4" s="114" t="n"/>
+      <c r="AF4" s="115" t="n"/>
+      <c r="AG4" s="119" t="n">
         <v>7</v>
       </c>
-      <c r="AH4" s="194" t="n"/>
-      <c r="AI4" s="194" t="n">
+      <c r="AH4" s="114" t="n"/>
+      <c r="AI4" s="114" t="n">
         <v>14</v>
       </c>
-      <c r="AJ4" s="194" t="n"/>
-      <c r="AK4" s="194" t="n"/>
-      <c r="AL4" s="194" t="n"/>
-      <c r="AM4" s="194" t="n"/>
-      <c r="AN4" s="194" t="n"/>
-      <c r="AO4" s="200" t="n"/>
-    </row>
-    <row r="5" ht="15" customFormat="1" customHeight="1" s="19">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="AJ4" s="114" t="n"/>
+      <c r="AK4" s="114" t="n"/>
+      <c r="AL4" s="114" t="n"/>
+      <c r="AM4" s="114" t="n"/>
+      <c r="AN4" s="114" t="n"/>
+      <c r="AO4" s="120" t="n"/>
+    </row>
+    <row r="5" ht="15" customFormat="1" customHeight="1" s="15">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>UNITHAI</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C5" s="201" t="n">
+      <c r="C5" s="121" t="n">
         <v>45</v>
       </c>
-      <c r="D5" s="202" t="n"/>
-      <c r="E5" s="202" t="n">
+      <c r="D5" s="122" t="n"/>
+      <c r="E5" s="122" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="202" t="n">
+      <c r="F5" s="122" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="202" t="n">
+      <c r="G5" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="202" t="n"/>
-      <c r="I5" s="202" t="n"/>
-      <c r="J5" s="202" t="n"/>
-      <c r="K5" s="203" t="n"/>
-      <c r="L5" s="204" t="n">
+      <c r="H5" s="122" t="n"/>
+      <c r="I5" s="122" t="n"/>
+      <c r="J5" s="122" t="n"/>
+      <c r="K5" s="123" t="n"/>
+      <c r="L5" s="124" t="n">
         <v>6</v>
       </c>
-      <c r="M5" s="202" t="n"/>
-      <c r="N5" s="202" t="n">
+      <c r="M5" s="122" t="n"/>
+      <c r="N5" s="122" t="n">
         <v>8</v>
       </c>
-      <c r="O5" s="202" t="n"/>
-      <c r="P5" s="202" t="n"/>
-      <c r="Q5" s="202" t="n"/>
-      <c r="R5" s="202" t="n"/>
-      <c r="S5" s="202" t="n"/>
-      <c r="T5" s="205" t="n"/>
-      <c r="V5" s="23" t="inlineStr">
+      <c r="O5" s="122" t="n"/>
+      <c r="P5" s="122" t="n"/>
+      <c r="Q5" s="122" t="n"/>
+      <c r="R5" s="122" t="n"/>
+      <c r="S5" s="122" t="n"/>
+      <c r="T5" s="125" t="n"/>
+      <c r="V5" s="16" t="inlineStr">
         <is>
           <t>ESCO</t>
         </is>
       </c>
-      <c r="W5" s="24" t="inlineStr">
+      <c r="W5" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X5" s="201" t="n">
+      <c r="X5" s="121" t="n">
         <v>17</v>
       </c>
-      <c r="Y5" s="202" t="n"/>
-      <c r="Z5" s="202" t="n">
+      <c r="Y5" s="122" t="n"/>
+      <c r="Z5" s="122" t="n">
         <v>28</v>
       </c>
-      <c r="AA5" s="202" t="n"/>
-      <c r="AB5" s="202" t="n">
+      <c r="AA5" s="122" t="n"/>
+      <c r="AB5" s="122" t="n">
         <v>3</v>
       </c>
-      <c r="AC5" s="202" t="n"/>
-      <c r="AD5" s="202" t="n"/>
-      <c r="AE5" s="202" t="n"/>
-      <c r="AF5" s="203" t="n"/>
-      <c r="AG5" s="204" t="n"/>
-      <c r="AH5" s="202" t="n"/>
-      <c r="AI5" s="202" t="n"/>
-      <c r="AJ5" s="202" t="n"/>
-      <c r="AK5" s="202" t="n"/>
-      <c r="AL5" s="202" t="n"/>
-      <c r="AM5" s="202" t="n"/>
-      <c r="AN5" s="202" t="n"/>
-      <c r="AO5" s="205" t="n"/>
-    </row>
-    <row r="6" ht="15" customFormat="1" customHeight="1" s="19">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="AC5" s="122" t="n"/>
+      <c r="AD5" s="122" t="n"/>
+      <c r="AE5" s="122" t="n"/>
+      <c r="AF5" s="123" t="n"/>
+      <c r="AG5" s="124" t="n"/>
+      <c r="AH5" s="122" t="n"/>
+      <c r="AI5" s="122" t="n"/>
+      <c r="AJ5" s="122" t="n"/>
+      <c r="AK5" s="122" t="n"/>
+      <c r="AL5" s="122" t="n"/>
+      <c r="AM5" s="122" t="n"/>
+      <c r="AN5" s="122" t="n"/>
+      <c r="AO5" s="125" t="n"/>
+    </row>
+    <row r="6" ht="15" customFormat="1" customHeight="1" s="15">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>ESCO #2</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C6" s="201" t="n">
+      <c r="C6" s="121" t="n">
         <v>19</v>
       </c>
-      <c r="D6" s="202" t="n"/>
-      <c r="E6" s="202" t="n">
+      <c r="D6" s="122" t="n"/>
+      <c r="E6" s="122" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="202" t="n"/>
-      <c r="G6" s="202" t="n">
+      <c r="F6" s="122" t="n"/>
+      <c r="G6" s="122" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="202" t="n"/>
-      <c r="I6" s="202" t="n"/>
-      <c r="J6" s="202" t="n"/>
-      <c r="K6" s="203" t="n"/>
-      <c r="L6" s="204" t="n">
+      <c r="H6" s="122" t="n"/>
+      <c r="I6" s="122" t="n"/>
+      <c r="J6" s="122" t="n"/>
+      <c r="K6" s="123" t="n"/>
+      <c r="L6" s="124" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="202" t="n"/>
-      <c r="N6" s="202" t="n">
+      <c r="M6" s="122" t="n"/>
+      <c r="N6" s="122" t="n">
         <v>14</v>
       </c>
-      <c r="O6" s="202" t="n"/>
-      <c r="P6" s="202" t="n"/>
-      <c r="Q6" s="202" t="n"/>
-      <c r="R6" s="202" t="n"/>
-      <c r="S6" s="202" t="n"/>
-      <c r="T6" s="205" t="n"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O6" s="122" t="n"/>
+      <c r="P6" s="122" t="n"/>
+      <c r="Q6" s="122" t="n"/>
+      <c r="R6" s="122" t="n"/>
+      <c r="S6" s="122" t="n"/>
+      <c r="T6" s="125" t="n"/>
+      <c r="V6" s="16" t="inlineStr">
         <is>
           <t>LCIT</t>
         </is>
       </c>
-      <c r="W6" s="24" t="inlineStr">
+      <c r="W6" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X6" s="201" t="n">
+      <c r="X6" s="121" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="202" t="n"/>
-      <c r="Z6" s="202" t="n">
+      <c r="Y6" s="122" t="n"/>
+      <c r="Z6" s="122" t="n">
         <v>5</v>
       </c>
-      <c r="AA6" s="202" t="n"/>
-      <c r="AB6" s="202" t="n"/>
-      <c r="AC6" s="202" t="n"/>
-      <c r="AD6" s="202" t="n"/>
-      <c r="AE6" s="202" t="n"/>
-      <c r="AF6" s="203" t="n"/>
-      <c r="AG6" s="204" t="n"/>
-      <c r="AH6" s="202" t="n"/>
-      <c r="AI6" s="202" t="n"/>
-      <c r="AJ6" s="202" t="n"/>
-      <c r="AK6" s="202" t="n"/>
-      <c r="AL6" s="202" t="n"/>
-      <c r="AM6" s="202" t="n"/>
-      <c r="AN6" s="202" t="n"/>
-      <c r="AO6" s="205" t="n"/>
-    </row>
-    <row r="7" ht="15" customFormat="1" customHeight="1" s="34">
-      <c r="A7" s="136" t="inlineStr">
+      <c r="AA6" s="122" t="n"/>
+      <c r="AB6" s="122" t="n"/>
+      <c r="AC6" s="122" t="n"/>
+      <c r="AD6" s="122" t="n"/>
+      <c r="AE6" s="122" t="n"/>
+      <c r="AF6" s="123" t="n"/>
+      <c r="AG6" s="124" t="n"/>
+      <c r="AH6" s="122" t="n"/>
+      <c r="AI6" s="122" t="n"/>
+      <c r="AJ6" s="122" t="n"/>
+      <c r="AK6" s="122" t="n"/>
+      <c r="AL6" s="122" t="n"/>
+      <c r="AM6" s="122" t="n"/>
+      <c r="AN6" s="122" t="n"/>
+      <c r="AO6" s="125" t="n"/>
+    </row>
+    <row r="7" ht="15" customFormat="1" customHeight="1" s="25">
+      <c r="A7" s="111" t="inlineStr">
         <is>
           <t>BMTP</t>
         </is>
       </c>
-      <c r="B7" s="137" t="inlineStr">
+      <c r="B7" s="112" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C7" s="201" t="n">
+      <c r="C7" s="121" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="202" t="n"/>
-      <c r="E7" s="202" t="n"/>
-      <c r="F7" s="202" t="n"/>
-      <c r="G7" s="202" t="n"/>
-      <c r="H7" s="202" t="n"/>
-      <c r="I7" s="202" t="n"/>
-      <c r="J7" s="202" t="n"/>
-      <c r="K7" s="203" t="n"/>
-      <c r="L7" s="204" t="n"/>
-      <c r="M7" s="202" t="n"/>
-      <c r="N7" s="202" t="n"/>
-      <c r="O7" s="202" t="n"/>
-      <c r="P7" s="202" t="n"/>
-      <c r="Q7" s="202" t="n"/>
-      <c r="R7" s="202" t="n"/>
-      <c r="S7" s="202" t="n"/>
-      <c r="T7" s="205" t="n"/>
-      <c r="V7" s="23" t="inlineStr">
+      <c r="D7" s="122" t="n"/>
+      <c r="E7" s="122" t="n"/>
+      <c r="F7" s="122" t="n"/>
+      <c r="G7" s="122" t="n"/>
+      <c r="H7" s="122" t="n"/>
+      <c r="I7" s="122" t="n"/>
+      <c r="J7" s="122" t="n"/>
+      <c r="K7" s="123" t="n"/>
+      <c r="L7" s="124" t="n"/>
+      <c r="M7" s="122" t="n"/>
+      <c r="N7" s="122" t="n"/>
+      <c r="O7" s="122" t="n"/>
+      <c r="P7" s="122" t="n"/>
+      <c r="Q7" s="122" t="n"/>
+      <c r="R7" s="122" t="n"/>
+      <c r="S7" s="122" t="n"/>
+      <c r="T7" s="125" t="n"/>
+      <c r="V7" s="16" t="inlineStr">
         <is>
           <t>HPT</t>
         </is>
       </c>
-      <c r="W7" s="24" t="inlineStr">
+      <c r="W7" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X7" s="201" t="n">
+      <c r="X7" s="121" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="202" t="n"/>
-      <c r="Z7" s="202" t="n">
+      <c r="Y7" s="122" t="n"/>
+      <c r="Z7" s="122" t="n">
         <v>5</v>
       </c>
-      <c r="AA7" s="202" t="n"/>
-      <c r="AB7" s="202" t="n"/>
-      <c r="AC7" s="202" t="n"/>
-      <c r="AD7" s="202" t="n"/>
-      <c r="AE7" s="202" t="n"/>
-      <c r="AF7" s="203" t="n"/>
-      <c r="AG7" s="204" t="n"/>
-      <c r="AH7" s="202" t="n"/>
-      <c r="AI7" s="202" t="n"/>
-      <c r="AJ7" s="202" t="n"/>
-      <c r="AK7" s="202" t="n"/>
-      <c r="AL7" s="202" t="n"/>
-      <c r="AM7" s="202" t="n"/>
-      <c r="AN7" s="202" t="n"/>
-      <c r="AO7" s="205" t="n"/>
+      <c r="AA7" s="122" t="n"/>
+      <c r="AB7" s="122" t="n"/>
+      <c r="AC7" s="122" t="n"/>
+      <c r="AD7" s="122" t="n"/>
+      <c r="AE7" s="122" t="n"/>
+      <c r="AF7" s="123" t="n"/>
+      <c r="AG7" s="124" t="n"/>
+      <c r="AH7" s="122" t="n"/>
+      <c r="AI7" s="122" t="n"/>
+      <c r="AJ7" s="122" t="n"/>
+      <c r="AK7" s="122" t="n"/>
+      <c r="AL7" s="122" t="n"/>
+      <c r="AM7" s="122" t="n"/>
+      <c r="AN7" s="122" t="n"/>
+      <c r="AO7" s="125" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C8" s="206" t="n"/>
-      <c r="D8" s="207" t="n"/>
-      <c r="E8" s="207" t="n"/>
-      <c r="F8" s="207" t="n"/>
-      <c r="G8" s="207" t="n"/>
-      <c r="H8" s="207" t="n"/>
-      <c r="I8" s="207" t="n"/>
-      <c r="J8" s="207" t="n"/>
-      <c r="K8" s="208" t="n"/>
-      <c r="L8" s="209" t="n">
+      <c r="C8" s="126" t="n"/>
+      <c r="D8" s="127" t="n"/>
+      <c r="E8" s="127" t="n"/>
+      <c r="F8" s="127" t="n"/>
+      <c r="G8" s="127" t="n"/>
+      <c r="H8" s="127" t="n"/>
+      <c r="I8" s="127" t="n"/>
+      <c r="J8" s="127" t="n"/>
+      <c r="K8" s="128" t="n"/>
+      <c r="L8" s="129" t="n">
         <v>820</v>
       </c>
-      <c r="M8" s="210" t="n"/>
-      <c r="N8" s="210" t="n">
+      <c r="M8" s="130" t="n"/>
+      <c r="N8" s="130" t="n">
         <v>835</v>
       </c>
-      <c r="O8" s="210" t="n"/>
-      <c r="P8" s="210" t="n"/>
-      <c r="Q8" s="210" t="n"/>
-      <c r="R8" s="210" t="n"/>
-      <c r="S8" s="210" t="n"/>
-      <c r="T8" s="211" t="n"/>
-      <c r="V8" s="35" t="inlineStr">
+      <c r="O8" s="130" t="n"/>
+      <c r="P8" s="130" t="n"/>
+      <c r="Q8" s="130" t="n"/>
+      <c r="R8" s="130" t="n"/>
+      <c r="S8" s="130" t="n"/>
+      <c r="T8" s="131" t="n"/>
+      <c r="V8" s="26" t="inlineStr">
         <is>
           <t>HAST</t>
         </is>
       </c>
-      <c r="W8" s="36" t="inlineStr">
+      <c r="W8" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X8" s="206" t="n"/>
-      <c r="Y8" s="207" t="n"/>
-      <c r="Z8" s="207" t="n"/>
-      <c r="AA8" s="207" t="n"/>
-      <c r="AB8" s="207" t="n"/>
-      <c r="AC8" s="207" t="n"/>
-      <c r="AD8" s="207" t="n"/>
-      <c r="AE8" s="207" t="n"/>
-      <c r="AF8" s="208" t="n"/>
-      <c r="AG8" s="209" t="n">
+      <c r="X8" s="126" t="n"/>
+      <c r="Y8" s="127" t="n"/>
+      <c r="Z8" s="127" t="n"/>
+      <c r="AA8" s="127" t="n"/>
+      <c r="AB8" s="127" t="n"/>
+      <c r="AC8" s="127" t="n"/>
+      <c r="AD8" s="127" t="n"/>
+      <c r="AE8" s="127" t="n"/>
+      <c r="AF8" s="128" t="n"/>
+      <c r="AG8" s="129" t="n">
         <v>803</v>
       </c>
-      <c r="AH8" s="210" t="n"/>
-      <c r="AI8" s="210" t="n">
+      <c r="AH8" s="130" t="n"/>
+      <c r="AI8" s="130" t="n">
         <v>174</v>
       </c>
-      <c r="AJ8" s="210" t="n">
+      <c r="AJ8" s="130" t="n">
         <v>8</v>
       </c>
-      <c r="AK8" s="210" t="n">
+      <c r="AK8" s="130" t="n">
         <v>60</v>
       </c>
-      <c r="AL8" s="210" t="n"/>
-      <c r="AM8" s="210" t="n"/>
-      <c r="AN8" s="210" t="n"/>
-      <c r="AO8" s="211" t="n">
+      <c r="AL8" s="130" t="n"/>
+      <c r="AM8" s="130" t="n"/>
+      <c r="AN8" s="130" t="n"/>
+      <c r="AO8" s="131" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>BC2</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C9" s="206" t="n"/>
-      <c r="D9" s="207" t="n"/>
-      <c r="E9" s="207" t="n"/>
-      <c r="F9" s="207" t="n"/>
-      <c r="G9" s="207" t="n"/>
-      <c r="H9" s="207" t="n"/>
-      <c r="I9" s="207" t="n"/>
-      <c r="J9" s="207" t="n"/>
-      <c r="K9" s="208" t="n"/>
-      <c r="L9" s="209" t="n">
+      <c r="C9" s="126" t="n"/>
+      <c r="D9" s="127" t="n"/>
+      <c r="E9" s="127" t="n"/>
+      <c r="F9" s="127" t="n"/>
+      <c r="G9" s="127" t="n"/>
+      <c r="H9" s="127" t="n"/>
+      <c r="I9" s="127" t="n"/>
+      <c r="J9" s="127" t="n"/>
+      <c r="K9" s="128" t="n"/>
+      <c r="L9" s="129" t="n">
         <v>840</v>
       </c>
-      <c r="M9" s="210" t="n">
+      <c r="M9" s="130" t="n">
         <v>5</v>
       </c>
-      <c r="N9" s="210" t="n">
+      <c r="N9" s="130" t="n">
         <v>749</v>
       </c>
-      <c r="O9" s="210" t="n">
+      <c r="O9" s="130" t="n">
         <v>31</v>
       </c>
-      <c r="P9" s="210" t="n">
+      <c r="P9" s="130" t="n">
         <v>47</v>
       </c>
-      <c r="Q9" s="210" t="n"/>
-      <c r="R9" s="210" t="n"/>
-      <c r="S9" s="210" t="n"/>
-      <c r="T9" s="211" t="n"/>
-      <c r="V9" s="35" t="inlineStr">
+      <c r="Q9" s="130" t="n"/>
+      <c r="R9" s="130" t="n"/>
+      <c r="S9" s="130" t="n"/>
+      <c r="T9" s="131" t="n"/>
+      <c r="V9" s="26" t="inlineStr">
         <is>
           <t>CELLO</t>
         </is>
       </c>
-      <c r="W9" s="36" t="inlineStr">
+      <c r="W9" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X9" s="206" t="n"/>
-      <c r="Y9" s="207" t="n"/>
-      <c r="Z9" s="207" t="n"/>
-      <c r="AA9" s="207" t="n"/>
-      <c r="AB9" s="207" t="n"/>
-      <c r="AC9" s="207" t="n"/>
-      <c r="AD9" s="207" t="n"/>
-      <c r="AE9" s="207" t="n"/>
-      <c r="AF9" s="208" t="n"/>
-      <c r="AG9" s="209" t="n">
+      <c r="X9" s="126" t="n"/>
+      <c r="Y9" s="127" t="n"/>
+      <c r="Z9" s="127" t="n"/>
+      <c r="AA9" s="127" t="n"/>
+      <c r="AB9" s="127" t="n"/>
+      <c r="AC9" s="127" t="n"/>
+      <c r="AD9" s="127" t="n"/>
+      <c r="AE9" s="127" t="n"/>
+      <c r="AF9" s="128" t="n"/>
+      <c r="AG9" s="129" t="n">
         <v>43</v>
       </c>
-      <c r="AH9" s="210" t="n"/>
-      <c r="AI9" s="210" t="n">
+      <c r="AH9" s="130" t="n"/>
+      <c r="AI9" s="130" t="n">
         <v>32</v>
       </c>
-      <c r="AJ9" s="210" t="n"/>
-      <c r="AK9" s="210" t="n"/>
-      <c r="AL9" s="210" t="n"/>
-      <c r="AM9" s="210" t="n"/>
-      <c r="AN9" s="210" t="n"/>
-      <c r="AO9" s="211" t="n"/>
+      <c r="AJ9" s="130" t="n"/>
+      <c r="AK9" s="130" t="n"/>
+      <c r="AL9" s="130" t="n"/>
+      <c r="AM9" s="130" t="n"/>
+      <c r="AN9" s="130" t="n"/>
+      <c r="AO9" s="131" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="28" t="n"/>
-      <c r="K10" s="42" t="n"/>
-      <c r="L10" s="35" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
-      <c r="P10" s="29" t="n"/>
-      <c r="Q10" s="29" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="29" t="n"/>
-      <c r="T10" s="30" t="n"/>
-      <c r="V10" s="35" t="inlineStr">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="33" t="n"/>
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="V10" s="26" t="inlineStr">
         <is>
           <t>PW</t>
         </is>
       </c>
-      <c r="W10" s="36" t="inlineStr">
+      <c r="W10" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X10" s="206" t="n"/>
-      <c r="Y10" s="207" t="n"/>
-      <c r="Z10" s="207" t="n"/>
-      <c r="AA10" s="207" t="n"/>
-      <c r="AB10" s="207" t="n"/>
-      <c r="AC10" s="207" t="n"/>
-      <c r="AD10" s="207" t="n"/>
-      <c r="AE10" s="207" t="n"/>
-      <c r="AF10" s="208" t="n"/>
-      <c r="AG10" s="209" t="n">
+      <c r="X10" s="126" t="n"/>
+      <c r="Y10" s="127" t="n"/>
+      <c r="Z10" s="127" t="n"/>
+      <c r="AA10" s="127" t="n"/>
+      <c r="AB10" s="127" t="n"/>
+      <c r="AC10" s="127" t="n"/>
+      <c r="AD10" s="127" t="n"/>
+      <c r="AE10" s="127" t="n"/>
+      <c r="AF10" s="128" t="n"/>
+      <c r="AG10" s="129" t="n">
         <v>1239</v>
       </c>
-      <c r="AH10" s="210" t="n">
+      <c r="AH10" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="AI10" s="210" t="n">
+      <c r="AI10" s="130" t="n">
         <v>705</v>
       </c>
-      <c r="AJ10" s="210" t="n"/>
-      <c r="AK10" s="210" t="n"/>
-      <c r="AL10" s="210" t="n"/>
-      <c r="AM10" s="210" t="n">
+      <c r="AJ10" s="130" t="n"/>
+      <c r="AK10" s="130" t="n"/>
+      <c r="AL10" s="130" t="n"/>
+      <c r="AM10" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="AN10" s="210" t="n">
+      <c r="AN10" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="AO10" s="211" t="n">
+      <c r="AO10" s="131" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="43" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="28" t="n"/>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="35" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="29" t="n"/>
-      <c r="P11" s="29" t="n"/>
-      <c r="Q11" s="29" t="n"/>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="29" t="n"/>
-      <c r="T11" s="30" t="n"/>
-      <c r="V11" s="35" t="n"/>
-      <c r="W11" s="36" t="n"/>
-      <c r="X11" s="39" t="n"/>
-      <c r="Y11" s="29" t="n"/>
-      <c r="Z11" s="29" t="n"/>
-      <c r="AA11" s="29" t="n"/>
-      <c r="AB11" s="29" t="n"/>
-      <c r="AC11" s="29" t="n"/>
-      <c r="AD11" s="29" t="n"/>
-      <c r="AE11" s="29" t="n"/>
-      <c r="AF11" s="40" t="n"/>
-      <c r="AG11" s="35" t="n"/>
-      <c r="AH11" s="29" t="n"/>
-      <c r="AI11" s="29" t="n"/>
-      <c r="AJ11" s="29" t="n"/>
-      <c r="AK11" s="29" t="n"/>
-      <c r="AL11" s="29" t="n"/>
-      <c r="AM11" s="29" t="n"/>
-      <c r="AN11" s="29" t="n"/>
-      <c r="AO11" s="30" t="n"/>
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="33" t="n"/>
+      <c r="L11" s="26" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="V11" s="26" t="n"/>
+      <c r="W11" s="27" t="n"/>
+      <c r="X11" s="30" t="n"/>
+      <c r="Y11" s="22" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="22" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="22" t="n"/>
+      <c r="AF11" s="31" t="n"/>
+      <c r="AG11" s="26" t="n"/>
+      <c r="AH11" s="22" t="n"/>
+      <c r="AI11" s="22" t="n"/>
+      <c r="AJ11" s="22" t="n"/>
+      <c r="AK11" s="22" t="n"/>
+      <c r="AL11" s="22" t="n"/>
+      <c r="AM11" s="22" t="n"/>
+      <c r="AN11" s="22" t="n"/>
+      <c r="AO11" s="23" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="43" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="28" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="35" t="n"/>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="29" t="n"/>
-      <c r="P12" s="29" t="n"/>
-      <c r="Q12" s="29" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="29" t="n"/>
-      <c r="T12" s="30" t="n"/>
-      <c r="V12" s="35" t="n"/>
-      <c r="W12" s="36" t="n"/>
-      <c r="X12" s="39" t="n"/>
-      <c r="Y12" s="29" t="n"/>
-      <c r="Z12" s="29" t="n"/>
-      <c r="AA12" s="29" t="n"/>
-      <c r="AB12" s="29" t="n"/>
-      <c r="AC12" s="29" t="n"/>
-      <c r="AD12" s="29" t="n"/>
-      <c r="AE12" s="29" t="n"/>
-      <c r="AF12" s="40" t="n"/>
-      <c r="AG12" s="35" t="n"/>
-      <c r="AH12" s="29" t="n"/>
-      <c r="AI12" s="29" t="n"/>
-      <c r="AJ12" s="29" t="n"/>
-      <c r="AK12" s="29" t="n"/>
-      <c r="AL12" s="29" t="n"/>
-      <c r="AM12" s="29" t="n"/>
-      <c r="AN12" s="29" t="n"/>
-      <c r="AO12" s="30" t="n"/>
+      <c r="A12" s="34" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="33" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="V12" s="26" t="n"/>
+      <c r="W12" s="27" t="n"/>
+      <c r="X12" s="30" t="n"/>
+      <c r="Y12" s="22" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="22" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="22" t="n"/>
+      <c r="AF12" s="31" t="n"/>
+      <c r="AG12" s="26" t="n"/>
+      <c r="AH12" s="22" t="n"/>
+      <c r="AI12" s="22" t="n"/>
+      <c r="AJ12" s="22" t="n"/>
+      <c r="AK12" s="22" t="n"/>
+      <c r="AL12" s="22" t="n"/>
+      <c r="AM12" s="22" t="n"/>
+      <c r="AN12" s="22" t="n"/>
+      <c r="AO12" s="23" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="26" t="n"/>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="50" t="n"/>
-      <c r="M13" s="51" t="n"/>
-      <c r="N13" s="51" t="n"/>
-      <c r="O13" s="51" t="n"/>
-      <c r="P13" s="51" t="n"/>
-      <c r="Q13" s="51" t="n"/>
-      <c r="R13" s="51" t="n"/>
-      <c r="S13" s="51" t="n"/>
-      <c r="T13" s="52" t="n"/>
-      <c r="V13" s="45" t="inlineStr">
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="41" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="42" t="n"/>
+      <c r="O13" s="42" t="n"/>
+      <c r="P13" s="42" t="n"/>
+      <c r="Q13" s="42" t="n"/>
+      <c r="R13" s="42" t="n"/>
+      <c r="S13" s="42" t="n"/>
+      <c r="T13" s="43" t="n"/>
+      <c r="V13" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="W13" s="46" t="n"/>
-      <c r="X13" s="91" t="n"/>
-      <c r="Y13" s="92" t="n"/>
-      <c r="Z13" s="92" t="n"/>
-      <c r="AA13" s="92" t="n"/>
-      <c r="AB13" s="92" t="n"/>
-      <c r="AC13" s="92" t="n"/>
-      <c r="AD13" s="92" t="n"/>
-      <c r="AE13" s="92" t="n"/>
-      <c r="AF13" s="93" t="n"/>
-      <c r="AG13" s="50" t="n"/>
-      <c r="AH13" s="51" t="n"/>
-      <c r="AI13" s="51" t="n"/>
-      <c r="AJ13" s="51" t="n"/>
-      <c r="AK13" s="51" t="n"/>
-      <c r="AL13" s="51" t="n"/>
-      <c r="AM13" s="51" t="n"/>
-      <c r="AN13" s="51" t="n"/>
-      <c r="AO13" s="52" t="n"/>
-      <c r="AR13" s="3" t="inlineStr">
+      <c r="W13" s="37" t="n"/>
+      <c r="X13" s="72" t="n"/>
+      <c r="Y13" s="73" t="n"/>
+      <c r="Z13" s="73" t="n"/>
+      <c r="AA13" s="73" t="n"/>
+      <c r="AB13" s="73" t="n"/>
+      <c r="AC13" s="73" t="n"/>
+      <c r="AD13" s="73" t="n"/>
+      <c r="AE13" s="73" t="n"/>
+      <c r="AF13" s="74" t="n"/>
+      <c r="AG13" s="41" t="n"/>
+      <c r="AH13" s="42" t="n"/>
+      <c r="AI13" s="42" t="n"/>
+      <c r="AJ13" s="42" t="n"/>
+      <c r="AK13" s="42" t="n"/>
+      <c r="AL13" s="42" t="n"/>
+      <c r="AM13" s="42" t="n"/>
+      <c r="AN13" s="42" t="n"/>
+      <c r="AO13" s="43" t="n"/>
+      <c r="AR13" s="165" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>REPO (E/P)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="50" t="n"/>
-      <c r="M14" s="51" t="n"/>
-      <c r="N14" s="51" t="n"/>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="n"/>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="n"/>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="52" t="n"/>
-      <c r="V14" s="45" t="inlineStr">
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="199" t="n"/>
+      <c r="M14" s="200" t="n"/>
+      <c r="N14" s="200" t="n"/>
+      <c r="O14" s="200" t="n"/>
+      <c r="P14" s="200" t="n"/>
+      <c r="Q14" s="200" t="n"/>
+      <c r="R14" s="200" t="n"/>
+      <c r="S14" s="200" t="n"/>
+      <c r="T14" s="201" t="n"/>
+      <c r="V14" s="36" t="inlineStr">
         <is>
           <t>REPO (E/P)</t>
         </is>
       </c>
-      <c r="W14" s="47" t="n"/>
-      <c r="X14" s="25" t="n"/>
-      <c r="Y14" s="26" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="26" t="n"/>
-      <c r="AB14" s="26" t="n"/>
-      <c r="AC14" s="26" t="n"/>
-      <c r="AD14" s="26" t="n"/>
-      <c r="AE14" s="26" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="50" t="n"/>
-      <c r="AH14" s="51" t="n"/>
-      <c r="AI14" s="51" t="n"/>
-      <c r="AJ14" s="51" t="n"/>
-      <c r="AK14" s="51" t="n"/>
-      <c r="AL14" s="51" t="n"/>
-      <c r="AM14" s="51" t="n"/>
-      <c r="AN14" s="51" t="n"/>
-      <c r="AO14" s="52" t="n"/>
+      <c r="W14" s="38" t="n"/>
+      <c r="X14" s="18" t="n"/>
+      <c r="Y14" s="19" t="n"/>
+      <c r="Z14" s="19" t="n"/>
+      <c r="AA14" s="19" t="n"/>
+      <c r="AB14" s="19" t="n"/>
+      <c r="AC14" s="19" t="n"/>
+      <c r="AD14" s="19" t="n"/>
+      <c r="AE14" s="19" t="n"/>
+      <c r="AF14" s="20" t="n"/>
+      <c r="AG14" s="199" t="n">
+        <v>169</v>
+      </c>
+      <c r="AH14" s="200" t="n"/>
+      <c r="AI14" s="200" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ14" s="200" t="n"/>
+      <c r="AK14" s="200" t="n"/>
+      <c r="AL14" s="200" t="n"/>
+      <c r="AM14" s="200" t="n"/>
+      <c r="AN14" s="200" t="n"/>
+      <c r="AO14" s="201" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="212" t="inlineStr">
+      <c r="A15" s="181" t="inlineStr">
         <is>
           <t>TOTAL AT BKK</t>
         </is>
       </c>
-      <c r="B15" s="213" t="n"/>
-      <c r="C15" s="54">
+      <c r="B15" s="182" t="n"/>
+      <c r="C15" s="45">
         <f>SUM(C4:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="46">
         <f>SUM(D4:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="46">
         <f>SUM(E4:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="46">
         <f>SUM(F4:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="46">
         <f>SUM(G4:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="46">
         <f>SUM(H4:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="46">
         <f>SUM(I4:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="55">
+      <c r="J15" s="46">
         <f>SUM(J4:J14)</f>
         <v/>
       </c>
-      <c r="K15" s="56">
+      <c r="K15" s="47">
         <f>SUM(K4:K14)</f>
         <v/>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="48">
         <f>SUM(L4:L14)</f>
         <v/>
       </c>
-      <c r="M15" s="58">
+      <c r="M15" s="49">
         <f>SUM(M4:M14)</f>
         <v/>
       </c>
-      <c r="N15" s="58">
+      <c r="N15" s="49">
         <f>SUM(N4:N14)</f>
         <v/>
       </c>
-      <c r="O15" s="58">
+      <c r="O15" s="49">
         <f>SUM(O4:O14)</f>
         <v/>
       </c>
-      <c r="P15" s="58">
+      <c r="P15" s="49">
         <f>SUM(P4:P14)</f>
         <v/>
       </c>
-      <c r="Q15" s="58">
+      <c r="Q15" s="49">
         <f>SUM(Q4:Q14)</f>
         <v/>
       </c>
-      <c r="R15" s="58">
+      <c r="R15" s="49">
         <f>SUM(R4:R14)</f>
         <v/>
       </c>
-      <c r="S15" s="58">
+      <c r="S15" s="49">
         <f>SUM(S4:S14)</f>
         <v/>
       </c>
-      <c r="T15" s="59">
+      <c r="T15" s="50">
         <f>SUM(T4:T14)</f>
         <v/>
       </c>
       <c r="U15" s="9" t="n"/>
-      <c r="V15" s="212" t="inlineStr">
+      <c r="V15" s="181" t="inlineStr">
         <is>
           <t>TOTAL AT LCH</t>
         </is>
       </c>
-      <c r="W15" s="213" t="n"/>
-      <c r="X15" s="54">
+      <c r="W15" s="182" t="n"/>
+      <c r="X15" s="45">
         <f>SUM(X4:X14)</f>
         <v/>
       </c>
-      <c r="Y15" s="55">
+      <c r="Y15" s="46">
         <f>SUM(Y4:Y14)</f>
         <v/>
       </c>
-      <c r="Z15" s="55">
+      <c r="Z15" s="46">
         <f>SUM(Z4:Z14)</f>
         <v/>
       </c>
-      <c r="AA15" s="55">
+      <c r="AA15" s="46">
         <f>SUM(AA4:AA14)</f>
         <v/>
       </c>
-      <c r="AB15" s="55">
+      <c r="AB15" s="46">
         <f>SUM(AB4:AB14)</f>
         <v/>
       </c>
-      <c r="AC15" s="55">
+      <c r="AC15" s="46">
         <f>SUM(AC4:AC14)</f>
         <v/>
       </c>
-      <c r="AD15" s="55">
+      <c r="AD15" s="46">
         <f>SUM(AD4:AD14)</f>
         <v/>
       </c>
-      <c r="AE15" s="55">
+      <c r="AE15" s="46">
         <f>SUM(AE4:AE14)</f>
         <v/>
       </c>
-      <c r="AF15" s="56">
+      <c r="AF15" s="47">
         <f>SUM(AF4:AF14)</f>
         <v/>
       </c>
-      <c r="AG15" s="57">
-        <f>AG13+AG12+AG11+AG10+AG9+AG8+AG7+AG6+AG5+AG4</f>
-        <v/>
-      </c>
-      <c r="AH15" s="58">
-        <f>AH13+AH12+AH11+AH10+AH9+AH8+AH7+AH6+AH5+AH4</f>
-        <v/>
-      </c>
-      <c r="AI15" s="58">
-        <f>AI13+AI12+AI11+AI10+AI9+AI8+AI7+AI6+AI5+AI4</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="58">
-        <f>AJ13+AJ12+AJ11+AJ10+AJ9+AJ8+AJ7+AJ6+AJ5+AJ4</f>
-        <v/>
-      </c>
-      <c r="AK15" s="58">
-        <f>AK13+AK12+AK11+AK10+AK9+AK8+AK7+AK6+AK5+AK4</f>
-        <v/>
-      </c>
-      <c r="AL15" s="58">
-        <f>AL13+AL12+AL11+AL10+AL9+AL8+AL7+AL6+AL5+AL4</f>
-        <v/>
-      </c>
-      <c r="AM15" s="58">
-        <f>AM13+AM12+AM11+AM10+AM9+AM8+AM7+AM6+AM5+AM4</f>
-        <v/>
-      </c>
-      <c r="AN15" s="58">
-        <f>AN13+AN12+AN11+AN10+AN9+AN8+AN7+AN6+AN5+AN4</f>
-        <v/>
-      </c>
-      <c r="AO15" s="59">
-        <f>AO13+AO12+AO11+AO10+AO9+AO8+AO7+AO6+AO5+AO4</f>
+      <c r="AG15" s="48">
+        <f>AG13+AG12+AG11+AG10+AG9+AG8+AG7+AG6+AG5+AG4+AG14</f>
+        <v/>
+      </c>
+      <c r="AH15" s="49">
+        <f>AH13+AH12+AH11+AH10+AH9+AH8+AH7+AH6+AH5+AH4+AH14</f>
+        <v/>
+      </c>
+      <c r="AI15" s="49">
+        <f>AI13+AI12+AI11+AI10+AI9+AI8+AI7+AI6+AI5+AI4+AI14</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="49">
+        <f>AJ13+AJ12+AJ11+AJ10+AJ9+AJ8+AJ7+AJ6+AJ5+AJ4+AJ14</f>
+        <v/>
+      </c>
+      <c r="AK15" s="49">
+        <f>AK13+AK12+AK11+AK10+AK9+AK8+AK7+AK6+AK5+AK4+AK14</f>
+        <v/>
+      </c>
+      <c r="AL15" s="49">
+        <f>AL13+AL12+AL11+AL10+AL9+AL8+AL7+AL6+AL5+AL4+AL14</f>
+        <v/>
+      </c>
+      <c r="AM15" s="49">
+        <f>AM13+AM12+AM11+AM10+AM9+AM8+AM7+AM6+AM5+AM4+AM14</f>
+        <v/>
+      </c>
+      <c r="AN15" s="49">
+        <f>AN13+AN12+AN11+AN10+AN9+AN8+AN7+AN6+AN5+AN4+AN14</f>
+        <v/>
+      </c>
+      <c r="AO15" s="50">
+        <f>AO13+AO12+AO11+AO10+AO9+AO8+AO7+AO6+AO5+AO4+AO14</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="12.75" customHeight="1">
-      <c r="A16" s="60" t="n"/>
-      <c r="B16" s="61" t="n"/>
-      <c r="V16" s="60" t="n"/>
-      <c r="W16" s="61" t="n"/>
-      <c r="AO16" s="61" t="n"/>
+      <c r="A16" s="51" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="V16" s="51" t="n"/>
+      <c r="W16" s="52" t="n"/>
+      <c r="AO16" s="52" t="n"/>
     </row>
     <row r="17" hidden="1" ht="12.75" customHeight="1">
-      <c r="A17" s="153" t="inlineStr">
+      <c r="A17" s="172" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="B17" s="62" t="n"/>
-      <c r="C17" s="151" t="n"/>
-      <c r="D17" s="187" t="n"/>
-      <c r="E17" s="187" t="n"/>
-      <c r="F17" s="187" t="n"/>
-      <c r="G17" s="187" t="n"/>
-      <c r="H17" s="187" t="n"/>
-      <c r="I17" s="187" t="n"/>
-      <c r="J17" s="187" t="n"/>
-      <c r="K17" s="188" t="n"/>
-      <c r="L17" s="144" t="inlineStr">
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="174" t="n"/>
+      <c r="D17" s="167" t="n"/>
+      <c r="E17" s="167" t="n"/>
+      <c r="F17" s="167" t="n"/>
+      <c r="G17" s="167" t="n"/>
+      <c r="H17" s="167" t="n"/>
+      <c r="I17" s="167" t="n"/>
+      <c r="J17" s="167" t="n"/>
+      <c r="K17" s="175" t="n"/>
+      <c r="L17" s="186" t="inlineStr">
         <is>
           <t>STOCK END WK</t>
         </is>
       </c>
-      <c r="M17" s="187" t="n"/>
-      <c r="N17" s="187" t="n"/>
-      <c r="O17" s="187" t="n"/>
-      <c r="P17" s="187" t="n"/>
-      <c r="Q17" s="187" t="n"/>
-      <c r="R17" s="187" t="n"/>
-      <c r="S17" s="187" t="n"/>
-      <c r="T17" s="188" t="n"/>
-      <c r="V17" s="153" t="inlineStr">
+      <c r="M17" s="167" t="n"/>
+      <c r="N17" s="167" t="n"/>
+      <c r="O17" s="167" t="n"/>
+      <c r="P17" s="167" t="n"/>
+      <c r="Q17" s="167" t="n"/>
+      <c r="R17" s="167" t="n"/>
+      <c r="S17" s="167" t="n"/>
+      <c r="T17" s="175" t="n"/>
+      <c r="V17" s="172" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="W17" s="62" t="n"/>
-      <c r="X17" s="151" t="n"/>
-      <c r="Y17" s="187" t="n"/>
-      <c r="Z17" s="187" t="n"/>
-      <c r="AA17" s="187" t="n"/>
-      <c r="AB17" s="187" t="n"/>
-      <c r="AC17" s="187" t="n"/>
-      <c r="AD17" s="187" t="n"/>
-      <c r="AE17" s="187" t="n"/>
-      <c r="AF17" s="188" t="n"/>
-      <c r="AG17" s="144" t="inlineStr">
+      <c r="W17" s="53" t="n"/>
+      <c r="X17" s="174" t="n"/>
+      <c r="Y17" s="167" t="n"/>
+      <c r="Z17" s="167" t="n"/>
+      <c r="AA17" s="167" t="n"/>
+      <c r="AB17" s="167" t="n"/>
+      <c r="AC17" s="167" t="n"/>
+      <c r="AD17" s="167" t="n"/>
+      <c r="AE17" s="167" t="n"/>
+      <c r="AF17" s="175" t="n"/>
+      <c r="AG17" s="186" t="inlineStr">
         <is>
           <t>STOCK END WK</t>
         </is>
       </c>
-      <c r="AH17" s="187" t="n"/>
-      <c r="AI17" s="187" t="n"/>
-      <c r="AJ17" s="187" t="n"/>
-      <c r="AK17" s="187" t="n"/>
-      <c r="AL17" s="187" t="n"/>
-      <c r="AM17" s="187" t="n"/>
-      <c r="AN17" s="187" t="n"/>
-      <c r="AO17" s="188" t="n"/>
+      <c r="AH17" s="167" t="n"/>
+      <c r="AI17" s="167" t="n"/>
+      <c r="AJ17" s="167" t="n"/>
+      <c r="AK17" s="167" t="n"/>
+      <c r="AL17" s="167" t="n"/>
+      <c r="AM17" s="167" t="n"/>
+      <c r="AN17" s="167" t="n"/>
+      <c r="AO17" s="175" t="n"/>
     </row>
     <row r="18" hidden="1" ht="12.75" customHeight="1">
-      <c r="A18" s="214" t="n"/>
-      <c r="B18" s="63" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="38" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="38" t="n"/>
-      <c r="L18" s="38" t="inlineStr">
+      <c r="A18" s="173" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="n"/>
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>22GP</t>
         </is>
       </c>
-      <c r="M18" s="38" t="inlineStr">
+      <c r="M18" s="29" t="inlineStr">
         <is>
           <t>42GP</t>
         </is>
       </c>
-      <c r="N18" s="38" t="inlineStr">
+      <c r="N18" s="29" t="inlineStr">
         <is>
           <t>45GP</t>
         </is>
       </c>
-      <c r="O18" s="38" t="inlineStr">
+      <c r="O18" s="29" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="P18" s="38" t="inlineStr">
+      <c r="P18" s="29" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="Q18" s="38" t="inlineStr">
+      <c r="Q18" s="29" t="inlineStr">
         <is>
           <t>22UT</t>
         </is>
       </c>
-      <c r="R18" s="38" t="inlineStr">
+      <c r="R18" s="29" t="inlineStr">
         <is>
           <t>42UT</t>
         </is>
       </c>
-      <c r="S18" s="38" t="inlineStr">
+      <c r="S18" s="29" t="inlineStr">
         <is>
           <t>22PC</t>
         </is>
       </c>
-      <c r="T18" s="64" t="inlineStr">
+      <c r="T18" s="55" t="inlineStr">
         <is>
           <t>42PC</t>
         </is>
       </c>
-      <c r="V18" s="214" t="n"/>
-      <c r="W18" s="63" t="n"/>
-      <c r="X18" s="37" t="n"/>
-      <c r="Y18" s="38" t="n"/>
-      <c r="Z18" s="38" t="n"/>
-      <c r="AA18" s="38" t="n"/>
-      <c r="AB18" s="38" t="n"/>
-      <c r="AC18" s="38" t="n"/>
-      <c r="AD18" s="38" t="n"/>
-      <c r="AE18" s="38" t="n"/>
-      <c r="AF18" s="38" t="n"/>
-      <c r="AG18" s="38" t="inlineStr">
+      <c r="V18" s="173" t="n"/>
+      <c r="W18" s="54" t="n"/>
+      <c r="X18" s="28" t="n"/>
+      <c r="Y18" s="29" t="n"/>
+      <c r="Z18" s="29" t="n"/>
+      <c r="AA18" s="29" t="n"/>
+      <c r="AB18" s="29" t="n"/>
+      <c r="AC18" s="29" t="n"/>
+      <c r="AD18" s="29" t="n"/>
+      <c r="AE18" s="29" t="n"/>
+      <c r="AF18" s="29" t="n"/>
+      <c r="AG18" s="29" t="inlineStr">
         <is>
           <t>22GP</t>
         </is>
       </c>
-      <c r="AH18" s="38" t="inlineStr">
+      <c r="AH18" s="29" t="inlineStr">
         <is>
           <t>42GP</t>
         </is>
       </c>
-      <c r="AI18" s="38" t="inlineStr">
+      <c r="AI18" s="29" t="inlineStr">
         <is>
           <t>45GP</t>
         </is>
       </c>
-      <c r="AJ18" s="38" t="inlineStr">
+      <c r="AJ18" s="29" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="AK18" s="38" t="inlineStr">
+      <c r="AK18" s="29" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="AL18" s="38" t="inlineStr">
+      <c r="AL18" s="29" t="inlineStr">
         <is>
           <t>22UT</t>
         </is>
       </c>
-      <c r="AM18" s="38" t="inlineStr">
+      <c r="AM18" s="29" t="inlineStr">
         <is>
           <t>42UT</t>
         </is>
       </c>
-      <c r="AN18" s="38" t="inlineStr">
+      <c r="AN18" s="29" t="inlineStr">
         <is>
           <t>22PC</t>
         </is>
       </c>
-      <c r="AO18" s="64" t="inlineStr">
+      <c r="AO18" s="55" t="inlineStr">
         <is>
           <t>42PC</t>
         </is>
       </c>
     </row>
     <row r="19" hidden="1" ht="12.75" customHeight="1">
-      <c r="A19" s="65" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">REPO IN（E/P）　　　　　　　　　</t>
         </is>
       </c>
-      <c r="B19" s="66" t="n"/>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="49" t="n"/>
-      <c r="G19" s="49" t="n"/>
-      <c r="H19" s="49" t="n"/>
-      <c r="I19" s="49" t="n"/>
-      <c r="J19" s="49" t="n"/>
-      <c r="K19" s="49" t="n"/>
-      <c r="L19" s="67" t="n"/>
-      <c r="M19" s="67" t="n"/>
-      <c r="N19" s="67" t="n"/>
-      <c r="O19" s="67" t="n"/>
-      <c r="P19" s="67" t="n"/>
-      <c r="Q19" s="67" t="n"/>
-      <c r="R19" s="67" t="n"/>
-      <c r="S19" s="67" t="n"/>
-      <c r="T19" s="68" t="n"/>
-      <c r="V19" s="65" t="inlineStr">
+      <c r="B19" s="57" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="40" t="n"/>
+      <c r="J19" s="40" t="n"/>
+      <c r="K19" s="40" t="n"/>
+      <c r="L19" s="58" t="n"/>
+      <c r="M19" s="58" t="n"/>
+      <c r="N19" s="58" t="n"/>
+      <c r="O19" s="58" t="n"/>
+      <c r="P19" s="58" t="n"/>
+      <c r="Q19" s="58" t="n"/>
+      <c r="R19" s="58" t="n"/>
+      <c r="S19" s="58" t="n"/>
+      <c r="T19" s="59" t="n"/>
+      <c r="V19" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">REPO IN（E/P）　　　　　　　　　</t>
         </is>
       </c>
-      <c r="W19" s="66" t="n"/>
-      <c r="X19" s="48" t="n"/>
-      <c r="Y19" s="49" t="n"/>
-      <c r="Z19" s="49" t="n"/>
-      <c r="AA19" s="49" t="n"/>
-      <c r="AB19" s="49" t="n"/>
-      <c r="AC19" s="49" t="n"/>
-      <c r="AD19" s="49" t="n"/>
-      <c r="AE19" s="49" t="n"/>
-      <c r="AF19" s="49" t="n"/>
-      <c r="AG19" s="67" t="n"/>
-      <c r="AH19" s="67" t="n"/>
-      <c r="AI19" s="67" t="n"/>
-      <c r="AJ19" s="67" t="n"/>
-      <c r="AK19" s="67" t="n"/>
-      <c r="AL19" s="67" t="n"/>
-      <c r="AM19" s="67" t="n"/>
-      <c r="AN19" s="67" t="n"/>
-      <c r="AO19" s="68" t="n"/>
+      <c r="W19" s="57" t="n"/>
+      <c r="X19" s="39" t="n"/>
+      <c r="Y19" s="40" t="n"/>
+      <c r="Z19" s="40" t="n"/>
+      <c r="AA19" s="40" t="n"/>
+      <c r="AB19" s="40" t="n"/>
+      <c r="AC19" s="40" t="n"/>
+      <c r="AD19" s="40" t="n"/>
+      <c r="AE19" s="40" t="n"/>
+      <c r="AF19" s="40" t="n"/>
+      <c r="AG19" s="58" t="n"/>
+      <c r="AH19" s="58" t="n"/>
+      <c r="AI19" s="58" t="n"/>
+      <c r="AJ19" s="58" t="n"/>
+      <c r="AK19" s="58" t="n"/>
+      <c r="AL19" s="58" t="n"/>
+      <c r="AM19" s="58" t="n"/>
+      <c r="AN19" s="58" t="n"/>
+      <c r="AO19" s="59" t="n"/>
     </row>
     <row r="20" hidden="1" ht="12.75" customHeight="1">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="B20" s="66" t="n"/>
-      <c r="C20" s="48" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="49" t="n"/>
-      <c r="I20" s="49" t="n"/>
-      <c r="J20" s="49" t="n"/>
-      <c r="K20" s="49" t="n"/>
-      <c r="L20" s="67" t="n"/>
-      <c r="M20" s="67" t="n"/>
-      <c r="N20" s="67" t="n"/>
-      <c r="O20" s="67" t="n"/>
-      <c r="P20" s="67" t="n"/>
-      <c r="Q20" s="67" t="n"/>
-      <c r="R20" s="67" t="n"/>
-      <c r="S20" s="67" t="n"/>
-      <c r="T20" s="68" t="n"/>
-      <c r="V20" s="65" t="inlineStr">
+      <c r="B20" s="57" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="40" t="n"/>
+      <c r="L20" s="58" t="n"/>
+      <c r="M20" s="58" t="n"/>
+      <c r="N20" s="58" t="n"/>
+      <c r="O20" s="58" t="n"/>
+      <c r="P20" s="58" t="n"/>
+      <c r="Q20" s="58" t="n"/>
+      <c r="R20" s="58" t="n"/>
+      <c r="S20" s="58" t="n"/>
+      <c r="T20" s="59" t="n"/>
+      <c r="V20" s="56" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="W20" s="66" t="n"/>
-      <c r="X20" s="48" t="n"/>
-      <c r="Y20" s="49" t="n"/>
-      <c r="Z20" s="49" t="n"/>
-      <c r="AA20" s="49" t="n"/>
-      <c r="AB20" s="49" t="n"/>
-      <c r="AC20" s="49" t="n"/>
-      <c r="AD20" s="49" t="n"/>
-      <c r="AE20" s="49" t="n"/>
-      <c r="AF20" s="49" t="n"/>
-      <c r="AG20" s="67" t="n"/>
-      <c r="AH20" s="67" t="n"/>
-      <c r="AI20" s="67" t="n"/>
-      <c r="AJ20" s="67" t="n"/>
-      <c r="AK20" s="67" t="n"/>
-      <c r="AL20" s="67" t="n"/>
-      <c r="AM20" s="67" t="n"/>
-      <c r="AN20" s="67" t="n"/>
-      <c r="AO20" s="68" t="n"/>
+      <c r="W20" s="57" t="n"/>
+      <c r="X20" s="39" t="n"/>
+      <c r="Y20" s="40" t="n"/>
+      <c r="Z20" s="40" t="n"/>
+      <c r="AA20" s="40" t="n"/>
+      <c r="AB20" s="40" t="n"/>
+      <c r="AC20" s="40" t="n"/>
+      <c r="AD20" s="40" t="n"/>
+      <c r="AE20" s="40" t="n"/>
+      <c r="AF20" s="40" t="n"/>
+      <c r="AG20" s="58" t="n"/>
+      <c r="AH20" s="58" t="n"/>
+      <c r="AI20" s="58" t="n"/>
+      <c r="AJ20" s="58" t="n"/>
+      <c r="AK20" s="58" t="n"/>
+      <c r="AL20" s="58" t="n"/>
+      <c r="AM20" s="58" t="n"/>
+      <c r="AN20" s="58" t="n"/>
+      <c r="AO20" s="59" t="n"/>
     </row>
     <row r="21" hidden="1" ht="12.75" customHeight="1">
-      <c r="A21" s="43" t="n"/>
-      <c r="B21" s="44" t="n"/>
-      <c r="C21" s="48" t="n"/>
-      <c r="D21" s="49" t="n"/>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="49" t="n"/>
-      <c r="G21" s="49" t="n"/>
-      <c r="H21" s="49" t="n"/>
-      <c r="I21" s="49" t="n"/>
-      <c r="J21" s="49" t="n"/>
-      <c r="K21" s="49" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="29" t="n"/>
-      <c r="N21" s="29" t="n"/>
-      <c r="O21" s="29" t="n"/>
-      <c r="P21" s="29" t="n"/>
-      <c r="Q21" s="29" t="n"/>
-      <c r="R21" s="29" t="n"/>
-      <c r="S21" s="29" t="n"/>
-      <c r="T21" s="30" t="n"/>
-      <c r="V21" s="43" t="n"/>
-      <c r="W21" s="44" t="n"/>
-      <c r="X21" s="48" t="n"/>
-      <c r="Y21" s="49" t="n"/>
-      <c r="Z21" s="49" t="n"/>
-      <c r="AA21" s="49" t="n"/>
-      <c r="AB21" s="49" t="n"/>
-      <c r="AC21" s="49" t="n"/>
-      <c r="AD21" s="49" t="n"/>
-      <c r="AE21" s="49" t="n"/>
-      <c r="AF21" s="49" t="n"/>
-      <c r="AG21" s="29" t="n"/>
-      <c r="AH21" s="29" t="n"/>
-      <c r="AI21" s="29" t="n"/>
-      <c r="AJ21" s="29" t="n"/>
-      <c r="AK21" s="29" t="n"/>
-      <c r="AL21" s="29" t="n"/>
-      <c r="AM21" s="29" t="n"/>
-      <c r="AN21" s="29" t="n"/>
-      <c r="AO21" s="30" t="n"/>
+      <c r="A21" s="34" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="40" t="n"/>
+      <c r="J21" s="40" t="n"/>
+      <c r="K21" s="40" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="V21" s="34" t="n"/>
+      <c r="W21" s="35" t="n"/>
+      <c r="X21" s="39" t="n"/>
+      <c r="Y21" s="40" t="n"/>
+      <c r="Z21" s="40" t="n"/>
+      <c r="AA21" s="40" t="n"/>
+      <c r="AB21" s="40" t="n"/>
+      <c r="AC21" s="40" t="n"/>
+      <c r="AD21" s="40" t="n"/>
+      <c r="AE21" s="40" t="n"/>
+      <c r="AF21" s="40" t="n"/>
+      <c r="AG21" s="22" t="n"/>
+      <c r="AH21" s="22" t="n"/>
+      <c r="AI21" s="22" t="n"/>
+      <c r="AJ21" s="22" t="n"/>
+      <c r="AK21" s="22" t="n"/>
+      <c r="AL21" s="22" t="n"/>
+      <c r="AM21" s="22" t="n"/>
+      <c r="AN21" s="22" t="n"/>
+      <c r="AO21" s="23" t="n"/>
     </row>
     <row r="22" hidden="1" ht="12.75" customHeight="1">
-      <c r="A22" s="43" t="n"/>
-      <c r="B22" s="44" t="n"/>
-      <c r="C22" s="48" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
-      <c r="G22" s="49" t="n"/>
-      <c r="H22" s="49" t="n"/>
-      <c r="I22" s="49" t="n"/>
-      <c r="J22" s="49" t="n"/>
-      <c r="K22" s="49" t="n"/>
-      <c r="L22" s="29" t="n"/>
-      <c r="M22" s="29" t="n"/>
-      <c r="N22" s="29" t="n"/>
-      <c r="O22" s="29" t="n"/>
-      <c r="P22" s="29" t="n"/>
-      <c r="Q22" s="29" t="n"/>
-      <c r="R22" s="29" t="n"/>
-      <c r="S22" s="29" t="n"/>
-      <c r="T22" s="30" t="n"/>
-      <c r="V22" s="43" t="n"/>
-      <c r="W22" s="44" t="n"/>
-      <c r="X22" s="48" t="n"/>
-      <c r="Y22" s="49" t="n"/>
-      <c r="Z22" s="49" t="n"/>
-      <c r="AA22" s="49" t="n"/>
-      <c r="AB22" s="49" t="n"/>
-      <c r="AC22" s="49" t="n"/>
-      <c r="AD22" s="49" t="n"/>
-      <c r="AE22" s="49" t="n"/>
-      <c r="AF22" s="49" t="n"/>
-      <c r="AG22" s="29" t="n"/>
-      <c r="AH22" s="29" t="n"/>
-      <c r="AI22" s="29" t="n"/>
-      <c r="AJ22" s="29" t="n"/>
-      <c r="AK22" s="29" t="n"/>
-      <c r="AL22" s="29" t="n"/>
-      <c r="AM22" s="29" t="n"/>
-      <c r="AN22" s="29" t="n"/>
-      <c r="AO22" s="30" t="n"/>
+      <c r="A22" s="34" t="n"/>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="40" t="n"/>
+      <c r="E22" s="40" t="n"/>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="40" t="n"/>
+      <c r="J22" s="40" t="n"/>
+      <c r="K22" s="40" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="22" t="n"/>
+      <c r="R22" s="22" t="n"/>
+      <c r="S22" s="22" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="V22" s="34" t="n"/>
+      <c r="W22" s="35" t="n"/>
+      <c r="X22" s="39" t="n"/>
+      <c r="Y22" s="40" t="n"/>
+      <c r="Z22" s="40" t="n"/>
+      <c r="AA22" s="40" t="n"/>
+      <c r="AB22" s="40" t="n"/>
+      <c r="AC22" s="40" t="n"/>
+      <c r="AD22" s="40" t="n"/>
+      <c r="AE22" s="40" t="n"/>
+      <c r="AF22" s="40" t="n"/>
+      <c r="AG22" s="22" t="n"/>
+      <c r="AH22" s="22" t="n"/>
+      <c r="AI22" s="22" t="n"/>
+      <c r="AJ22" s="22" t="n"/>
+      <c r="AK22" s="22" t="n"/>
+      <c r="AL22" s="22" t="n"/>
+      <c r="AM22" s="22" t="n"/>
+      <c r="AN22" s="22" t="n"/>
+      <c r="AO22" s="23" t="n"/>
     </row>
     <row r="23" hidden="1" ht="12.75" customHeight="1">
-      <c r="A23" s="43" t="n"/>
-      <c r="B23" s="44" t="n"/>
-      <c r="C23" s="48" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
-      <c r="G23" s="49" t="n"/>
-      <c r="H23" s="49" t="n"/>
-      <c r="I23" s="49" t="n"/>
-      <c r="J23" s="49" t="n"/>
-      <c r="K23" s="49" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="29" t="n"/>
-      <c r="N23" s="29" t="n"/>
-      <c r="O23" s="29" t="n"/>
-      <c r="P23" s="29" t="n"/>
-      <c r="Q23" s="29" t="n"/>
-      <c r="R23" s="29" t="n"/>
-      <c r="S23" s="29" t="n"/>
-      <c r="T23" s="30" t="n"/>
-      <c r="V23" s="43" t="n"/>
-      <c r="W23" s="44" t="n"/>
-      <c r="X23" s="48" t="n"/>
-      <c r="Y23" s="49" t="n"/>
-      <c r="Z23" s="49" t="n"/>
-      <c r="AA23" s="49" t="n"/>
-      <c r="AB23" s="49" t="n"/>
-      <c r="AC23" s="49" t="n"/>
-      <c r="AD23" s="49" t="n"/>
-      <c r="AE23" s="49" t="n"/>
-      <c r="AF23" s="49" t="n"/>
-      <c r="AG23" s="29" t="n"/>
-      <c r="AH23" s="29" t="n"/>
-      <c r="AI23" s="29" t="n"/>
-      <c r="AJ23" s="29" t="n"/>
-      <c r="AK23" s="29" t="n"/>
-      <c r="AL23" s="29" t="n"/>
-      <c r="AM23" s="29" t="n"/>
-      <c r="AN23" s="29" t="n"/>
-      <c r="AO23" s="30" t="n"/>
+      <c r="A23" s="34" t="n"/>
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="40" t="n"/>
+      <c r="J23" s="40" t="n"/>
+      <c r="K23" s="40" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="23" t="n"/>
+      <c r="V23" s="34" t="n"/>
+      <c r="W23" s="35" t="n"/>
+      <c r="X23" s="39" t="n"/>
+      <c r="Y23" s="40" t="n"/>
+      <c r="Z23" s="40" t="n"/>
+      <c r="AA23" s="40" t="n"/>
+      <c r="AB23" s="40" t="n"/>
+      <c r="AC23" s="40" t="n"/>
+      <c r="AD23" s="40" t="n"/>
+      <c r="AE23" s="40" t="n"/>
+      <c r="AF23" s="40" t="n"/>
+      <c r="AG23" s="22" t="n"/>
+      <c r="AH23" s="22" t="n"/>
+      <c r="AI23" s="22" t="n"/>
+      <c r="AJ23" s="22" t="n"/>
+      <c r="AK23" s="22" t="n"/>
+      <c r="AL23" s="22" t="n"/>
+      <c r="AM23" s="22" t="n"/>
+      <c r="AN23" s="22" t="n"/>
+      <c r="AO23" s="23" t="n"/>
     </row>
     <row r="24" hidden="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A24" s="69" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>TOTAL AT BKK</t>
         </is>
       </c>
-      <c r="B24" s="139" t="n"/>
-      <c r="C24" s="70" t="n"/>
-      <c r="D24" s="71" t="n"/>
-      <c r="E24" s="71" t="n"/>
-      <c r="F24" s="71" t="n"/>
-      <c r="G24" s="71" t="n"/>
-      <c r="H24" s="71" t="n"/>
-      <c r="I24" s="71" t="n"/>
-      <c r="J24" s="71" t="n"/>
-      <c r="K24" s="71" t="n"/>
-      <c r="L24" s="58" t="n"/>
-      <c r="M24" s="58" t="n"/>
-      <c r="N24" s="58" t="n"/>
-      <c r="O24" s="58" t="n"/>
-      <c r="P24" s="58" t="n"/>
-      <c r="Q24" s="58" t="n"/>
-      <c r="R24" s="58" t="n"/>
-      <c r="S24" s="58" t="n"/>
-      <c r="T24" s="59" t="n"/>
-      <c r="V24" s="69" t="inlineStr">
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="62" t="n"/>
+      <c r="E24" s="62" t="n"/>
+      <c r="F24" s="62" t="n"/>
+      <c r="G24" s="62" t="n"/>
+      <c r="H24" s="62" t="n"/>
+      <c r="I24" s="62" t="n"/>
+      <c r="J24" s="62" t="n"/>
+      <c r="K24" s="62" t="n"/>
+      <c r="L24" s="49" t="n"/>
+      <c r="M24" s="49" t="n"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="49" t="n"/>
+      <c r="P24" s="49" t="n"/>
+      <c r="Q24" s="49" t="n"/>
+      <c r="R24" s="49" t="n"/>
+      <c r="S24" s="49" t="n"/>
+      <c r="T24" s="50" t="n"/>
+      <c r="V24" s="60" t="inlineStr">
         <is>
           <t>TOTAL AT BKK</t>
         </is>
       </c>
-      <c r="W24" s="139" t="n"/>
-      <c r="X24" s="70" t="n"/>
-      <c r="Y24" s="71" t="n"/>
-      <c r="Z24" s="71" t="n"/>
-      <c r="AA24" s="71" t="n"/>
-      <c r="AB24" s="71" t="n"/>
-      <c r="AC24" s="71" t="n"/>
-      <c r="AD24" s="71" t="n"/>
-      <c r="AE24" s="71" t="n"/>
-      <c r="AF24" s="71" t="n"/>
-      <c r="AG24" s="58" t="n"/>
-      <c r="AH24" s="58" t="n"/>
-      <c r="AI24" s="58" t="n"/>
-      <c r="AJ24" s="58" t="n"/>
-      <c r="AK24" s="58" t="n"/>
-      <c r="AL24" s="58" t="n"/>
-      <c r="AM24" s="58" t="n"/>
-      <c r="AN24" s="58" t="n"/>
-      <c r="AO24" s="59" t="n"/>
+      <c r="W24" s="44" t="n"/>
+      <c r="X24" s="61" t="n"/>
+      <c r="Y24" s="62" t="n"/>
+      <c r="Z24" s="62" t="n"/>
+      <c r="AA24" s="62" t="n"/>
+      <c r="AB24" s="62" t="n"/>
+      <c r="AC24" s="62" t="n"/>
+      <c r="AD24" s="62" t="n"/>
+      <c r="AE24" s="62" t="n"/>
+      <c r="AF24" s="62" t="n"/>
+      <c r="AG24" s="49" t="n"/>
+      <c r="AH24" s="49" t="n"/>
+      <c r="AI24" s="49" t="n"/>
+      <c r="AJ24" s="49" t="n"/>
+      <c r="AK24" s="49" t="n"/>
+      <c r="AL24" s="49" t="n"/>
+      <c r="AM24" s="49" t="n"/>
+      <c r="AN24" s="49" t="n"/>
+      <c r="AO24" s="50" t="n"/>
     </row>
     <row r="25" hidden="1" ht="12.75" customHeight="1">
-      <c r="A25" s="60" t="n"/>
-      <c r="B25" s="61" t="n"/>
-      <c r="V25" s="60" t="n"/>
-      <c r="W25" s="61" t="n"/>
-      <c r="AO25" s="61" t="n"/>
+      <c r="A25" s="51" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="V25" s="51" t="n"/>
+      <c r="W25" s="52" t="n"/>
+      <c r="AO25" s="52" t="n"/>
     </row>
     <row r="26" hidden="1" ht="12.75" customHeight="1">
-      <c r="A26" s="60" t="n"/>
-      <c r="B26" s="61" t="n"/>
-      <c r="V26" s="60" t="n"/>
-      <c r="W26" s="61" t="n"/>
-      <c r="AO26" s="61" t="n"/>
+      <c r="A26" s="51" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="V26" s="51" t="n"/>
+      <c r="W26" s="52" t="n"/>
+      <c r="AO26" s="52" t="n"/>
     </row>
     <row r="27" hidden="1" ht="12.75" customHeight="1">
-      <c r="A27" s="60" t="n"/>
-      <c r="B27" s="61" t="n"/>
-      <c r="V27" s="60" t="n"/>
-      <c r="W27" s="61" t="n"/>
-      <c r="AO27" s="61" t="n"/>
+      <c r="A27" s="51" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="V27" s="51" t="n"/>
+      <c r="W27" s="52" t="n"/>
+      <c r="AO27" s="52" t="n"/>
     </row>
     <row r="28" ht="9.949999999999999" customHeight="1" thickBot="1">
-      <c r="A28" s="60" t="n"/>
-      <c r="AO28" s="61" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="185" t="inlineStr">
+      <c r="A28" s="51" t="n"/>
+      <c r="AO28" s="52" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" thickBot="1">
+      <c r="A29" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="B29" s="186" t="n"/>
-      <c r="C29" s="151" t="inlineStr">
+      <c r="B29" s="178" t="n"/>
+      <c r="C29" s="174" t="inlineStr">
         <is>
           <t>BOOKING (BKK)</t>
         </is>
       </c>
-      <c r="D29" s="187" t="n"/>
-      <c r="E29" s="187" t="n"/>
-      <c r="F29" s="187" t="n"/>
-      <c r="G29" s="187" t="n"/>
-      <c r="H29" s="188" t="n"/>
-      <c r="I29" s="215" t="inlineStr">
+      <c r="D29" s="167" t="n"/>
+      <c r="E29" s="167" t="n"/>
+      <c r="F29" s="167" t="n"/>
+      <c r="G29" s="167" t="n"/>
+      <c r="H29" s="175" t="n"/>
+      <c r="I29" s="166" t="inlineStr">
         <is>
           <t>14-20/09/2026</t>
         </is>
       </c>
-      <c r="J29" s="187" t="n"/>
-      <c r="K29" s="190" t="n"/>
-      <c r="L29" s="143" t="inlineStr">
+      <c r="J29" s="167" t="n"/>
+      <c r="K29" s="168" t="n"/>
+      <c r="L29" s="176" t="inlineStr">
         <is>
           <t>STOCK END WK (BKK)</t>
         </is>
       </c>
-      <c r="M29" s="187" t="n"/>
-      <c r="N29" s="187" t="n"/>
-      <c r="O29" s="187" t="n"/>
-      <c r="P29" s="187" t="n"/>
-      <c r="Q29" s="187" t="n"/>
-      <c r="R29" s="187" t="n"/>
-      <c r="S29" s="187" t="n"/>
-      <c r="T29" s="188" t="n"/>
+      <c r="M29" s="167" t="n"/>
+      <c r="N29" s="167" t="n"/>
+      <c r="O29" s="167" t="n"/>
+      <c r="P29" s="167" t="n"/>
+      <c r="Q29" s="167" t="n"/>
+      <c r="R29" s="167" t="n"/>
+      <c r="S29" s="167" t="n"/>
+      <c r="T29" s="175" t="n"/>
       <c r="U29" s="2" t="n"/>
-      <c r="V29" s="185" t="inlineStr">
+      <c r="V29" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="W29" s="186" t="n"/>
-      <c r="X29" s="151" t="inlineStr">
+      <c r="W29" s="178" t="n"/>
+      <c r="X29" s="174" t="inlineStr">
         <is>
           <t>BOOKING (LCH)</t>
         </is>
       </c>
-      <c r="Y29" s="187" t="n"/>
-      <c r="Z29" s="187" t="n"/>
-      <c r="AA29" s="187" t="n"/>
-      <c r="AB29" s="187" t="n"/>
-      <c r="AC29" s="188" t="n"/>
-      <c r="AD29" s="215" t="inlineStr">
+      <c r="Y29" s="167" t="n"/>
+      <c r="Z29" s="167" t="n"/>
+      <c r="AA29" s="167" t="n"/>
+      <c r="AB29" s="167" t="n"/>
+      <c r="AC29" s="175" t="n"/>
+      <c r="AD29" s="166" t="inlineStr">
         <is>
           <t>14-20/09/2026</t>
         </is>
       </c>
-      <c r="AE29" s="187" t="n"/>
-      <c r="AF29" s="190" t="n"/>
-      <c r="AG29" s="143" t="inlineStr">
+      <c r="AE29" s="167" t="n"/>
+      <c r="AF29" s="168" t="n"/>
+      <c r="AG29" s="176" t="inlineStr">
         <is>
           <t>STOCK END WK (LCH)</t>
         </is>
       </c>
-      <c r="AH29" s="187" t="n"/>
-      <c r="AI29" s="187" t="n"/>
-      <c r="AJ29" s="187" t="n"/>
-      <c r="AK29" s="187" t="n"/>
-      <c r="AL29" s="187" t="n"/>
-      <c r="AM29" s="187" t="n"/>
-      <c r="AN29" s="187" t="n"/>
-      <c r="AO29" s="188" t="n"/>
+      <c r="AH29" s="167" t="n"/>
+      <c r="AI29" s="167" t="n"/>
+      <c r="AJ29" s="167" t="n"/>
+      <c r="AK29" s="167" t="n"/>
+      <c r="AL29" s="167" t="n"/>
+      <c r="AM29" s="167" t="n"/>
+      <c r="AN29" s="167" t="n"/>
+      <c r="AO29" s="175" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="191" t="n"/>
-      <c r="B30" s="192" t="n"/>
+      <c r="A30" s="179" t="n"/>
+      <c r="B30" s="180" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -4150,8 +4039,8 @@
         </is>
       </c>
       <c r="U30" s="9" t="n"/>
-      <c r="V30" s="191" t="n"/>
-      <c r="W30" s="192" t="n"/>
+      <c r="V30" s="179" t="n"/>
+      <c r="W30" s="180" t="n"/>
       <c r="X30" s="4" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -4244,62 +4133,62 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="72" t="inlineStr">
+      <c r="A31" s="63" t="inlineStr">
         <is>
           <t>PAT</t>
         </is>
       </c>
-      <c r="B31" s="73" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C31" s="193" t="n">
+      <c r="C31" s="113" t="n">
         <v>24</v>
       </c>
-      <c r="D31" s="194" t="n"/>
-      <c r="E31" s="194" t="n">
+      <c r="D31" s="114" t="n"/>
+      <c r="E31" s="114" t="n">
         <v>42</v>
       </c>
-      <c r="F31" s="194" t="n"/>
-      <c r="G31" s="194" t="n"/>
-      <c r="H31" s="194" t="n"/>
-      <c r="I31" s="194" t="n"/>
-      <c r="J31" s="194" t="n"/>
-      <c r="K31" s="195" t="n"/>
-      <c r="L31" s="216">
+      <c r="F31" s="114" t="n"/>
+      <c r="G31" s="114" t="n"/>
+      <c r="H31" s="114" t="n"/>
+      <c r="I31" s="114" t="n"/>
+      <c r="J31" s="114" t="n"/>
+      <c r="K31" s="115" t="n"/>
+      <c r="L31" s="204">
         <f>SUM(L4-C31)</f>
         <v/>
       </c>
-      <c r="M31" s="217">
+      <c r="M31" s="205">
         <f>SUM(M4-D31)</f>
         <v/>
       </c>
-      <c r="N31" s="218">
+      <c r="N31" s="206">
         <f>SUM(N4-E31)</f>
         <v/>
       </c>
-      <c r="O31" s="217">
+      <c r="O31" s="205">
         <f>SUM(O4-F31)</f>
         <v/>
       </c>
-      <c r="P31" s="217">
+      <c r="P31" s="205">
         <f>SUM(P4-G31)</f>
         <v/>
       </c>
-      <c r="Q31" s="217">
+      <c r="Q31" s="205">
         <f>SUM(Q4-H31)</f>
         <v/>
       </c>
-      <c r="R31" s="217">
+      <c r="R31" s="205">
         <f>SUM(R4-I31)</f>
         <v/>
       </c>
-      <c r="S31" s="217">
+      <c r="S31" s="205">
         <f>SUM(S4-J31)</f>
         <v/>
       </c>
-      <c r="T31" s="219">
+      <c r="T31" s="207">
         <f>SUM(T4-K31)</f>
         <v/>
       </c>
@@ -4313,1288 +4202,1294 @@
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X31" s="220" t="n"/>
-      <c r="Y31" s="221" t="n"/>
-      <c r="Z31" s="221" t="n"/>
-      <c r="AA31" s="221" t="n"/>
-      <c r="AB31" s="221" t="n"/>
-      <c r="AC31" s="221" t="n"/>
-      <c r="AD31" s="221" t="n"/>
-      <c r="AE31" s="221" t="n"/>
-      <c r="AF31" s="222" t="n"/>
-      <c r="AG31" s="223">
+      <c r="X31" s="136" t="n"/>
+      <c r="Y31" s="137" t="n"/>
+      <c r="Z31" s="137" t="n"/>
+      <c r="AA31" s="137" t="n"/>
+      <c r="AB31" s="137" t="n"/>
+      <c r="AC31" s="137" t="n"/>
+      <c r="AD31" s="137" t="n"/>
+      <c r="AE31" s="137" t="n"/>
+      <c r="AF31" s="138" t="n"/>
+      <c r="AG31" s="208">
         <f>SUM(AG4-X31)</f>
         <v/>
       </c>
-      <c r="AH31" s="217">
+      <c r="AH31" s="205">
         <f>SUM(AH4-Y31)</f>
         <v/>
       </c>
-      <c r="AI31" s="217">
+      <c r="AI31" s="205">
         <f>SUM(AI4-Z31)</f>
         <v/>
       </c>
-      <c r="AJ31" s="217">
+      <c r="AJ31" s="205">
         <f>SUM(AJ4-AA31)</f>
         <v/>
       </c>
-      <c r="AK31" s="217">
+      <c r="AK31" s="205">
         <f>SUM(AK4-AB31)</f>
         <v/>
       </c>
-      <c r="AL31" s="217">
+      <c r="AL31" s="205">
         <f>SUM(AL4-AC31)</f>
         <v/>
       </c>
-      <c r="AM31" s="217">
+      <c r="AM31" s="205">
         <f>SUM(AM4-AD31)</f>
         <v/>
       </c>
-      <c r="AN31" s="217">
+      <c r="AN31" s="205">
         <f>SUM(AN4-AE31)</f>
         <v/>
       </c>
-      <c r="AO31" s="219">
+      <c r="AO31" s="207">
         <f>SUM(AO4-AF31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>UNITHAI</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C32" s="201" t="n">
+      <c r="C32" s="121" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="202" t="n"/>
-      <c r="E32" s="202" t="n">
+      <c r="D32" s="122" t="n"/>
+      <c r="E32" s="122" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="202" t="n"/>
-      <c r="G32" s="202" t="n"/>
-      <c r="H32" s="202" t="n"/>
-      <c r="I32" s="202" t="n"/>
-      <c r="J32" s="202" t="n"/>
-      <c r="K32" s="203" t="n"/>
-      <c r="L32" s="224">
+      <c r="F32" s="122" t="n"/>
+      <c r="G32" s="122" t="n"/>
+      <c r="H32" s="122" t="n"/>
+      <c r="I32" s="122" t="n"/>
+      <c r="J32" s="122" t="n"/>
+      <c r="K32" s="123" t="n"/>
+      <c r="L32" s="209">
         <f>SUM(L5-C32)</f>
         <v/>
       </c>
-      <c r="M32" s="225">
+      <c r="M32" s="210">
         <f>SUM(M5-D32)</f>
         <v/>
       </c>
-      <c r="N32" s="225">
+      <c r="N32" s="210">
         <f>SUM(N5-E32)</f>
         <v/>
       </c>
-      <c r="O32" s="225">
+      <c r="O32" s="210">
         <f>SUM(O5-F32)</f>
         <v/>
       </c>
-      <c r="P32" s="225">
+      <c r="P32" s="210">
         <f>SUM(P5-G32)</f>
         <v/>
       </c>
-      <c r="Q32" s="225">
+      <c r="Q32" s="210">
         <f>SUM(Q5-H32)</f>
         <v/>
       </c>
-      <c r="R32" s="225">
+      <c r="R32" s="210">
         <f>SUM(R5-I32)</f>
         <v/>
       </c>
-      <c r="S32" s="225">
+      <c r="S32" s="210">
         <f>SUM(S5-J32)</f>
         <v/>
       </c>
-      <c r="T32" s="226">
+      <c r="T32" s="211">
         <f>SUM(T5-K32)</f>
         <v/>
       </c>
-      <c r="V32" s="23" t="inlineStr">
+      <c r="V32" s="16" t="inlineStr">
         <is>
           <t>ESCO</t>
         </is>
       </c>
-      <c r="W32" s="24" t="inlineStr">
+      <c r="W32" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X32" s="227" t="n"/>
-      <c r="Y32" s="228" t="n"/>
-      <c r="Z32" s="228" t="n"/>
-      <c r="AA32" s="228" t="n"/>
-      <c r="AB32" s="228" t="n"/>
-      <c r="AC32" s="228" t="n"/>
-      <c r="AD32" s="228" t="n"/>
-      <c r="AE32" s="228" t="n"/>
-      <c r="AF32" s="229" t="n"/>
-      <c r="AG32" s="224">
+      <c r="X32" s="143" t="n"/>
+      <c r="Y32" s="144" t="n"/>
+      <c r="Z32" s="144" t="n"/>
+      <c r="AA32" s="144" t="n"/>
+      <c r="AB32" s="144" t="n"/>
+      <c r="AC32" s="144" t="n"/>
+      <c r="AD32" s="144" t="n"/>
+      <c r="AE32" s="144" t="n"/>
+      <c r="AF32" s="145" t="n"/>
+      <c r="AG32" s="209">
         <f>SUM(AG5-X32)</f>
         <v/>
       </c>
-      <c r="AH32" s="225">
+      <c r="AH32" s="210">
         <f>SUM(AH5-Y32)</f>
         <v/>
       </c>
-      <c r="AI32" s="225">
+      <c r="AI32" s="210">
         <f>SUM(AI5-Z32)</f>
         <v/>
       </c>
-      <c r="AJ32" s="225">
+      <c r="AJ32" s="210">
         <f>SUM(AJ5-AA32)</f>
         <v/>
       </c>
-      <c r="AK32" s="225">
+      <c r="AK32" s="210">
         <f>SUM(AK5-AB32)</f>
         <v/>
       </c>
-      <c r="AL32" s="225">
+      <c r="AL32" s="210">
         <f>SUM(AL5-AC32)</f>
         <v/>
       </c>
-      <c r="AM32" s="225">
+      <c r="AM32" s="210">
         <f>SUM(AM5-AD32)</f>
         <v/>
       </c>
-      <c r="AN32" s="225">
+      <c r="AN32" s="210">
         <f>SUM(AN5-AE32)</f>
         <v/>
       </c>
-      <c r="AO32" s="226">
+      <c r="AO32" s="211">
         <f>SUM(AO5-AF32)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>ESCO #2</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C33" s="201" t="n">
+      <c r="C33" s="121" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="202" t="n"/>
-      <c r="E33" s="202" t="n"/>
-      <c r="F33" s="202" t="n"/>
-      <c r="G33" s="202" t="n"/>
-      <c r="H33" s="202" t="n"/>
-      <c r="I33" s="202" t="n"/>
-      <c r="J33" s="202" t="n"/>
-      <c r="K33" s="203" t="n"/>
-      <c r="L33" s="224">
+      <c r="D33" s="122" t="n"/>
+      <c r="E33" s="122" t="n"/>
+      <c r="F33" s="122" t="n"/>
+      <c r="G33" s="122" t="n"/>
+      <c r="H33" s="122" t="n"/>
+      <c r="I33" s="122" t="n"/>
+      <c r="J33" s="122" t="n"/>
+      <c r="K33" s="123" t="n"/>
+      <c r="L33" s="209">
         <f>SUM(L6-C33)</f>
         <v/>
       </c>
-      <c r="M33" s="225">
+      <c r="M33" s="210">
         <f>SUM(M6-D33)</f>
         <v/>
       </c>
-      <c r="N33" s="225">
+      <c r="N33" s="210">
         <f>SUM(N6-E33)</f>
         <v/>
       </c>
-      <c r="O33" s="225">
+      <c r="O33" s="210">
         <f>SUM(O6-F33)</f>
         <v/>
       </c>
-      <c r="P33" s="225">
+      <c r="P33" s="210">
         <f>SUM(P6-G33)</f>
         <v/>
       </c>
-      <c r="Q33" s="225">
+      <c r="Q33" s="210">
         <f>SUM(Q6-H33)</f>
         <v/>
       </c>
-      <c r="R33" s="225">
+      <c r="R33" s="210">
         <f>SUM(R6-I33)</f>
         <v/>
       </c>
-      <c r="S33" s="225">
+      <c r="S33" s="210">
         <f>SUM(S6-J33)</f>
         <v/>
       </c>
-      <c r="T33" s="226">
+      <c r="T33" s="211">
         <f>SUM(T6-K33)</f>
         <v/>
       </c>
-      <c r="V33" s="23" t="inlineStr">
+      <c r="V33" s="16" t="inlineStr">
         <is>
           <t>LCIT</t>
         </is>
       </c>
-      <c r="W33" s="24" t="inlineStr">
+      <c r="W33" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X33" s="227" t="n"/>
-      <c r="Y33" s="228" t="n"/>
-      <c r="Z33" s="228" t="n"/>
-      <c r="AA33" s="228" t="n"/>
-      <c r="AB33" s="228" t="n"/>
-      <c r="AC33" s="228" t="n"/>
-      <c r="AD33" s="228" t="n"/>
-      <c r="AE33" s="228" t="n"/>
-      <c r="AF33" s="229" t="n"/>
-      <c r="AG33" s="224">
+      <c r="X33" s="143" t="n"/>
+      <c r="Y33" s="144" t="n"/>
+      <c r="Z33" s="144" t="n"/>
+      <c r="AA33" s="144" t="n"/>
+      <c r="AB33" s="144" t="n"/>
+      <c r="AC33" s="144" t="n"/>
+      <c r="AD33" s="144" t="n"/>
+      <c r="AE33" s="144" t="n"/>
+      <c r="AF33" s="145" t="n"/>
+      <c r="AG33" s="209">
         <f>SUM(AG6-X33)</f>
         <v/>
       </c>
-      <c r="AH33" s="225">
+      <c r="AH33" s="210">
         <f>SUM(AH6-Y33)</f>
         <v/>
       </c>
-      <c r="AI33" s="225">
+      <c r="AI33" s="210">
         <f>SUM(AI6-Z33)</f>
         <v/>
       </c>
-      <c r="AJ33" s="225">
+      <c r="AJ33" s="210">
         <f>SUM(AJ6-AA33)</f>
         <v/>
       </c>
-      <c r="AK33" s="225">
+      <c r="AK33" s="210">
         <f>SUM(AK6-AB33)</f>
         <v/>
       </c>
-      <c r="AL33" s="225">
+      <c r="AL33" s="210">
         <f>SUM(AL6-AC33)</f>
         <v/>
       </c>
-      <c r="AM33" s="225">
+      <c r="AM33" s="210">
         <f>SUM(AM6-AD33)</f>
         <v/>
       </c>
-      <c r="AN33" s="225">
+      <c r="AN33" s="210">
         <f>SUM(AN6-AE33)</f>
         <v/>
       </c>
-      <c r="AO33" s="226">
+      <c r="AO33" s="211">
         <f>SUM(AO6-AF33)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="136" t="inlineStr">
+      <c r="A34" s="111" t="inlineStr">
         <is>
           <t>BMTP</t>
         </is>
       </c>
-      <c r="B34" s="137" t="inlineStr">
+      <c r="B34" s="112" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C34" s="227" t="n"/>
-      <c r="D34" s="228" t="n"/>
-      <c r="E34" s="228" t="n"/>
-      <c r="F34" s="228" t="n"/>
-      <c r="G34" s="228" t="n"/>
-      <c r="H34" s="228" t="n"/>
-      <c r="I34" s="228" t="n"/>
-      <c r="J34" s="228" t="n"/>
-      <c r="K34" s="229" t="n"/>
-      <c r="L34" s="224">
+      <c r="C34" s="143" t="n"/>
+      <c r="D34" s="144" t="n"/>
+      <c r="E34" s="144" t="n"/>
+      <c r="F34" s="144" t="n"/>
+      <c r="G34" s="144" t="n"/>
+      <c r="H34" s="144" t="n"/>
+      <c r="I34" s="144" t="n"/>
+      <c r="J34" s="144" t="n"/>
+      <c r="K34" s="145" t="n"/>
+      <c r="L34" s="209">
         <f>SUM(L7-C34)</f>
         <v/>
       </c>
-      <c r="M34" s="225">
+      <c r="M34" s="210">
         <f>SUM(M7-D34)</f>
         <v/>
       </c>
-      <c r="N34" s="225">
+      <c r="N34" s="210">
         <f>SUM(N7-E34)</f>
         <v/>
       </c>
-      <c r="O34" s="225">
+      <c r="O34" s="210">
         <f>SUM(O7-F34)</f>
         <v/>
       </c>
-      <c r="P34" s="225">
+      <c r="P34" s="210">
         <f>SUM(P7-G34)</f>
         <v/>
       </c>
-      <c r="Q34" s="225">
+      <c r="Q34" s="210">
         <f>SUM(Q7-H34)</f>
         <v/>
       </c>
-      <c r="R34" s="225">
+      <c r="R34" s="210">
         <f>SUM(R7-I34)</f>
         <v/>
       </c>
-      <c r="S34" s="225">
+      <c r="S34" s="210">
         <f>SUM(S7-J34)</f>
         <v/>
       </c>
-      <c r="T34" s="226">
+      <c r="T34" s="211">
         <f>SUM(T7-K34)</f>
         <v/>
       </c>
-      <c r="V34" s="23" t="inlineStr">
+      <c r="V34" s="16" t="inlineStr">
         <is>
           <t>HPT</t>
         </is>
       </c>
-      <c r="W34" s="24" t="inlineStr">
+      <c r="W34" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X34" s="227" t="n"/>
-      <c r="Y34" s="228" t="n"/>
-      <c r="Z34" s="228" t="n"/>
-      <c r="AA34" s="228" t="n"/>
-      <c r="AB34" s="228" t="n"/>
-      <c r="AC34" s="228" t="n"/>
-      <c r="AD34" s="228" t="n"/>
-      <c r="AE34" s="228" t="n"/>
-      <c r="AF34" s="229" t="n"/>
-      <c r="AG34" s="224">
+      <c r="X34" s="143" t="n"/>
+      <c r="Y34" s="144" t="n"/>
+      <c r="Z34" s="144" t="n"/>
+      <c r="AA34" s="144" t="n"/>
+      <c r="AB34" s="144" t="n"/>
+      <c r="AC34" s="144" t="n"/>
+      <c r="AD34" s="144" t="n"/>
+      <c r="AE34" s="144" t="n"/>
+      <c r="AF34" s="145" t="n"/>
+      <c r="AG34" s="209">
         <f>SUM(AG7-X34)</f>
         <v/>
       </c>
-      <c r="AH34" s="225">
+      <c r="AH34" s="210">
         <f>SUM(AH7-Y34)</f>
         <v/>
       </c>
-      <c r="AI34" s="225">
+      <c r="AI34" s="210">
         <f>SUM(AI7-Z34)</f>
         <v/>
       </c>
-      <c r="AJ34" s="225">
+      <c r="AJ34" s="210">
         <f>SUM(AJ7-AA34)</f>
         <v/>
       </c>
-      <c r="AK34" s="225">
+      <c r="AK34" s="210">
         <f>SUM(AK7-AB34)</f>
         <v/>
       </c>
-      <c r="AL34" s="225">
+      <c r="AL34" s="210">
         <f>SUM(AL7-AC34)</f>
         <v/>
       </c>
-      <c r="AM34" s="225">
+      <c r="AM34" s="210">
         <f>SUM(AM7-AD34)</f>
         <v/>
       </c>
-      <c r="AN34" s="225">
+      <c r="AN34" s="210">
         <f>SUM(AN7-AE34)</f>
         <v/>
       </c>
-      <c r="AO34" s="226">
+      <c r="AO34" s="211">
         <f>SUM(AO7-AF34)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C35" s="230" t="n">
+      <c r="C35" s="146" t="n">
         <v>221</v>
       </c>
-      <c r="D35" s="210" t="n"/>
-      <c r="E35" s="210" t="n">
+      <c r="D35" s="130" t="n"/>
+      <c r="E35" s="130" t="n">
         <v>87</v>
       </c>
-      <c r="F35" s="210" t="n"/>
-      <c r="G35" s="210" t="n"/>
-      <c r="H35" s="210" t="n"/>
-      <c r="I35" s="210" t="n"/>
-      <c r="J35" s="210" t="n"/>
-      <c r="K35" s="231" t="n"/>
-      <c r="L35" s="232">
+      <c r="F35" s="130" t="n"/>
+      <c r="G35" s="130" t="n"/>
+      <c r="H35" s="130" t="n"/>
+      <c r="I35" s="130" t="n"/>
+      <c r="J35" s="130" t="n"/>
+      <c r="K35" s="147" t="n"/>
+      <c r="L35" s="212">
         <f>SUM(L8-C35)</f>
         <v/>
       </c>
-      <c r="M35" s="233">
+      <c r="M35" s="213">
         <f>SUM(M8-D35)</f>
         <v/>
       </c>
-      <c r="N35" s="233">
+      <c r="N35" s="213">
         <f>SUM(N8-E35)</f>
         <v/>
       </c>
-      <c r="O35" s="233">
+      <c r="O35" s="213">
         <f>SUM(O8-F35)</f>
         <v/>
       </c>
-      <c r="P35" s="233">
+      <c r="P35" s="213">
         <f>SUM(P8-G35)</f>
         <v/>
       </c>
-      <c r="Q35" s="233">
+      <c r="Q35" s="213">
         <f>SUM(Q8-H35)</f>
         <v/>
       </c>
-      <c r="R35" s="233">
+      <c r="R35" s="213">
         <f>SUM(R8-I35)</f>
         <v/>
       </c>
-      <c r="S35" s="233">
+      <c r="S35" s="213">
         <f>SUM(S8-J35)</f>
         <v/>
       </c>
-      <c r="T35" s="234">
+      <c r="T35" s="214">
         <f>SUM(T8-K35)</f>
         <v/>
       </c>
-      <c r="V35" s="35" t="inlineStr">
+      <c r="V35" s="26" t="inlineStr">
         <is>
           <t>HAST</t>
         </is>
       </c>
-      <c r="W35" s="36" t="inlineStr">
+      <c r="W35" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X35" s="230" t="n">
+      <c r="X35" s="146" t="n">
         <v>75</v>
       </c>
-      <c r="Y35" s="210" t="n"/>
-      <c r="Z35" s="210" t="n">
+      <c r="Y35" s="130" t="n"/>
+      <c r="Z35" s="130" t="n">
         <v>92</v>
       </c>
-      <c r="AA35" s="210" t="n">
+      <c r="AA35" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="AB35" s="210" t="n">
+      <c r="AB35" s="130" t="n">
         <v>37</v>
       </c>
-      <c r="AC35" s="210" t="n"/>
-      <c r="AD35" s="210" t="n"/>
-      <c r="AE35" s="210" t="n"/>
-      <c r="AF35" s="231" t="n"/>
-      <c r="AG35" s="232">
+      <c r="AC35" s="130" t="n"/>
+      <c r="AD35" s="130" t="n"/>
+      <c r="AE35" s="130" t="n"/>
+      <c r="AF35" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="212">
         <f>SUM(AG8-X35)</f>
         <v/>
       </c>
-      <c r="AH35" s="233">
+      <c r="AH35" s="213">
         <f>SUM(AH8-Y35)</f>
         <v/>
       </c>
-      <c r="AI35" s="233">
+      <c r="AI35" s="213">
         <f>SUM(AI8-Z35)</f>
         <v/>
       </c>
-      <c r="AJ35" s="233">
+      <c r="AJ35" s="213">
         <f>SUM(AJ8-AA35)</f>
         <v/>
       </c>
-      <c r="AK35" s="233">
+      <c r="AK35" s="213">
         <f>SUM(AK8-AB35)</f>
         <v/>
       </c>
-      <c r="AL35" s="233">
+      <c r="AL35" s="213">
         <f>SUM(AL8-AC35)</f>
         <v/>
       </c>
-      <c r="AM35" s="233">
+      <c r="AM35" s="213">
         <f>SUM(AM8-AD35)</f>
         <v/>
       </c>
-      <c r="AN35" s="233">
+      <c r="AN35" s="213">
         <f>SUM(AN8-AE35)</f>
         <v/>
       </c>
-      <c r="AO35" s="234">
+      <c r="AO35" s="214">
         <f>SUM(AO8-AF35)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>BC2</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C36" s="230" t="n">
+      <c r="C36" s="146" t="n">
         <v>234</v>
       </c>
-      <c r="D36" s="210" t="n"/>
-      <c r="E36" s="210" t="n">
+      <c r="D36" s="130" t="n"/>
+      <c r="E36" s="130" t="n">
         <v>143</v>
       </c>
-      <c r="F36" s="210" t="n">
+      <c r="F36" s="130" t="n">
         <v>12</v>
       </c>
-      <c r="G36" s="210" t="n">
+      <c r="G36" s="130" t="n">
         <v>41</v>
       </c>
-      <c r="H36" s="210" t="n"/>
-      <c r="I36" s="210" t="n"/>
-      <c r="J36" s="210" t="n"/>
-      <c r="K36" s="231" t="n"/>
-      <c r="L36" s="232">
+      <c r="H36" s="130" t="n"/>
+      <c r="I36" s="130" t="n"/>
+      <c r="J36" s="130" t="n"/>
+      <c r="K36" s="147" t="n"/>
+      <c r="L36" s="212">
         <f>SUM(L9-C36)</f>
         <v/>
       </c>
-      <c r="M36" s="233">
+      <c r="M36" s="213">
         <f>SUM(M9-D36)</f>
         <v/>
       </c>
-      <c r="N36" s="233">
+      <c r="N36" s="213">
         <f>SUM(N9-E36)</f>
         <v/>
       </c>
-      <c r="O36" s="233">
+      <c r="O36" s="213">
         <f>SUM(O9-F36)</f>
         <v/>
       </c>
-      <c r="P36" s="233">
+      <c r="P36" s="213">
         <f>SUM(P9-G36)</f>
         <v/>
       </c>
-      <c r="Q36" s="233">
+      <c r="Q36" s="213">
         <f>SUM(Q9-H36)</f>
         <v/>
       </c>
-      <c r="R36" s="233">
+      <c r="R36" s="213">
         <f>SUM(R9-I36)</f>
         <v/>
       </c>
-      <c r="S36" s="233">
+      <c r="S36" s="213">
         <f>SUM(S9-J36)</f>
         <v/>
       </c>
-      <c r="T36" s="234">
+      <c r="T36" s="214">
         <f>SUM(T9-K36)</f>
         <v/>
       </c>
-      <c r="V36" s="35" t="inlineStr">
+      <c r="V36" s="26" t="inlineStr">
         <is>
           <t>CELLO</t>
         </is>
       </c>
-      <c r="W36" s="36" t="inlineStr">
+      <c r="W36" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X36" s="230" t="n">
+      <c r="X36" s="146" t="n">
         <v>6</v>
       </c>
-      <c r="Y36" s="210" t="n"/>
-      <c r="Z36" s="210" t="n">
+      <c r="Y36" s="130" t="n"/>
+      <c r="Z36" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="AA36" s="210" t="n"/>
-      <c r="AB36" s="210" t="n"/>
-      <c r="AC36" s="210" t="n"/>
-      <c r="AD36" s="210" t="n"/>
-      <c r="AE36" s="210" t="n"/>
-      <c r="AF36" s="231" t="n"/>
-      <c r="AG36" s="232">
+      <c r="AA36" s="130" t="n"/>
+      <c r="AB36" s="130" t="n"/>
+      <c r="AC36" s="130" t="n"/>
+      <c r="AD36" s="130" t="n"/>
+      <c r="AE36" s="130" t="n"/>
+      <c r="AF36" s="147" t="n"/>
+      <c r="AG36" s="212">
         <f>SUM(AG9-X36)</f>
         <v/>
       </c>
-      <c r="AH36" s="233">
+      <c r="AH36" s="213">
         <f>SUM(AH9-Y36)</f>
         <v/>
       </c>
-      <c r="AI36" s="233">
+      <c r="AI36" s="213">
         <f>SUM(AI9-Z36)</f>
         <v/>
       </c>
-      <c r="AJ36" s="233">
+      <c r="AJ36" s="213">
         <f>SUM(AJ9-AA36)</f>
         <v/>
       </c>
-      <c r="AK36" s="233">
+      <c r="AK36" s="213">
         <f>SUM(AK9-AB36)</f>
         <v/>
       </c>
-      <c r="AL36" s="233">
+      <c r="AL36" s="213">
         <f>SUM(AL9-AC36)</f>
         <v/>
       </c>
-      <c r="AM36" s="233">
+      <c r="AM36" s="213">
         <f>SUM(AM9-AD36)</f>
         <v/>
       </c>
-      <c r="AN36" s="233">
+      <c r="AN36" s="213">
         <f>SUM(AN9-AE36)</f>
         <v/>
       </c>
-      <c r="AO36" s="234">
+      <c r="AO36" s="214">
         <f>SUM(AO9-AF36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="43" t="n"/>
-      <c r="B37" s="44" t="n"/>
-      <c r="C37" s="48" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="82" t="n"/>
-      <c r="L37" s="235">
+      <c r="A37" s="34" t="n"/>
+      <c r="B37" s="35" t="n"/>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="40" t="n"/>
+      <c r="E37" s="40" t="n"/>
+      <c r="F37" s="40" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="40" t="n"/>
+      <c r="I37" s="40" t="n"/>
+      <c r="J37" s="40" t="n"/>
+      <c r="K37" s="65" t="n"/>
+      <c r="L37" s="215">
         <f>SUM(L10-C37)</f>
         <v/>
       </c>
-      <c r="M37" s="236">
+      <c r="M37" s="216">
         <f>SUM(M10-D37)</f>
         <v/>
       </c>
-      <c r="N37" s="236">
+      <c r="N37" s="216">
         <f>SUM(N10-E37)</f>
         <v/>
       </c>
-      <c r="O37" s="236">
+      <c r="O37" s="216">
         <f>SUM(O10-F37)</f>
         <v/>
       </c>
-      <c r="P37" s="236">
+      <c r="P37" s="216">
         <f>SUM(P10-G37)</f>
         <v/>
       </c>
-      <c r="Q37" s="236">
+      <c r="Q37" s="216">
         <f>SUM(Q10-H37)</f>
         <v/>
       </c>
-      <c r="R37" s="236">
+      <c r="R37" s="216">
         <f>SUM(R10-I37)</f>
         <v/>
       </c>
-      <c r="S37" s="236">
+      <c r="S37" s="216">
         <f>SUM(S10-J37)</f>
         <v/>
       </c>
-      <c r="T37" s="237">
+      <c r="T37" s="217">
         <f>SUM(T10-K37)</f>
         <v/>
       </c>
-      <c r="V37" s="35" t="inlineStr">
+      <c r="V37" s="26" t="inlineStr">
         <is>
           <t>PW</t>
         </is>
       </c>
-      <c r="W37" s="36" t="inlineStr">
+      <c r="W37" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X37" s="230" t="n">
+      <c r="X37" s="146" t="n">
         <v>254</v>
       </c>
-      <c r="Y37" s="210" t="n"/>
-      <c r="Z37" s="210" t="n">
+      <c r="Y37" s="130" t="n"/>
+      <c r="Z37" s="130" t="n">
         <v>218</v>
       </c>
-      <c r="AA37" s="210" t="n"/>
-      <c r="AB37" s="210" t="n"/>
-      <c r="AC37" s="210" t="n"/>
-      <c r="AD37" s="210" t="n"/>
-      <c r="AE37" s="210" t="n"/>
-      <c r="AF37" s="231" t="n"/>
-      <c r="AG37" s="232">
+      <c r="AA37" s="130" t="n"/>
+      <c r="AB37" s="130" t="n"/>
+      <c r="AC37" s="130" t="n"/>
+      <c r="AD37" s="130" t="n"/>
+      <c r="AE37" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="212">
         <f>SUM(AG10-X37)</f>
         <v/>
       </c>
-      <c r="AH37" s="233">
+      <c r="AH37" s="213">
         <f>SUM(AH10-Y37)</f>
         <v/>
       </c>
-      <c r="AI37" s="233">
+      <c r="AI37" s="213">
         <f>SUM(AI10-Z37)</f>
         <v/>
       </c>
-      <c r="AJ37" s="233">
+      <c r="AJ37" s="213">
         <f>SUM(AJ10-AA37)</f>
         <v/>
       </c>
-      <c r="AK37" s="233">
+      <c r="AK37" s="213">
         <f>SUM(AK10-AB37)</f>
         <v/>
       </c>
-      <c r="AL37" s="233">
+      <c r="AL37" s="213">
         <f>SUM(AL10-AC37)</f>
         <v/>
       </c>
-      <c r="AM37" s="233">
+      <c r="AM37" s="213">
         <f>SUM(AM10-AD37)</f>
         <v/>
       </c>
-      <c r="AN37" s="233">
+      <c r="AN37" s="213">
         <f>SUM(AN10-AE37)</f>
         <v/>
       </c>
-      <c r="AO37" s="234">
+      <c r="AO37" s="214">
         <f>SUM(AO10-AF37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="43" t="n"/>
-      <c r="B38" s="44" t="n"/>
-      <c r="C38" s="48" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="82" t="n"/>
-      <c r="L38" s="235">
+      <c r="A38" s="34" t="n"/>
+      <c r="B38" s="35" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="40" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="40" t="n"/>
+      <c r="I38" s="40" t="n"/>
+      <c r="J38" s="40" t="n"/>
+      <c r="K38" s="65" t="n"/>
+      <c r="L38" s="215">
         <f>SUM(L11-C38)</f>
         <v/>
       </c>
-      <c r="M38" s="236">
+      <c r="M38" s="216">
         <f>SUM(M11-D38)</f>
         <v/>
       </c>
-      <c r="N38" s="236">
+      <c r="N38" s="216">
         <f>SUM(N11-E38)</f>
         <v/>
       </c>
-      <c r="O38" s="236">
+      <c r="O38" s="216">
         <f>SUM(O11-F38)</f>
         <v/>
       </c>
-      <c r="P38" s="236">
+      <c r="P38" s="216">
         <f>SUM(P11-G38)</f>
         <v/>
       </c>
-      <c r="Q38" s="236">
+      <c r="Q38" s="216">
         <f>SUM(Q11-H38)</f>
         <v/>
       </c>
-      <c r="R38" s="236">
+      <c r="R38" s="216">
         <f>SUM(R11-I38)</f>
         <v/>
       </c>
-      <c r="S38" s="236">
+      <c r="S38" s="216">
         <f>SUM(S11-J38)</f>
         <v/>
       </c>
-      <c r="T38" s="237">
+      <c r="T38" s="217">
         <f>SUM(T11-K38)</f>
         <v/>
       </c>
-      <c r="V38" s="35" t="n"/>
-      <c r="W38" s="36" t="n"/>
-      <c r="X38" s="48" t="n"/>
-      <c r="Y38" s="49" t="n"/>
-      <c r="Z38" s="49" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="49" t="n"/>
-      <c r="AD38" s="49" t="n"/>
-      <c r="AE38" s="49" t="n"/>
-      <c r="AF38" s="82" t="n"/>
-      <c r="AG38" s="235">
+      <c r="V38" s="26" t="n"/>
+      <c r="W38" s="27" t="n"/>
+      <c r="X38" s="39" t="n"/>
+      <c r="Y38" s="40" t="n"/>
+      <c r="Z38" s="40" t="n"/>
+      <c r="AA38" s="21" t="n"/>
+      <c r="AB38" s="21" t="n"/>
+      <c r="AC38" s="40" t="n"/>
+      <c r="AD38" s="40" t="n"/>
+      <c r="AE38" s="40" t="n"/>
+      <c r="AF38" s="65" t="n"/>
+      <c r="AG38" s="215">
         <f>SUM(AG11-X38)</f>
         <v/>
       </c>
-      <c r="AH38" s="236">
+      <c r="AH38" s="216">
         <f>SUM(AH11-Y38)</f>
         <v/>
       </c>
-      <c r="AI38" s="236">
+      <c r="AI38" s="216">
         <f>SUM(AI11-Z38)</f>
         <v/>
       </c>
-      <c r="AJ38" s="236">
+      <c r="AJ38" s="216">
         <f>SUM(AJ11-AA38)</f>
         <v/>
       </c>
-      <c r="AK38" s="236">
+      <c r="AK38" s="216">
         <f>SUM(AK11-AB38)</f>
         <v/>
       </c>
-      <c r="AL38" s="236">
+      <c r="AL38" s="216">
         <f>SUM(AL11-AC38)</f>
         <v/>
       </c>
-      <c r="AM38" s="236">
+      <c r="AM38" s="216">
         <f>SUM(AM11-AD38)</f>
         <v/>
       </c>
-      <c r="AN38" s="236">
+      <c r="AN38" s="216">
         <f>SUM(AN11-AE38)</f>
         <v/>
       </c>
-      <c r="AO38" s="237">
+      <c r="AO38" s="217">
         <f>SUM(AO11-AF38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="43" t="n"/>
-      <c r="B39" s="44" t="n"/>
-      <c r="C39" s="48" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
-      <c r="J39" s="49" t="n"/>
-      <c r="K39" s="82" t="n"/>
-      <c r="L39" s="235">
+      <c r="A39" s="34" t="n"/>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="40" t="n"/>
+      <c r="E39" s="40" t="n"/>
+      <c r="F39" s="40" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="40" t="n"/>
+      <c r="I39" s="40" t="n"/>
+      <c r="J39" s="40" t="n"/>
+      <c r="K39" s="65" t="n"/>
+      <c r="L39" s="215">
         <f>SUM(L12-C39)</f>
         <v/>
       </c>
-      <c r="M39" s="236">
+      <c r="M39" s="216">
         <f>SUM(M12-D39)</f>
         <v/>
       </c>
-      <c r="N39" s="236">
+      <c r="N39" s="216">
         <f>SUM(N12-E39)</f>
         <v/>
       </c>
-      <c r="O39" s="236">
+      <c r="O39" s="216">
         <f>SUM(O12-F39)</f>
         <v/>
       </c>
-      <c r="P39" s="236">
+      <c r="P39" s="216">
         <f>SUM(P12-G39)</f>
         <v/>
       </c>
-      <c r="Q39" s="236">
+      <c r="Q39" s="216">
         <f>SUM(Q12-H39)</f>
         <v/>
       </c>
-      <c r="R39" s="236">
+      <c r="R39" s="216">
         <f>SUM(R12-I39)</f>
         <v/>
       </c>
-      <c r="S39" s="236">
+      <c r="S39" s="216">
         <f>SUM(S12-J39)</f>
         <v/>
       </c>
-      <c r="T39" s="237">
+      <c r="T39" s="217">
         <f>SUM(T12-K39)</f>
         <v/>
       </c>
-      <c r="V39" s="35" t="n"/>
-      <c r="W39" s="36" t="n"/>
-      <c r="X39" s="48" t="n"/>
-      <c r="Y39" s="49" t="n"/>
-      <c r="Z39" s="49" t="n"/>
-      <c r="AA39" s="49" t="n"/>
-      <c r="AB39" s="49" t="n"/>
-      <c r="AC39" s="49" t="n"/>
-      <c r="AD39" s="49" t="n"/>
-      <c r="AE39" s="49" t="n"/>
-      <c r="AF39" s="82" t="n"/>
-      <c r="AG39" s="235">
+      <c r="V39" s="26" t="n"/>
+      <c r="W39" s="27" t="n"/>
+      <c r="X39" s="39" t="n"/>
+      <c r="Y39" s="40" t="n"/>
+      <c r="Z39" s="40" t="n"/>
+      <c r="AA39" s="40" t="n"/>
+      <c r="AB39" s="40" t="n"/>
+      <c r="AC39" s="40" t="n"/>
+      <c r="AD39" s="40" t="n"/>
+      <c r="AE39" s="40" t="n"/>
+      <c r="AF39" s="65" t="n"/>
+      <c r="AG39" s="215">
         <f>SUM(AG12-X39)</f>
         <v/>
       </c>
-      <c r="AH39" s="236">
+      <c r="AH39" s="216">
         <f>SUM(AH12-Y39)</f>
         <v/>
       </c>
-      <c r="AI39" s="236">
+      <c r="AI39" s="216">
         <f>SUM(AI12-Z39)</f>
         <v/>
       </c>
-      <c r="AJ39" s="236">
+      <c r="AJ39" s="216">
         <f>SUM(AJ12-AA39)</f>
         <v/>
       </c>
-      <c r="AK39" s="236">
+      <c r="AK39" s="216">
         <f>SUM(AK12-AB39)</f>
         <v/>
       </c>
-      <c r="AL39" s="236">
+      <c r="AL39" s="216">
         <f>SUM(AL12-AC39)</f>
         <v/>
       </c>
-      <c r="AM39" s="236">
+      <c r="AM39" s="216">
         <f>SUM(AM12-AD39)</f>
         <v/>
       </c>
-      <c r="AN39" s="236">
+      <c r="AN39" s="216">
         <f>SUM(AN12-AE39)</f>
         <v/>
       </c>
-      <c r="AO39" s="237">
+      <c r="AO39" s="217">
         <f>SUM(AO12-AF39)</f>
         <v/>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AS39" s="165" t="inlineStr">
         <is>
           <t xml:space="preserve">   </t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="45" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="B40" s="46" t="n"/>
-      <c r="C40" s="84" t="n"/>
-      <c r="D40" s="85" t="n"/>
-      <c r="E40" s="85" t="n"/>
-      <c r="F40" s="85" t="n"/>
-      <c r="G40" s="85" t="n"/>
-      <c r="H40" s="85" t="n"/>
-      <c r="I40" s="85" t="n"/>
-      <c r="J40" s="85" t="n"/>
-      <c r="K40" s="86" t="n"/>
-      <c r="L40" s="238">
+      <c r="B40" s="37" t="n"/>
+      <c r="C40" s="66" t="n"/>
+      <c r="D40" s="67" t="n"/>
+      <c r="E40" s="67" t="n"/>
+      <c r="F40" s="67" t="n"/>
+      <c r="G40" s="67" t="n"/>
+      <c r="H40" s="67" t="n"/>
+      <c r="I40" s="67" t="n"/>
+      <c r="J40" s="67" t="n"/>
+      <c r="K40" s="68" t="n"/>
+      <c r="L40" s="218">
         <f>SUM(L13-C40)</f>
         <v/>
       </c>
-      <c r="M40" s="239">
+      <c r="M40" s="219">
         <f>SUM(M13-D40)</f>
         <v/>
       </c>
-      <c r="N40" s="239">
+      <c r="N40" s="219">
         <f>SUM(N13-E40)</f>
         <v/>
       </c>
-      <c r="O40" s="239">
+      <c r="O40" s="219">
         <f>SUM(O13-F40)</f>
         <v/>
       </c>
-      <c r="P40" s="239">
+      <c r="P40" s="219">
         <f>SUM(P13-G40)</f>
         <v/>
       </c>
-      <c r="Q40" s="239">
+      <c r="Q40" s="219">
         <f>SUM(Q13-H40)</f>
         <v/>
       </c>
-      <c r="R40" s="239">
+      <c r="R40" s="219">
         <f>SUM(R13-I40)</f>
         <v/>
       </c>
-      <c r="S40" s="239">
+      <c r="S40" s="219">
         <f>SUM(S13-J40)</f>
         <v/>
       </c>
-      <c r="T40" s="240">
+      <c r="T40" s="220">
         <f>SUM(T13-K40)</f>
         <v/>
       </c>
-      <c r="V40" s="45" t="inlineStr">
+      <c r="V40" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="W40" s="46" t="n"/>
-      <c r="X40" s="84" t="n"/>
-      <c r="Y40" s="85" t="n"/>
-      <c r="Z40" s="85" t="n"/>
-      <c r="AA40" s="85" t="n"/>
-      <c r="AB40" s="85" t="n"/>
-      <c r="AC40" s="85" t="n"/>
-      <c r="AD40" s="85" t="n"/>
-      <c r="AE40" s="85" t="n"/>
-      <c r="AF40" s="86" t="n"/>
-      <c r="AG40" s="235">
+      <c r="W40" s="37" t="n"/>
+      <c r="X40" s="66" t="n"/>
+      <c r="Y40" s="67" t="n"/>
+      <c r="Z40" s="67" t="n"/>
+      <c r="AA40" s="67" t="n"/>
+      <c r="AB40" s="67" t="n"/>
+      <c r="AC40" s="67" t="n"/>
+      <c r="AD40" s="67" t="n"/>
+      <c r="AE40" s="67" t="n"/>
+      <c r="AF40" s="68" t="n"/>
+      <c r="AG40" s="215">
         <f>SUM(AG13-X40)</f>
         <v/>
       </c>
-      <c r="AH40" s="236">
+      <c r="AH40" s="216">
         <f>SUM(AH13-Y40)</f>
         <v/>
       </c>
-      <c r="AI40" s="236">
+      <c r="AI40" s="216">
         <f>SUM(AI13-Z40)</f>
         <v/>
       </c>
-      <c r="AJ40" s="236">
+      <c r="AJ40" s="216">
         <f>SUM(AJ13-AA40)</f>
         <v/>
       </c>
-      <c r="AK40" s="236">
+      <c r="AK40" s="216">
         <f>SUM(AK13-AB40)</f>
         <v/>
       </c>
-      <c r="AL40" s="236">
+      <c r="AL40" s="216">
         <f>SUM(AL13-AC40)</f>
         <v/>
       </c>
-      <c r="AM40" s="236">
+      <c r="AM40" s="216">
         <f>SUM(AM13-AD40)</f>
         <v/>
       </c>
-      <c r="AN40" s="236">
+      <c r="AN40" s="216">
         <f>SUM(AN13-AE40)</f>
         <v/>
       </c>
-      <c r="AO40" s="237">
+      <c r="AO40" s="217">
         <f>SUM(AO13-AF40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="212" t="n"/>
-      <c r="B41" s="213" t="n"/>
-      <c r="C41" s="70">
+      <c r="A41" s="181" t="n"/>
+      <c r="B41" s="182" t="n"/>
+      <c r="C41" s="61">
         <f>SUM(C31:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="71">
+      <c r="D41" s="62">
         <f>SUM(D31:D40)</f>
         <v/>
       </c>
-      <c r="E41" s="71">
+      <c r="E41" s="62">
         <f>SUM(E31:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="71">
+      <c r="F41" s="62">
         <f>SUM(F31:F40)</f>
         <v/>
       </c>
-      <c r="G41" s="71">
+      <c r="G41" s="62">
         <f>SUM(G31:G40)</f>
         <v/>
       </c>
-      <c r="H41" s="71">
+      <c r="H41" s="62">
         <f>SUM(H31:H40)</f>
         <v/>
       </c>
-      <c r="I41" s="71">
+      <c r="I41" s="62">
         <f>SUM(I31:I40)</f>
         <v/>
       </c>
-      <c r="J41" s="71">
+      <c r="J41" s="62">
         <f>SUM(J31:J40)</f>
         <v/>
       </c>
-      <c r="K41" s="87">
+      <c r="K41" s="69">
         <f>SUM(K31:K40)</f>
         <v/>
       </c>
-      <c r="L41" s="57">
+      <c r="L41" s="48">
         <f>SUM(L31:L40)</f>
         <v/>
       </c>
-      <c r="M41" s="58">
+      <c r="M41" s="49">
         <f>SUM(M31:M40)</f>
         <v/>
       </c>
-      <c r="N41" s="58">
+      <c r="N41" s="49">
         <f>SUM(N31:N40)</f>
         <v/>
       </c>
-      <c r="O41" s="58">
+      <c r="O41" s="49">
         <f>SUM(O31:O40)</f>
         <v/>
       </c>
-      <c r="P41" s="58">
+      <c r="P41" s="49">
         <f>SUM(P31:P40)</f>
         <v/>
       </c>
-      <c r="Q41" s="58">
+      <c r="Q41" s="49">
         <f>SUM(Q31:Q40)</f>
         <v/>
       </c>
-      <c r="R41" s="58">
+      <c r="R41" s="49">
         <f>SUM(R31:R40)</f>
         <v/>
       </c>
-      <c r="S41" s="58">
+      <c r="S41" s="49">
         <f>SUM(S31:S40)</f>
         <v/>
       </c>
-      <c r="T41" s="59">
+      <c r="T41" s="50">
         <f>SUM(T31:T40)</f>
         <v/>
       </c>
       <c r="U41" s="9" t="n"/>
-      <c r="V41" s="212" t="inlineStr">
+      <c r="V41" s="181" t="inlineStr">
         <is>
           <t>TOTAL AT LCH</t>
         </is>
       </c>
-      <c r="W41" s="213" t="n"/>
-      <c r="X41" s="70">
+      <c r="W41" s="182" t="n"/>
+      <c r="X41" s="61">
         <f>SUM(X31:X40)</f>
         <v/>
       </c>
-      <c r="Y41" s="71">
+      <c r="Y41" s="62">
         <f>SUM(Y31:Y40)</f>
         <v/>
       </c>
-      <c r="Z41" s="71">
+      <c r="Z41" s="62">
         <f>SUM(Z31:Z40)</f>
         <v/>
       </c>
-      <c r="AA41" s="71">
+      <c r="AA41" s="62">
         <f>SUM(AA31:AA40)</f>
         <v/>
       </c>
-      <c r="AB41" s="71">
+      <c r="AB41" s="62">
         <f>SUM(AB31:AB40)</f>
         <v/>
       </c>
-      <c r="AC41" s="71">
+      <c r="AC41" s="62">
         <f>SUM(AC31:AC40)</f>
         <v/>
       </c>
-      <c r="AD41" s="71">
+      <c r="AD41" s="62">
         <f>SUM(AD31:AD40)</f>
         <v/>
       </c>
-      <c r="AE41" s="71">
+      <c r="AE41" s="62">
         <f>SUM(AE31:AE40)</f>
         <v/>
       </c>
-      <c r="AF41" s="87">
+      <c r="AF41" s="69">
         <f>SUM(AF31:AF40)</f>
         <v/>
       </c>
-      <c r="AG41" s="57">
+      <c r="AG41" s="48">
         <f>SUM(AG31:AG40)</f>
         <v/>
       </c>
-      <c r="AH41" s="58">
+      <c r="AH41" s="49">
         <f>SUM(AH31:AH40)</f>
         <v/>
       </c>
-      <c r="AI41" s="58">
+      <c r="AI41" s="49">
         <f>SUM(AI31:AI40)</f>
         <v/>
       </c>
-      <c r="AJ41" s="58">
+      <c r="AJ41" s="49">
         <f>SUM(AJ31:AJ40)</f>
         <v/>
       </c>
-      <c r="AK41" s="58">
+      <c r="AK41" s="49">
         <f>SUM(AK31:AK40)</f>
         <v/>
       </c>
-      <c r="AL41" s="58">
+      <c r="AL41" s="49">
         <f>SUM(AL31:AL40)</f>
         <v/>
       </c>
-      <c r="AM41" s="58">
+      <c r="AM41" s="49">
         <f>SUM(AM31:AM40)</f>
         <v/>
       </c>
-      <c r="AN41" s="58">
+      <c r="AN41" s="49">
         <f>SUM(AN31:AN40)</f>
         <v/>
       </c>
-      <c r="AO41" s="59">
+      <c r="AO41" s="50">
         <f>SUM(AO31:AO40)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="9.949999999999999" customHeight="1" thickBot="1">
-      <c r="A42" s="60" t="n"/>
-      <c r="AO42" s="61" t="n"/>
+      <c r="A42" s="51" t="n"/>
+      <c r="AO42" s="52" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="185" t="inlineStr">
+      <c r="A43" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="B43" s="186" t="n"/>
-      <c r="C43" s="151" t="inlineStr">
+      <c r="B43" s="178" t="n"/>
+      <c r="C43" s="174" t="inlineStr">
         <is>
           <t>BOOKING (BKK)</t>
         </is>
       </c>
-      <c r="D43" s="187" t="n"/>
-      <c r="E43" s="187" t="n"/>
-      <c r="F43" s="187" t="n"/>
-      <c r="G43" s="187" t="n"/>
-      <c r="H43" s="188" t="n"/>
-      <c r="I43" s="241" t="inlineStr">
+      <c r="D43" s="167" t="n"/>
+      <c r="E43" s="167" t="n"/>
+      <c r="F43" s="167" t="n"/>
+      <c r="G43" s="167" t="n"/>
+      <c r="H43" s="175" t="n"/>
+      <c r="I43" s="183" t="inlineStr">
         <is>
           <t>21-27/09/2026</t>
         </is>
       </c>
-      <c r="J43" s="187" t="n"/>
-      <c r="K43" s="190" t="n"/>
-      <c r="L43" s="143" t="inlineStr">
+      <c r="J43" s="167" t="n"/>
+      <c r="K43" s="168" t="n"/>
+      <c r="L43" s="176" t="inlineStr">
         <is>
           <t>STOCK END WK (BKK)</t>
         </is>
       </c>
-      <c r="M43" s="187" t="n"/>
-      <c r="N43" s="187" t="n"/>
-      <c r="O43" s="187" t="n"/>
-      <c r="P43" s="187" t="n"/>
-      <c r="Q43" s="187" t="n"/>
-      <c r="R43" s="187" t="n"/>
-      <c r="S43" s="187" t="n"/>
-      <c r="T43" s="188" t="n"/>
+      <c r="M43" s="167" t="n"/>
+      <c r="N43" s="167" t="n"/>
+      <c r="O43" s="167" t="n"/>
+      <c r="P43" s="167" t="n"/>
+      <c r="Q43" s="167" t="n"/>
+      <c r="R43" s="167" t="n"/>
+      <c r="S43" s="167" t="n"/>
+      <c r="T43" s="175" t="n"/>
       <c r="U43" s="2" t="n"/>
-      <c r="V43" s="185" t="inlineStr">
+      <c r="V43" s="177" t="inlineStr">
         <is>
           <t>LOCATION</t>
         </is>
       </c>
-      <c r="W43" s="186" t="n"/>
-      <c r="X43" s="151" t="inlineStr">
+      <c r="W43" s="178" t="n"/>
+      <c r="X43" s="174" t="inlineStr">
         <is>
           <t>BOOKING (LCH)</t>
         </is>
       </c>
-      <c r="Y43" s="187" t="n"/>
-      <c r="Z43" s="187" t="n"/>
-      <c r="AA43" s="187" t="n"/>
-      <c r="AB43" s="187" t="n"/>
-      <c r="AC43" s="188" t="n"/>
-      <c r="AD43" s="241" t="inlineStr">
+      <c r="Y43" s="167" t="n"/>
+      <c r="Z43" s="167" t="n"/>
+      <c r="AA43" s="167" t="n"/>
+      <c r="AB43" s="167" t="n"/>
+      <c r="AC43" s="175" t="n"/>
+      <c r="AD43" s="183" t="inlineStr">
         <is>
           <t>21-27/09/2026</t>
         </is>
       </c>
-      <c r="AE43" s="187" t="n"/>
-      <c r="AF43" s="190" t="n"/>
-      <c r="AG43" s="143" t="inlineStr">
+      <c r="AE43" s="167" t="n"/>
+      <c r="AF43" s="168" t="n"/>
+      <c r="AG43" s="176" t="inlineStr">
         <is>
           <t>STOCK END WK (LCH)</t>
         </is>
       </c>
-      <c r="AH43" s="187" t="n"/>
-      <c r="AI43" s="187" t="n"/>
-      <c r="AJ43" s="187" t="n"/>
-      <c r="AK43" s="187" t="n"/>
-      <c r="AL43" s="187" t="n"/>
-      <c r="AM43" s="187" t="n"/>
-      <c r="AN43" s="187" t="n"/>
-      <c r="AO43" s="188" t="n"/>
+      <c r="AH43" s="167" t="n"/>
+      <c r="AI43" s="167" t="n"/>
+      <c r="AJ43" s="167" t="n"/>
+      <c r="AK43" s="167" t="n"/>
+      <c r="AL43" s="167" t="n"/>
+      <c r="AM43" s="167" t="n"/>
+      <c r="AN43" s="167" t="n"/>
+      <c r="AO43" s="175" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="191" t="n"/>
-      <c r="B44" s="192" t="n"/>
+      <c r="A44" s="179" t="n"/>
+      <c r="B44" s="180" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -5686,8 +5581,8 @@
         </is>
       </c>
       <c r="U44" s="9" t="n"/>
-      <c r="V44" s="191" t="n"/>
-      <c r="W44" s="192" t="n"/>
+      <c r="V44" s="179" t="n"/>
+      <c r="W44" s="180" t="n"/>
       <c r="X44" s="4" t="inlineStr">
         <is>
           <t>22GP</t>
@@ -5780,62 +5675,62 @@
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="72" t="inlineStr">
+      <c r="A45" s="63" t="inlineStr">
         <is>
           <t>PAT</t>
         </is>
       </c>
-      <c r="B45" s="73" t="inlineStr">
+      <c r="B45" s="64" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C45" s="193" t="n">
+      <c r="C45" s="113" t="n">
         <v>11</v>
       </c>
-      <c r="D45" s="194" t="n"/>
-      <c r="E45" s="194" t="n">
+      <c r="D45" s="114" t="n"/>
+      <c r="E45" s="114" t="n">
         <v>18</v>
       </c>
-      <c r="F45" s="194" t="n"/>
-      <c r="G45" s="194" t="n"/>
-      <c r="H45" s="194" t="n"/>
-      <c r="I45" s="194" t="n"/>
-      <c r="J45" s="194" t="n"/>
-      <c r="K45" s="195" t="n"/>
-      <c r="L45" s="216">
+      <c r="F45" s="114" t="n"/>
+      <c r="G45" s="114" t="n"/>
+      <c r="H45" s="114" t="n"/>
+      <c r="I45" s="114" t="n"/>
+      <c r="J45" s="114" t="n"/>
+      <c r="K45" s="115" t="n"/>
+      <c r="L45" s="204">
         <f>SUM(L31-C45)</f>
         <v/>
       </c>
-      <c r="M45" s="217">
+      <c r="M45" s="205">
         <f>SUM(M31-D45)</f>
         <v/>
       </c>
-      <c r="N45" s="218">
+      <c r="N45" s="206">
         <f>SUM(N31-E45)</f>
         <v/>
       </c>
-      <c r="O45" s="217">
+      <c r="O45" s="205">
         <f>SUM(O31-F45)</f>
         <v/>
       </c>
-      <c r="P45" s="217">
+      <c r="P45" s="205">
         <f>SUM(P31-G45)</f>
         <v/>
       </c>
-      <c r="Q45" s="217">
+      <c r="Q45" s="205">
         <f>SUM(Q31-H45)</f>
         <v/>
       </c>
-      <c r="R45" s="217">
+      <c r="R45" s="205">
         <f>SUM(R31-I45)</f>
         <v/>
       </c>
-      <c r="S45" s="217">
+      <c r="S45" s="205">
         <f>SUM(S31-J45)</f>
         <v/>
       </c>
-      <c r="T45" s="219">
+      <c r="T45" s="207">
         <f>SUM(T31-K45)</f>
         <v/>
       </c>
@@ -5849,1227 +5744,1227 @@
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X45" s="220" t="n"/>
-      <c r="Y45" s="221" t="n"/>
-      <c r="Z45" s="221" t="n"/>
-      <c r="AA45" s="221" t="n"/>
-      <c r="AB45" s="221" t="n"/>
-      <c r="AC45" s="221" t="n"/>
-      <c r="AD45" s="221" t="n"/>
-      <c r="AE45" s="221" t="n"/>
-      <c r="AF45" s="222" t="n"/>
-      <c r="AG45" s="223">
+      <c r="X45" s="136" t="n"/>
+      <c r="Y45" s="137" t="n"/>
+      <c r="Z45" s="137" t="n"/>
+      <c r="AA45" s="137" t="n"/>
+      <c r="AB45" s="137" t="n"/>
+      <c r="AC45" s="137" t="n"/>
+      <c r="AD45" s="137" t="n"/>
+      <c r="AE45" s="137" t="n"/>
+      <c r="AF45" s="138" t="n"/>
+      <c r="AG45" s="208">
         <f>SUM(AG31-X45)</f>
         <v/>
       </c>
-      <c r="AH45" s="217">
+      <c r="AH45" s="205">
         <f>SUM(AH31-Y45)</f>
         <v/>
       </c>
-      <c r="AI45" s="217">
+      <c r="AI45" s="205">
         <f>SUM(AI31-Z45)</f>
         <v/>
       </c>
-      <c r="AJ45" s="217">
+      <c r="AJ45" s="205">
         <f>SUM(AJ31-AA45)</f>
         <v/>
       </c>
-      <c r="AK45" s="217">
+      <c r="AK45" s="205">
         <f>SUM(AK31-AB45)</f>
         <v/>
       </c>
-      <c r="AL45" s="217">
+      <c r="AL45" s="205">
         <f>SUM(AL31-AC45)</f>
         <v/>
       </c>
-      <c r="AM45" s="217">
+      <c r="AM45" s="205">
         <f>SUM(AM31-AD45)</f>
         <v/>
       </c>
-      <c r="AN45" s="217">
+      <c r="AN45" s="205">
         <f>SUM(AN31-AE45)</f>
         <v/>
       </c>
-      <c r="AO45" s="219">
+      <c r="AO45" s="207">
         <f>SUM(AO31-AF45)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>UNITHAI</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="C46" s="201" t="n"/>
-      <c r="D46" s="202" t="n"/>
-      <c r="E46" s="202" t="n">
+      <c r="C46" s="121" t="n"/>
+      <c r="D46" s="122" t="n"/>
+      <c r="E46" s="122" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="202" t="n"/>
-      <c r="G46" s="202" t="n"/>
-      <c r="H46" s="202" t="n"/>
-      <c r="I46" s="202" t="n"/>
-      <c r="J46" s="202" t="n"/>
-      <c r="K46" s="203" t="n"/>
-      <c r="L46" s="224">
+      <c r="F46" s="122" t="n"/>
+      <c r="G46" s="122" t="n"/>
+      <c r="H46" s="122" t="n"/>
+      <c r="I46" s="122" t="n"/>
+      <c r="J46" s="122" t="n"/>
+      <c r="K46" s="123" t="n"/>
+      <c r="L46" s="209">
         <f>SUM(L32-C46)</f>
         <v/>
       </c>
-      <c r="M46" s="225">
+      <c r="M46" s="210">
         <f>SUM(M32-D46)</f>
         <v/>
       </c>
-      <c r="N46" s="225">
+      <c r="N46" s="210">
         <f>SUM(N32-E46)</f>
         <v/>
       </c>
-      <c r="O46" s="225">
+      <c r="O46" s="210">
         <f>SUM(O32-F46)</f>
         <v/>
       </c>
-      <c r="P46" s="225">
+      <c r="P46" s="210">
         <f>SUM(P32-G46)</f>
         <v/>
       </c>
-      <c r="Q46" s="225">
+      <c r="Q46" s="210">
         <f>SUM(Q32-H46)</f>
         <v/>
       </c>
-      <c r="R46" s="225">
+      <c r="R46" s="210">
         <f>SUM(R32-I46)</f>
         <v/>
       </c>
-      <c r="S46" s="225">
+      <c r="S46" s="210">
         <f>SUM(S32-J46)</f>
         <v/>
       </c>
-      <c r="T46" s="226">
+      <c r="T46" s="211">
         <f>SUM(T32-K46)</f>
         <v/>
       </c>
-      <c r="V46" s="23" t="inlineStr">
+      <c r="V46" s="16" t="inlineStr">
         <is>
           <t>ESCO</t>
         </is>
       </c>
-      <c r="W46" s="24" t="inlineStr">
+      <c r="W46" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X46" s="227" t="n"/>
-      <c r="Y46" s="228" t="n"/>
-      <c r="Z46" s="228" t="n"/>
-      <c r="AA46" s="228" t="n"/>
-      <c r="AB46" s="228" t="n"/>
-      <c r="AC46" s="228" t="n"/>
-      <c r="AD46" s="228" t="n"/>
-      <c r="AE46" s="228" t="n"/>
-      <c r="AF46" s="229" t="n"/>
-      <c r="AG46" s="224">
+      <c r="X46" s="143" t="n"/>
+      <c r="Y46" s="144" t="n"/>
+      <c r="Z46" s="144" t="n"/>
+      <c r="AA46" s="144" t="n"/>
+      <c r="AB46" s="144" t="n"/>
+      <c r="AC46" s="144" t="n"/>
+      <c r="AD46" s="144" t="n"/>
+      <c r="AE46" s="144" t="n"/>
+      <c r="AF46" s="145" t="n"/>
+      <c r="AG46" s="209">
         <f>SUM(AG32-X46)</f>
         <v/>
       </c>
-      <c r="AH46" s="225">
+      <c r="AH46" s="210">
         <f>SUM(AH32-Y46)</f>
         <v/>
       </c>
-      <c r="AI46" s="225">
+      <c r="AI46" s="210">
         <f>SUM(AI32-Z46)</f>
         <v/>
       </c>
-      <c r="AJ46" s="225">
+      <c r="AJ46" s="210">
         <f>SUM(AJ32-AA46)</f>
         <v/>
       </c>
-      <c r="AK46" s="225">
+      <c r="AK46" s="210">
         <f>SUM(AK32-AB46)</f>
         <v/>
       </c>
-      <c r="AL46" s="225">
+      <c r="AL46" s="210">
         <f>SUM(AL32-AC46)</f>
         <v/>
       </c>
-      <c r="AM46" s="225">
+      <c r="AM46" s="210">
         <f>SUM(AM32-AD46)</f>
         <v/>
       </c>
-      <c r="AN46" s="225">
+      <c r="AN46" s="210">
         <f>SUM(AN32-AE46)</f>
         <v/>
       </c>
-      <c r="AO46" s="226">
+      <c r="AO46" s="211">
         <f>SUM(AO32-AF46)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>ESCO #2</t>
         </is>
       </c>
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C47" s="201" t="n"/>
-      <c r="D47" s="202" t="n"/>
-      <c r="E47" s="202" t="n"/>
-      <c r="F47" s="202" t="n"/>
-      <c r="G47" s="202" t="n"/>
-      <c r="H47" s="202" t="n"/>
-      <c r="I47" s="202" t="n"/>
-      <c r="J47" s="202" t="n"/>
-      <c r="K47" s="203" t="n"/>
-      <c r="L47" s="224">
+      <c r="C47" s="121" t="n"/>
+      <c r="D47" s="122" t="n"/>
+      <c r="E47" s="122" t="n"/>
+      <c r="F47" s="122" t="n"/>
+      <c r="G47" s="122" t="n"/>
+      <c r="H47" s="122" t="n"/>
+      <c r="I47" s="122" t="n"/>
+      <c r="J47" s="122" t="n"/>
+      <c r="K47" s="123" t="n"/>
+      <c r="L47" s="209">
         <f>SUM(L33-C47)</f>
         <v/>
       </c>
-      <c r="M47" s="225">
+      <c r="M47" s="210">
         <f>SUM(M33-D47)</f>
         <v/>
       </c>
-      <c r="N47" s="225">
+      <c r="N47" s="210">
         <f>SUM(N33-E47)</f>
         <v/>
       </c>
-      <c r="O47" s="225">
+      <c r="O47" s="210">
         <f>SUM(O33-F47)</f>
         <v/>
       </c>
-      <c r="P47" s="225">
+      <c r="P47" s="210">
         <f>SUM(P33-G47)</f>
         <v/>
       </c>
-      <c r="Q47" s="225">
+      <c r="Q47" s="210">
         <f>SUM(Q33-H47)</f>
         <v/>
       </c>
-      <c r="R47" s="225">
+      <c r="R47" s="210">
         <f>SUM(R33-I47)</f>
         <v/>
       </c>
-      <c r="S47" s="225">
+      <c r="S47" s="210">
         <f>SUM(S33-J47)</f>
         <v/>
       </c>
-      <c r="T47" s="226">
+      <c r="T47" s="211">
         <f>SUM(T33-K47)</f>
         <v/>
       </c>
-      <c r="V47" s="23" t="inlineStr">
+      <c r="V47" s="16" t="inlineStr">
         <is>
           <t>LCIT</t>
         </is>
       </c>
-      <c r="W47" s="24" t="inlineStr">
+      <c r="W47" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X47" s="227" t="n"/>
-      <c r="Y47" s="228" t="n"/>
-      <c r="Z47" s="228" t="n"/>
-      <c r="AA47" s="228" t="n"/>
-      <c r="AB47" s="228" t="n"/>
-      <c r="AC47" s="228" t="n"/>
-      <c r="AD47" s="228" t="n"/>
-      <c r="AE47" s="228" t="n"/>
-      <c r="AF47" s="229" t="n"/>
-      <c r="AG47" s="224">
+      <c r="X47" s="143" t="n"/>
+      <c r="Y47" s="144" t="n"/>
+      <c r="Z47" s="144" t="n"/>
+      <c r="AA47" s="144" t="n"/>
+      <c r="AB47" s="144" t="n"/>
+      <c r="AC47" s="144" t="n"/>
+      <c r="AD47" s="144" t="n"/>
+      <c r="AE47" s="144" t="n"/>
+      <c r="AF47" s="145" t="n"/>
+      <c r="AG47" s="209">
         <f>SUM(AG33-X47)</f>
         <v/>
       </c>
-      <c r="AH47" s="225">
+      <c r="AH47" s="210">
         <f>SUM(AH33-Y47)</f>
         <v/>
       </c>
-      <c r="AI47" s="225">
+      <c r="AI47" s="210">
         <f>SUM(AI33-Z47)</f>
         <v/>
       </c>
-      <c r="AJ47" s="225">
+      <c r="AJ47" s="210">
         <f>SUM(AJ33-AA47)</f>
         <v/>
       </c>
-      <c r="AK47" s="225">
+      <c r="AK47" s="210">
         <f>SUM(AK33-AB47)</f>
         <v/>
       </c>
-      <c r="AL47" s="225">
+      <c r="AL47" s="210">
         <f>SUM(AL33-AC47)</f>
         <v/>
       </c>
-      <c r="AM47" s="225">
+      <c r="AM47" s="210">
         <f>SUM(AM33-AD47)</f>
         <v/>
       </c>
-      <c r="AN47" s="225">
+      <c r="AN47" s="210">
         <f>SUM(AN33-AE47)</f>
         <v/>
       </c>
-      <c r="AO47" s="226">
+      <c r="AO47" s="211">
         <f>SUM(AO33-AF47)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="136" t="inlineStr">
+      <c r="A48" s="111" t="inlineStr">
         <is>
           <t>BMTP</t>
         </is>
       </c>
-      <c r="B48" s="137" t="inlineStr">
+      <c r="B48" s="112" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C48" s="227" t="n"/>
-      <c r="D48" s="228" t="n"/>
-      <c r="E48" s="228" t="n"/>
-      <c r="F48" s="228" t="n"/>
-      <c r="G48" s="228" t="n"/>
-      <c r="H48" s="228" t="n"/>
-      <c r="I48" s="228" t="n"/>
-      <c r="J48" s="228" t="n"/>
-      <c r="K48" s="229" t="n"/>
-      <c r="L48" s="224">
+      <c r="C48" s="143" t="n"/>
+      <c r="D48" s="144" t="n"/>
+      <c r="E48" s="144" t="n"/>
+      <c r="F48" s="144" t="n"/>
+      <c r="G48" s="144" t="n"/>
+      <c r="H48" s="144" t="n"/>
+      <c r="I48" s="144" t="n"/>
+      <c r="J48" s="144" t="n"/>
+      <c r="K48" s="145" t="n"/>
+      <c r="L48" s="209">
         <f>SUM(L34-C48)</f>
         <v/>
       </c>
-      <c r="M48" s="225">
+      <c r="M48" s="210">
         <f>SUM(M34-D48)</f>
         <v/>
       </c>
-      <c r="N48" s="225">
+      <c r="N48" s="210">
         <f>SUM(N34-E48)</f>
         <v/>
       </c>
-      <c r="O48" s="225">
+      <c r="O48" s="210">
         <f>SUM(O34-F48)</f>
         <v/>
       </c>
-      <c r="P48" s="225">
+      <c r="P48" s="210">
         <f>SUM(P34-G48)</f>
         <v/>
       </c>
-      <c r="Q48" s="225">
+      <c r="Q48" s="210">
         <f>SUM(Q34-H48)</f>
         <v/>
       </c>
-      <c r="R48" s="225">
+      <c r="R48" s="210">
         <f>SUM(R34-I48)</f>
         <v/>
       </c>
-      <c r="S48" s="225">
+      <c r="S48" s="210">
         <f>SUM(S34-J48)</f>
         <v/>
       </c>
-      <c r="T48" s="226">
+      <c r="T48" s="211">
         <f>SUM(T34-K48)</f>
         <v/>
       </c>
-      <c r="V48" s="23" t="inlineStr">
+      <c r="V48" s="16" t="inlineStr">
         <is>
           <t>HPT</t>
         </is>
       </c>
-      <c r="W48" s="24" t="inlineStr">
+      <c r="W48" s="17" t="inlineStr">
         <is>
           <t>TERMINAL</t>
         </is>
       </c>
-      <c r="X48" s="227" t="n"/>
-      <c r="Y48" s="228" t="n"/>
-      <c r="Z48" s="228" t="n"/>
-      <c r="AA48" s="228" t="n"/>
-      <c r="AB48" s="228" t="n"/>
-      <c r="AC48" s="228" t="n"/>
-      <c r="AD48" s="228" t="n"/>
-      <c r="AE48" s="228" t="n"/>
-      <c r="AF48" s="229" t="n"/>
-      <c r="AG48" s="224">
+      <c r="X48" s="143" t="n"/>
+      <c r="Y48" s="144" t="n"/>
+      <c r="Z48" s="144" t="n"/>
+      <c r="AA48" s="144" t="n"/>
+      <c r="AB48" s="144" t="n"/>
+      <c r="AC48" s="144" t="n"/>
+      <c r="AD48" s="144" t="n"/>
+      <c r="AE48" s="144" t="n"/>
+      <c r="AF48" s="145" t="n"/>
+      <c r="AG48" s="209">
         <f>SUM(AG34-X48)</f>
         <v/>
       </c>
-      <c r="AH48" s="225">
+      <c r="AH48" s="210">
         <f>SUM(AH34-Y48)</f>
         <v/>
       </c>
-      <c r="AI48" s="225">
+      <c r="AI48" s="210">
         <f>SUM(AI34-Z48)</f>
         <v/>
       </c>
-      <c r="AJ48" s="225">
+      <c r="AJ48" s="210">
         <f>SUM(AJ34-AA48)</f>
         <v/>
       </c>
-      <c r="AK48" s="225">
+      <c r="AK48" s="210">
         <f>SUM(AK34-AB48)</f>
         <v/>
       </c>
-      <c r="AL48" s="225">
+      <c r="AL48" s="210">
         <f>SUM(AL34-AC48)</f>
         <v/>
       </c>
-      <c r="AM48" s="225">
+      <c r="AM48" s="210">
         <f>SUM(AM34-AD48)</f>
         <v/>
       </c>
-      <c r="AN48" s="225">
+      <c r="AN48" s="210">
         <f>SUM(AN34-AE48)</f>
         <v/>
       </c>
-      <c r="AO48" s="226">
+      <c r="AO48" s="211">
         <f>SUM(AO34-AF48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C49" s="230" t="n">
+      <c r="C49" s="146" t="n">
         <v>87</v>
       </c>
-      <c r="D49" s="210" t="n"/>
-      <c r="E49" s="210" t="n">
+      <c r="D49" s="130" t="n"/>
+      <c r="E49" s="130" t="n">
         <v>57</v>
       </c>
-      <c r="F49" s="210" t="n"/>
-      <c r="G49" s="210" t="n"/>
-      <c r="H49" s="210" t="n"/>
-      <c r="I49" s="210" t="n"/>
-      <c r="J49" s="210" t="n"/>
-      <c r="K49" s="231" t="n"/>
-      <c r="L49" s="232">
+      <c r="F49" s="130" t="n"/>
+      <c r="G49" s="130" t="n"/>
+      <c r="H49" s="130" t="n"/>
+      <c r="I49" s="130" t="n"/>
+      <c r="J49" s="130" t="n"/>
+      <c r="K49" s="147" t="n"/>
+      <c r="L49" s="212">
         <f>SUM(L35-C49)</f>
         <v/>
       </c>
-      <c r="M49" s="233">
+      <c r="M49" s="213">
         <f>SUM(M35-D49)</f>
         <v/>
       </c>
-      <c r="N49" s="233">
+      <c r="N49" s="213">
         <f>SUM(N35-E49)</f>
         <v/>
       </c>
-      <c r="O49" s="233">
+      <c r="O49" s="213">
         <f>SUM(O35-F49)</f>
         <v/>
       </c>
-      <c r="P49" s="233">
+      <c r="P49" s="213">
         <f>SUM(P35-G49)</f>
         <v/>
       </c>
-      <c r="Q49" s="233">
+      <c r="Q49" s="213">
         <f>SUM(Q35-H49)</f>
         <v/>
       </c>
-      <c r="R49" s="233">
+      <c r="R49" s="213">
         <f>SUM(R35-I49)</f>
         <v/>
       </c>
-      <c r="S49" s="233">
+      <c r="S49" s="213">
         <f>SUM(S35-J49)</f>
         <v/>
       </c>
-      <c r="T49" s="234">
+      <c r="T49" s="214">
         <f>SUM(T35-K49)</f>
         <v/>
       </c>
-      <c r="V49" s="35" t="inlineStr">
+      <c r="V49" s="26" t="inlineStr">
         <is>
           <t>HAST</t>
         </is>
       </c>
-      <c r="W49" s="36" t="inlineStr">
+      <c r="W49" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X49" s="230" t="n">
+      <c r="X49" s="146" t="n">
         <v>79</v>
       </c>
-      <c r="Y49" s="210" t="n"/>
-      <c r="Z49" s="210" t="n">
+      <c r="Y49" s="130" t="n"/>
+      <c r="Z49" s="130" t="n">
         <v>70</v>
       </c>
-      <c r="AA49" s="210" t="n">
+      <c r="AA49" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="AB49" s="210" t="n">
+      <c r="AB49" s="130" t="n">
         <v>7</v>
       </c>
-      <c r="AC49" s="210" t="n"/>
-      <c r="AD49" s="210" t="n"/>
-      <c r="AE49" s="210" t="n"/>
-      <c r="AF49" s="231" t="n"/>
-      <c r="AG49" s="232">
+      <c r="AC49" s="130" t="n"/>
+      <c r="AD49" s="130" t="n"/>
+      <c r="AE49" s="130" t="n"/>
+      <c r="AF49" s="147" t="n"/>
+      <c r="AG49" s="212">
         <f>SUM(AG35-X49)</f>
         <v/>
       </c>
-      <c r="AH49" s="233">
+      <c r="AH49" s="213">
         <f>SUM(AH35-Y49)</f>
         <v/>
       </c>
-      <c r="AI49" s="233">
+      <c r="AI49" s="213">
         <f>SUM(AI35-Z49)</f>
         <v/>
       </c>
-      <c r="AJ49" s="233">
+      <c r="AJ49" s="213">
         <f>SUM(AJ35-AA49)</f>
         <v/>
       </c>
-      <c r="AK49" s="233">
+      <c r="AK49" s="213">
         <f>SUM(AK35-AB49)</f>
         <v/>
       </c>
-      <c r="AL49" s="233">
+      <c r="AL49" s="213">
         <f>SUM(AL35-AC49)</f>
         <v/>
       </c>
-      <c r="AM49" s="233">
+      <c r="AM49" s="213">
         <f>SUM(AM35-AD49)</f>
         <v/>
       </c>
-      <c r="AN49" s="233">
+      <c r="AN49" s="213">
         <f>SUM(AN35-AE49)</f>
         <v/>
       </c>
-      <c r="AO49" s="234">
+      <c r="AO49" s="214">
         <f>SUM(AO35-AF49)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>BC2</t>
         </is>
       </c>
-      <c r="B50" s="44" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C50" s="230" t="n">
+      <c r="C50" s="146" t="n">
         <v>99</v>
       </c>
-      <c r="D50" s="210" t="n"/>
-      <c r="E50" s="210" t="n">
+      <c r="D50" s="130" t="n"/>
+      <c r="E50" s="130" t="n">
         <v>96</v>
       </c>
-      <c r="F50" s="210" t="n">
+      <c r="F50" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="210" t="n">
+      <c r="G50" s="130" t="n">
         <v>24</v>
       </c>
-      <c r="H50" s="210" t="n"/>
-      <c r="I50" s="210" t="n"/>
-      <c r="J50" s="210" t="n"/>
-      <c r="K50" s="231" t="n"/>
-      <c r="L50" s="232">
+      <c r="H50" s="130" t="n"/>
+      <c r="I50" s="130" t="n"/>
+      <c r="J50" s="130" t="n"/>
+      <c r="K50" s="147" t="n"/>
+      <c r="L50" s="212">
         <f>SUM(L36-C50)</f>
         <v/>
       </c>
-      <c r="M50" s="233">
+      <c r="M50" s="213">
         <f>SUM(M36-D50)</f>
         <v/>
       </c>
-      <c r="N50" s="233">
+      <c r="N50" s="213">
         <f>SUM(N36-E50)</f>
         <v/>
       </c>
-      <c r="O50" s="233">
+      <c r="O50" s="213">
         <f>SUM(O36-F50)</f>
         <v/>
       </c>
-      <c r="P50" s="242">
+      <c r="P50" s="221">
         <f>SUM(P36-G50)</f>
         <v/>
       </c>
-      <c r="Q50" s="233">
+      <c r="Q50" s="213">
         <f>SUM(Q36-H50)</f>
         <v/>
       </c>
-      <c r="R50" s="233">
+      <c r="R50" s="213">
         <f>SUM(R36-I50)</f>
         <v/>
       </c>
-      <c r="S50" s="233">
+      <c r="S50" s="213">
         <f>SUM(S36-J50)</f>
         <v/>
       </c>
-      <c r="T50" s="234">
+      <c r="T50" s="214">
         <f>SUM(T36-K50)</f>
         <v/>
       </c>
-      <c r="V50" s="35" t="inlineStr">
+      <c r="V50" s="26" t="inlineStr">
         <is>
           <t>CELLO</t>
         </is>
       </c>
-      <c r="W50" s="36" t="inlineStr">
+      <c r="W50" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X50" s="230" t="n">
+      <c r="X50" s="146" t="n">
         <v>8</v>
       </c>
-      <c r="Y50" s="210" t="n"/>
-      <c r="Z50" s="210" t="n">
+      <c r="Y50" s="130" t="n"/>
+      <c r="Z50" s="130" t="n">
         <v>50</v>
       </c>
-      <c r="AA50" s="210" t="n"/>
-      <c r="AB50" s="210" t="n"/>
-      <c r="AC50" s="210" t="n"/>
-      <c r="AD50" s="210" t="n"/>
-      <c r="AE50" s="210" t="n"/>
-      <c r="AF50" s="231" t="n"/>
-      <c r="AG50" s="232">
+      <c r="AA50" s="130" t="n"/>
+      <c r="AB50" s="130" t="n"/>
+      <c r="AC50" s="130" t="n"/>
+      <c r="AD50" s="130" t="n"/>
+      <c r="AE50" s="130" t="n"/>
+      <c r="AF50" s="147" t="n"/>
+      <c r="AG50" s="212">
         <f>SUM(AG36-X50)</f>
         <v/>
       </c>
-      <c r="AH50" s="233">
+      <c r="AH50" s="213">
         <f>SUM(AH36-Y50)</f>
         <v/>
       </c>
-      <c r="AI50" s="242">
+      <c r="AI50" s="221">
         <f>SUM(AI36-Z50)</f>
         <v/>
       </c>
-      <c r="AJ50" s="233">
+      <c r="AJ50" s="213">
         <f>SUM(AJ36-AA50)</f>
         <v/>
       </c>
-      <c r="AK50" s="233">
+      <c r="AK50" s="213">
         <f>SUM(AK36-AB50)</f>
         <v/>
       </c>
-      <c r="AL50" s="233">
+      <c r="AL50" s="213">
         <f>SUM(AL36-AC50)</f>
         <v/>
       </c>
-      <c r="AM50" s="233">
+      <c r="AM50" s="213">
         <f>SUM(AM36-AD50)</f>
         <v/>
       </c>
-      <c r="AN50" s="233">
+      <c r="AN50" s="213">
         <f>SUM(AN36-AE50)</f>
         <v/>
       </c>
-      <c r="AO50" s="234">
+      <c r="AO50" s="214">
         <f>SUM(AO36-AF50)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="43" t="n"/>
-      <c r="B51" s="44" t="n"/>
-      <c r="C51" s="41" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n"/>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="28" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="28" t="n"/>
-      <c r="K51" s="42" t="n"/>
-      <c r="L51" s="235">
+      <c r="A51" s="34" t="n"/>
+      <c r="B51" s="35" t="n"/>
+      <c r="C51" s="32" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
+      <c r="J51" s="21" t="n"/>
+      <c r="K51" s="33" t="n"/>
+      <c r="L51" s="215">
         <f>SUM(L37-C51)</f>
         <v/>
       </c>
-      <c r="M51" s="236">
+      <c r="M51" s="216">
         <f>SUM(M37-D51)</f>
         <v/>
       </c>
-      <c r="N51" s="236">
+      <c r="N51" s="216">
         <f>SUM(N37-E51)</f>
         <v/>
       </c>
-      <c r="O51" s="236">
+      <c r="O51" s="216">
         <f>SUM(O37-F51)</f>
         <v/>
       </c>
-      <c r="P51" s="236">
+      <c r="P51" s="216">
         <f>SUM(P37-G51)</f>
         <v/>
       </c>
-      <c r="Q51" s="236">
+      <c r="Q51" s="216">
         <f>SUM(Q37-H51)</f>
         <v/>
       </c>
-      <c r="R51" s="236">
+      <c r="R51" s="216">
         <f>SUM(R37-I51)</f>
         <v/>
       </c>
-      <c r="S51" s="236">
+      <c r="S51" s="216">
         <f>SUM(S37-J51)</f>
         <v/>
       </c>
-      <c r="T51" s="237">
+      <c r="T51" s="217">
         <f>SUM(T37-K51)</f>
         <v/>
       </c>
-      <c r="V51" s="35" t="inlineStr">
+      <c r="V51" s="26" t="inlineStr">
         <is>
           <t>PW</t>
         </is>
       </c>
-      <c r="W51" s="36" t="inlineStr">
+      <c r="W51" s="27" t="inlineStr">
         <is>
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X51" s="230" t="n">
+      <c r="X51" s="146" t="n">
         <v>174</v>
       </c>
-      <c r="Y51" s="210" t="n"/>
-      <c r="Z51" s="210" t="n">
+      <c r="Y51" s="130" t="n"/>
+      <c r="Z51" s="130" t="n">
         <v>98</v>
       </c>
-      <c r="AA51" s="210" t="n"/>
-      <c r="AB51" s="210" t="n"/>
-      <c r="AC51" s="210" t="n"/>
-      <c r="AD51" s="210" t="n"/>
-      <c r="AE51" s="210" t="n"/>
-      <c r="AF51" s="231" t="n"/>
-      <c r="AG51" s="232">
+      <c r="AA51" s="130" t="n"/>
+      <c r="AB51" s="130" t="n"/>
+      <c r="AC51" s="130" t="n"/>
+      <c r="AD51" s="130" t="n"/>
+      <c r="AE51" s="130" t="n"/>
+      <c r="AF51" s="147" t="n"/>
+      <c r="AG51" s="212">
         <f>SUM(AG37-X51)</f>
         <v/>
       </c>
-      <c r="AH51" s="233">
+      <c r="AH51" s="213">
         <f>SUM(AH37-Y51)</f>
         <v/>
       </c>
-      <c r="AI51" s="233">
+      <c r="AI51" s="213">
         <f>SUM(AI37-Z51)</f>
         <v/>
       </c>
-      <c r="AJ51" s="233">
+      <c r="AJ51" s="213">
         <f>SUM(AJ37-AA51)</f>
         <v/>
       </c>
-      <c r="AK51" s="233">
+      <c r="AK51" s="213">
         <f>SUM(AK37-AB51)</f>
         <v/>
       </c>
-      <c r="AL51" s="233">
+      <c r="AL51" s="213">
         <f>SUM(AL37-AC51)</f>
         <v/>
       </c>
-      <c r="AM51" s="233">
+      <c r="AM51" s="213">
         <f>SUM(AM37-AD51)</f>
         <v/>
       </c>
-      <c r="AN51" s="233">
+      <c r="AN51" s="213">
         <f>SUM(AN37-AE51)</f>
         <v/>
       </c>
-      <c r="AO51" s="234">
+      <c r="AO51" s="214">
         <f>SUM(AO37-AF51)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="43" t="n"/>
-      <c r="B52" s="44" t="n"/>
-      <c r="C52" s="41" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
-      <c r="G52" s="28" t="n"/>
-      <c r="H52" s="28" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="42" t="n"/>
-      <c r="L52" s="235">
+      <c r="A52" s="34" t="n"/>
+      <c r="B52" s="35" t="n"/>
+      <c r="C52" s="32" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+      <c r="J52" s="21" t="n"/>
+      <c r="K52" s="33" t="n"/>
+      <c r="L52" s="215">
         <f>SUM(L38-C52)</f>
         <v/>
       </c>
-      <c r="M52" s="236">
+      <c r="M52" s="216">
         <f>SUM(M38-D52)</f>
         <v/>
       </c>
-      <c r="N52" s="236">
+      <c r="N52" s="216">
         <f>SUM(N38-E52)</f>
         <v/>
       </c>
-      <c r="O52" s="236">
+      <c r="O52" s="216">
         <f>SUM(O38-F52)</f>
         <v/>
       </c>
-      <c r="P52" s="236">
+      <c r="P52" s="216">
         <f>SUM(P38-G52)</f>
         <v/>
       </c>
-      <c r="Q52" s="236">
+      <c r="Q52" s="216">
         <f>SUM(Q38-H52)</f>
         <v/>
       </c>
-      <c r="R52" s="236">
+      <c r="R52" s="216">
         <f>SUM(R38-I52)</f>
         <v/>
       </c>
-      <c r="S52" s="236">
+      <c r="S52" s="216">
         <f>SUM(S38-J52)</f>
         <v/>
       </c>
-      <c r="T52" s="237">
+      <c r="T52" s="217">
         <f>SUM(T38-K52)</f>
         <v/>
       </c>
-      <c r="V52" s="35" t="n"/>
-      <c r="W52" s="36" t="n"/>
-      <c r="X52" s="48" t="n"/>
-      <c r="Y52" s="49" t="n"/>
-      <c r="Z52" s="49" t="n"/>
-      <c r="AA52" s="49" t="n"/>
-      <c r="AB52" s="49" t="n"/>
-      <c r="AC52" s="49" t="n"/>
-      <c r="AD52" s="49" t="n"/>
-      <c r="AE52" s="49" t="n"/>
-      <c r="AF52" s="82" t="n"/>
-      <c r="AG52" s="235">
+      <c r="V52" s="26" t="n"/>
+      <c r="W52" s="27" t="n"/>
+      <c r="X52" s="39" t="n"/>
+      <c r="Y52" s="40" t="n"/>
+      <c r="Z52" s="40" t="n"/>
+      <c r="AA52" s="40" t="n"/>
+      <c r="AB52" s="40" t="n"/>
+      <c r="AC52" s="40" t="n"/>
+      <c r="AD52" s="40" t="n"/>
+      <c r="AE52" s="40" t="n"/>
+      <c r="AF52" s="65" t="n"/>
+      <c r="AG52" s="215">
         <f>SUM(AG38-X52)</f>
         <v/>
       </c>
-      <c r="AH52" s="236">
+      <c r="AH52" s="216">
         <f>SUM(AH38-Y52)</f>
         <v/>
       </c>
-      <c r="AI52" s="236">
+      <c r="AI52" s="216">
         <f>SUM(AI38-Z52)</f>
         <v/>
       </c>
-      <c r="AJ52" s="236">
+      <c r="AJ52" s="216">
         <f>SUM(AJ38-AA52)</f>
         <v/>
       </c>
-      <c r="AK52" s="236">
+      <c r="AK52" s="216">
         <f>SUM(AK38-AB52)</f>
         <v/>
       </c>
-      <c r="AL52" s="236">
+      <c r="AL52" s="216">
         <f>SUM(AL38-AC52)</f>
         <v/>
       </c>
-      <c r="AM52" s="236">
+      <c r="AM52" s="216">
         <f>SUM(AM38-AD52)</f>
         <v/>
       </c>
-      <c r="AN52" s="236">
+      <c r="AN52" s="216">
         <f>SUM(AN38-AE52)</f>
         <v/>
       </c>
-      <c r="AO52" s="237">
+      <c r="AO52" s="217">
         <f>SUM(AO38-AF52)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="43" t="n"/>
-      <c r="B53" s="44" t="n"/>
-      <c r="C53" s="41" t="n"/>
-      <c r="D53" s="28" t="n"/>
-      <c r="E53" s="28" t="n"/>
-      <c r="F53" s="28" t="n"/>
-      <c r="G53" s="28" t="n"/>
-      <c r="H53" s="28" t="n"/>
-      <c r="I53" s="28" t="n"/>
-      <c r="J53" s="28" t="n"/>
-      <c r="K53" s="42" t="n"/>
-      <c r="L53" s="235">
+      <c r="A53" s="34" t="n"/>
+      <c r="B53" s="35" t="n"/>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="21" t="n"/>
+      <c r="I53" s="21" t="n"/>
+      <c r="J53" s="21" t="n"/>
+      <c r="K53" s="33" t="n"/>
+      <c r="L53" s="215">
         <f>SUM(L39-C53)</f>
         <v/>
       </c>
-      <c r="M53" s="236">
+      <c r="M53" s="216">
         <f>SUM(M39-D53)</f>
         <v/>
       </c>
-      <c r="N53" s="236">
+      <c r="N53" s="216">
         <f>SUM(N39-E53)</f>
         <v/>
       </c>
-      <c r="O53" s="236">
+      <c r="O53" s="216">
         <f>SUM(O39-F53)</f>
         <v/>
       </c>
-      <c r="P53" s="236">
+      <c r="P53" s="216">
         <f>SUM(P39-G53)</f>
         <v/>
       </c>
-      <c r="Q53" s="236">
+      <c r="Q53" s="216">
         <f>SUM(Q39-H53)</f>
         <v/>
       </c>
-      <c r="R53" s="236">
+      <c r="R53" s="216">
         <f>SUM(R39-I53)</f>
         <v/>
       </c>
-      <c r="S53" s="236">
+      <c r="S53" s="216">
         <f>SUM(S39-J53)</f>
         <v/>
       </c>
-      <c r="T53" s="237">
+      <c r="T53" s="217">
         <f>SUM(T39-K53)</f>
         <v/>
       </c>
-      <c r="V53" s="35" t="n"/>
-      <c r="W53" s="36" t="n"/>
-      <c r="X53" s="48" t="n"/>
-      <c r="Y53" s="49" t="n"/>
-      <c r="Z53" s="49" t="n"/>
-      <c r="AA53" s="49" t="n"/>
-      <c r="AB53" s="49" t="n"/>
-      <c r="AC53" s="49" t="n"/>
-      <c r="AD53" s="49" t="n"/>
-      <c r="AE53" s="49" t="n"/>
-      <c r="AF53" s="82" t="n"/>
-      <c r="AG53" s="235">
+      <c r="V53" s="26" t="n"/>
+      <c r="W53" s="27" t="n"/>
+      <c r="X53" s="39" t="n"/>
+      <c r="Y53" s="40" t="n"/>
+      <c r="Z53" s="40" t="n"/>
+      <c r="AA53" s="40" t="n"/>
+      <c r="AB53" s="40" t="n"/>
+      <c r="AC53" s="40" t="n"/>
+      <c r="AD53" s="40" t="n"/>
+      <c r="AE53" s="40" t="n"/>
+      <c r="AF53" s="65" t="n"/>
+      <c r="AG53" s="215">
         <f>SUM(AG39-X53)</f>
         <v/>
       </c>
-      <c r="AH53" s="236">
+      <c r="AH53" s="216">
         <f>SUM(AH39-Y53)</f>
         <v/>
       </c>
-      <c r="AI53" s="236">
+      <c r="AI53" s="216">
         <f>SUM(AI39-Z53)</f>
         <v/>
       </c>
-      <c r="AJ53" s="236">
+      <c r="AJ53" s="216">
         <f>SUM(AJ39-AA53)</f>
         <v/>
       </c>
-      <c r="AK53" s="236">
+      <c r="AK53" s="216">
         <f>SUM(AK39-AB53)</f>
         <v/>
       </c>
-      <c r="AL53" s="236">
+      <c r="AL53" s="216">
         <f>SUM(AL39-AC53)</f>
         <v/>
       </c>
-      <c r="AM53" s="236">
+      <c r="AM53" s="216">
         <f>SUM(AM39-AD53)</f>
         <v/>
       </c>
-      <c r="AN53" s="236">
+      <c r="AN53" s="216">
         <f>SUM(AN39-AE53)</f>
         <v/>
       </c>
-      <c r="AO53" s="237">
+      <c r="AO53" s="217">
         <f>SUM(AO39-AF53)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="45" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="B54" s="46" t="n"/>
-      <c r="C54" s="84" t="n"/>
-      <c r="D54" s="85" t="n"/>
-      <c r="E54" s="85" t="n"/>
-      <c r="F54" s="85" t="n"/>
-      <c r="G54" s="85" t="n"/>
-      <c r="H54" s="85" t="n"/>
-      <c r="I54" s="85" t="n"/>
-      <c r="J54" s="85" t="n"/>
-      <c r="K54" s="86" t="n"/>
-      <c r="L54" s="238">
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="66" t="n"/>
+      <c r="D54" s="67" t="n"/>
+      <c r="E54" s="67" t="n"/>
+      <c r="F54" s="67" t="n"/>
+      <c r="G54" s="67" t="n"/>
+      <c r="H54" s="67" t="n"/>
+      <c r="I54" s="67" t="n"/>
+      <c r="J54" s="67" t="n"/>
+      <c r="K54" s="68" t="n"/>
+      <c r="L54" s="218">
         <f>SUM(L40-C54)</f>
         <v/>
       </c>
-      <c r="M54" s="239">
+      <c r="M54" s="219">
         <f>SUM(M40-D54)</f>
         <v/>
       </c>
-      <c r="N54" s="239">
+      <c r="N54" s="219">
         <f>SUM(N40-E54)</f>
         <v/>
       </c>
-      <c r="O54" s="239">
+      <c r="O54" s="219">
         <f>SUM(O40-F54)</f>
         <v/>
       </c>
-      <c r="P54" s="239">
+      <c r="P54" s="219">
         <f>SUM(P40-G54)</f>
         <v/>
       </c>
-      <c r="Q54" s="239">
+      <c r="Q54" s="219">
         <f>SUM(Q40-H54)</f>
         <v/>
       </c>
-      <c r="R54" s="239">
+      <c r="R54" s="219">
         <f>SUM(R40-I54)</f>
         <v/>
       </c>
-      <c r="S54" s="239">
+      <c r="S54" s="219">
         <f>SUM(S40-J54)</f>
         <v/>
       </c>
-      <c r="T54" s="240">
+      <c r="T54" s="220">
         <f>SUM(T40-K54)</f>
         <v/>
       </c>
-      <c r="U54" s="89" t="n"/>
-      <c r="V54" s="45" t="inlineStr">
+      <c r="U54" s="70" t="n"/>
+      <c r="V54" s="36" t="inlineStr">
         <is>
           <t>LEASE IN</t>
         </is>
       </c>
-      <c r="W54" s="46" t="n"/>
-      <c r="X54" s="84" t="n"/>
-      <c r="Y54" s="85" t="n"/>
-      <c r="Z54" s="85" t="n"/>
-      <c r="AA54" s="85" t="n"/>
-      <c r="AB54" s="85" t="n"/>
-      <c r="AC54" s="85" t="n"/>
-      <c r="AD54" s="85" t="n"/>
-      <c r="AE54" s="85" t="n"/>
-      <c r="AF54" s="86" t="n"/>
-      <c r="AG54" s="235">
+      <c r="W54" s="37" t="n"/>
+      <c r="X54" s="66" t="n"/>
+      <c r="Y54" s="67" t="n"/>
+      <c r="Z54" s="67" t="n"/>
+      <c r="AA54" s="67" t="n"/>
+      <c r="AB54" s="67" t="n"/>
+      <c r="AC54" s="67" t="n"/>
+      <c r="AD54" s="67" t="n"/>
+      <c r="AE54" s="67" t="n"/>
+      <c r="AF54" s="68" t="n"/>
+      <c r="AG54" s="215">
         <f>SUM(AG40-X54)</f>
         <v/>
       </c>
-      <c r="AH54" s="236">
+      <c r="AH54" s="216">
         <f>SUM(AH40-Y54)</f>
         <v/>
       </c>
-      <c r="AI54" s="236">
+      <c r="AI54" s="216">
         <f>SUM(AI40-Z54)</f>
         <v/>
       </c>
-      <c r="AJ54" s="236">
+      <c r="AJ54" s="216">
         <f>SUM(AJ40-AA54)</f>
         <v/>
       </c>
-      <c r="AK54" s="236">
+      <c r="AK54" s="216">
         <f>SUM(AK40-AB54)</f>
         <v/>
       </c>
-      <c r="AL54" s="236">
+      <c r="AL54" s="216">
         <f>SUM(AL40-AC54)</f>
         <v/>
       </c>
-      <c r="AM54" s="236">
+      <c r="AM54" s="216">
         <f>SUM(AM40-AD54)</f>
         <v/>
       </c>
-      <c r="AN54" s="236">
+      <c r="AN54" s="216">
         <f>SUM(AN40-AE54)</f>
         <v/>
       </c>
-      <c r="AO54" s="237">
+      <c r="AO54" s="217">
         <f>SUM(AO40-AF54)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" thickBot="1">
-      <c r="A55" s="212" t="inlineStr">
+      <c r="A55" s="181" t="inlineStr">
         <is>
           <t>TOTAL AT BKK</t>
         </is>
       </c>
-      <c r="B55" s="213" t="n"/>
-      <c r="C55" s="70">
+      <c r="B55" s="182" t="n"/>
+      <c r="C55" s="61">
         <f>SUM(C45:C54)</f>
         <v/>
       </c>
-      <c r="D55" s="71">
+      <c r="D55" s="62">
         <f>SUM(D45:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="71">
+      <c r="E55" s="62">
         <f>SUM(E45:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="71">
+      <c r="F55" s="62">
         <f>SUM(F45:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="71">
+      <c r="G55" s="62">
         <f>SUM(G45:G54)</f>
         <v/>
       </c>
-      <c r="H55" s="71">
+      <c r="H55" s="62">
         <f>SUM(H45:H54)</f>
         <v/>
       </c>
-      <c r="I55" s="71">
+      <c r="I55" s="62">
         <f>SUM(I45:I54)</f>
         <v/>
       </c>
-      <c r="J55" s="71">
+      <c r="J55" s="62">
         <f>SUM(J45:J54)</f>
         <v/>
       </c>
-      <c r="K55" s="87">
+      <c r="K55" s="69">
         <f>SUM(K45:K54)</f>
         <v/>
       </c>
-      <c r="L55" s="57">
+      <c r="L55" s="48">
         <f>SUM(L45:L54)</f>
         <v/>
       </c>
-      <c r="M55" s="58">
+      <c r="M55" s="49">
         <f>SUM(M45:M54)</f>
         <v/>
       </c>
-      <c r="N55" s="58">
+      <c r="N55" s="49">
         <f>SUM(N45:N54)</f>
         <v/>
       </c>
-      <c r="O55" s="58">
+      <c r="O55" s="49">
         <f>SUM(O45:O54)</f>
         <v/>
       </c>
-      <c r="P55" s="58">
+      <c r="P55" s="49">
         <f>SUM(P45:P54)</f>
         <v/>
       </c>
-      <c r="Q55" s="58">
+      <c r="Q55" s="49">
         <f>SUM(Q45:Q54)</f>
         <v/>
       </c>
-      <c r="R55" s="58">
+      <c r="R55" s="49">
         <f>SUM(R45:R54)</f>
         <v/>
       </c>
-      <c r="S55" s="58">
+      <c r="S55" s="49">
         <f>SUM(S45:S54)</f>
         <v/>
       </c>
-      <c r="T55" s="59">
+      <c r="T55" s="50">
         <f>SUM(T45:T54)</f>
         <v/>
       </c>
       <c r="U55" s="9" t="n"/>
-      <c r="V55" s="212" t="inlineStr">
+      <c r="V55" s="181" t="inlineStr">
         <is>
           <t>TOTAL AT LCH</t>
         </is>
       </c>
-      <c r="W55" s="213" t="n"/>
-      <c r="X55" s="70">
+      <c r="W55" s="182" t="n"/>
+      <c r="X55" s="61">
         <f>SUM(X45:X54)</f>
         <v/>
       </c>
-      <c r="Y55" s="71">
+      <c r="Y55" s="62">
         <f>SUM(Y45:Y54)</f>
         <v/>
       </c>
-      <c r="Z55" s="71">
+      <c r="Z55" s="62">
         <f>SUM(Z45:Z54)</f>
         <v/>
       </c>
-      <c r="AA55" s="71">
+      <c r="AA55" s="62">
         <f>SUM(AA45:AA54)</f>
         <v/>
       </c>
-      <c r="AB55" s="71">
+      <c r="AB55" s="62">
         <f>SUM(AB45:AB54)</f>
         <v/>
       </c>
-      <c r="AC55" s="71">
+      <c r="AC55" s="62">
         <f>SUM(AC45:AC54)</f>
         <v/>
       </c>
-      <c r="AD55" s="71">
+      <c r="AD55" s="62">
         <f>SUM(AD45:AD54)</f>
         <v/>
       </c>
-      <c r="AE55" s="71">
+      <c r="AE55" s="62">
         <f>SUM(AE45:AE54)</f>
         <v/>
       </c>
-      <c r="AF55" s="87">
+      <c r="AF55" s="69">
         <f>SUM(AF45:AF54)</f>
         <v/>
       </c>
-      <c r="AG55" s="57">
+      <c r="AG55" s="48">
         <f>SUM(AG45:AG54)</f>
         <v/>
       </c>
-      <c r="AH55" s="58">
+      <c r="AH55" s="49">
         <f>SUM(AH45:AH54)</f>
         <v/>
       </c>
-      <c r="AI55" s="58">
+      <c r="AI55" s="49">
         <f>SUM(AI45:AI54)</f>
         <v/>
       </c>
-      <c r="AJ55" s="58">
+      <c r="AJ55" s="49">
         <f>SUM(AJ45:AJ54)</f>
         <v/>
       </c>
-      <c r="AK55" s="58">
+      <c r="AK55" s="49">
         <f>SUM(AK45:AK54)</f>
         <v/>
       </c>
-      <c r="AL55" s="58">
+      <c r="AL55" s="49">
         <f>SUM(AL45:AL54)</f>
         <v/>
       </c>
-      <c r="AM55" s="58">
+      <c r="AM55" s="49">
         <f>SUM(AM45:AM54)</f>
         <v/>
       </c>
-      <c r="AN55" s="58">
+      <c r="AN55" s="49">
         <f>SUM(AN45:AN54)</f>
         <v/>
       </c>
-      <c r="AO55" s="59">
+      <c r="AO55" s="50">
         <f>SUM(AO45:AO54)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16.9" customHeight="1">
-      <c r="A57" s="19" t="n"/>
+      <c r="A57" s="15" t="n"/>
       <c r="B57" s="171" t="n"/>
-      <c r="V57" s="89" t="n"/>
+      <c r="V57" s="70" t="n"/>
       <c r="W57" s="171" t="n"/>
     </row>
     <row r="58" ht="16.9" customHeight="1">
       <c r="B58" s="171" t="n"/>
-      <c r="V58" s="89" t="n"/>
+      <c r="V58" s="70" t="n"/>
       <c r="W58" s="171" t="n"/>
     </row>
     <row r="59" ht="16.9" customHeight="1">
-      <c r="B59" s="170" t="n"/>
-      <c r="W59" s="170" t="n"/>
+      <c r="B59" s="164" t="n"/>
+      <c r="W59" s="164" t="n"/>
     </row>
     <row r="60" ht="16.9" customHeight="1">
-      <c r="B60" s="170" t="n"/>
-      <c r="W60" s="170" t="n"/>
+      <c r="B60" s="164" t="n"/>
+      <c r="W60" s="164" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="46">
     <mergeCell ref="V55:W55"/>
     <mergeCell ref="W59:AO59"/>
+    <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="W58:AO58"/>
     <mergeCell ref="I43:K43"/>
@@ -7090,10 +6985,10 @@
     <mergeCell ref="V43:W44"/>
     <mergeCell ref="B59:T59"/>
     <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V2:W3"/>
+    <mergeCell ref="R2:T2"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="V2:W3"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="R2:T2"/>
     <mergeCell ref="B58:T58"/>
     <mergeCell ref="AG43:AO43"/>
     <mergeCell ref="V29:W30"/>
@@ -7193,13 +7088,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A28:W28 AP4:IV65536">
-    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="AD29">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD29">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="A28:W28 AP4:IV65536">
+    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7219,247 +7114,248 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.15" customHeight="1"/>
   <cols>
-    <col width="5.75" bestFit="1" customWidth="1" style="96" min="1" max="1"/>
-    <col width="7.875" customWidth="1" style="96" min="2" max="4"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="96" min="5" max="5"/>
-    <col width="5.75" bestFit="1" customWidth="1" style="96" min="6" max="6"/>
-    <col width="7.875" customWidth="1" style="96" min="7" max="9"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="96" min="10" max="13"/>
-    <col width="9" customWidth="1" style="96" min="14" max="16384"/>
+    <col width="5.75" bestFit="1" customWidth="1" style="76" min="1" max="1"/>
+    <col width="7.875" customWidth="1" style="76" min="2" max="4"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="76" min="5" max="5"/>
+    <col width="5.75" bestFit="1" customWidth="1" style="76" min="6" max="6"/>
+    <col width="7.875" customWidth="1" style="76" min="7" max="9"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="76" min="10" max="13"/>
+    <col width="9" customWidth="1" style="76" min="14" max="14"/>
+    <col width="9" customWidth="1" style="76" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1">
-      <c r="A1" s="172" t="inlineStr">
+      <c r="A1" s="189" t="inlineStr">
         <is>
           <t>HAL (THBKK)</t>
         </is>
       </c>
-      <c r="B1" s="243" t="n"/>
-      <c r="C1" s="243" t="n"/>
-      <c r="D1" s="244" t="n"/>
-      <c r="E1" s="116" t="n"/>
-      <c r="F1" s="172" t="inlineStr">
+      <c r="B1" s="190" t="n"/>
+      <c r="C1" s="190" t="n"/>
+      <c r="D1" s="191" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="189" t="inlineStr">
         <is>
           <t>HAL (THLCH)</t>
         </is>
       </c>
-      <c r="G1" s="243" t="n"/>
-      <c r="H1" s="243" t="n"/>
-      <c r="I1" s="244" t="n"/>
-      <c r="J1" s="117" t="n"/>
-      <c r="K1" s="117" t="n"/>
-      <c r="L1" s="117" t="n"/>
-      <c r="M1" s="117" t="n"/>
+      <c r="G1" s="190" t="n"/>
+      <c r="H1" s="190" t="n"/>
+      <c r="I1" s="191" t="n"/>
+      <c r="J1" s="92" t="n"/>
+      <c r="K1" s="92" t="n"/>
+      <c r="L1" s="92" t="n"/>
+      <c r="M1" s="92" t="n"/>
     </row>
     <row r="2" ht="16.15" customHeight="1">
-      <c r="A2" s="173" t="inlineStr">
+      <c r="A2" s="194" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="B2" s="172" t="inlineStr">
+      <c r="B2" s="189" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="C2" s="172" t="inlineStr">
+      <c r="C2" s="189" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="D2" s="172" t="inlineStr">
+      <c r="D2" s="189" t="inlineStr">
         <is>
           <t>TRMK</t>
         </is>
       </c>
-      <c r="E2" s="118" t="n"/>
-      <c r="F2" s="174" t="inlineStr">
+      <c r="E2" s="93" t="n"/>
+      <c r="F2" s="192" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="G2" s="172" t="inlineStr">
+      <c r="G2" s="189" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="H2" s="172" t="inlineStr">
+      <c r="H2" s="189" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="I2" s="172" t="inlineStr">
+      <c r="I2" s="189" t="inlineStr">
         <is>
           <t>TRMK</t>
         </is>
       </c>
-      <c r="J2" s="117" t="n"/>
-      <c r="K2" s="117" t="n"/>
-      <c r="L2" s="117" t="n"/>
-      <c r="M2" s="117" t="n"/>
+      <c r="J2" s="92" t="n"/>
+      <c r="K2" s="92" t="n"/>
+      <c r="L2" s="92" t="n"/>
+      <c r="M2" s="92" t="n"/>
     </row>
     <row r="3" ht="16.15" customHeight="1">
-      <c r="A3" s="245" t="n"/>
-      <c r="B3" s="175" t="inlineStr">
+      <c r="A3" s="193" t="n"/>
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="C3" s="175" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="D3" s="175" t="inlineStr">
+      <c r="D3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="E3" s="118" t="n"/>
-      <c r="F3" s="245" t="n"/>
-      <c r="G3" s="175" t="inlineStr">
+      <c r="E3" s="93" t="n"/>
+      <c r="F3" s="193" t="n"/>
+      <c r="G3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="H3" s="175" t="inlineStr">
+      <c r="H3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="I3" s="175" t="inlineStr">
+      <c r="I3" s="94" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="J3" s="120" t="n"/>
-      <c r="K3" s="120" t="n"/>
-      <c r="L3" s="120" t="n"/>
-      <c r="M3" s="120" t="n"/>
+      <c r="J3" s="95" t="n"/>
+      <c r="K3" s="95" t="n"/>
+      <c r="L3" s="95" t="n"/>
+      <c r="M3" s="95" t="n"/>
     </row>
     <row r="4" ht="16.15" customHeight="1">
-      <c r="A4" s="121" t="n">
+      <c r="A4" s="96" t="n">
         <v>2025</v>
       </c>
-      <c r="B4" s="122" t="n">
+      <c r="B4" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="n"/>
-      <c r="E4" s="118" t="n"/>
-      <c r="F4" s="122" t="n">
+      <c r="C4" s="97" t="n"/>
+      <c r="D4" s="97" t="n"/>
+      <c r="E4" s="93" t="n"/>
+      <c r="F4" s="97" t="n">
         <v>2025</v>
       </c>
-      <c r="G4" s="122" t="n">
+      <c r="G4" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="H4" s="122" t="n"/>
-      <c r="I4" s="122" t="n"/>
-      <c r="J4" s="120" t="n"/>
-      <c r="K4" s="120" t="n"/>
-      <c r="L4" s="120" t="n"/>
-      <c r="M4" s="120" t="n"/>
+      <c r="H4" s="97" t="n"/>
+      <c r="I4" s="97" t="n"/>
+      <c r="J4" s="95" t="n"/>
+      <c r="K4" s="95" t="n"/>
+      <c r="L4" s="95" t="n"/>
+      <c r="M4" s="95" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1">
-      <c r="A5" s="122" t="n">
+      <c r="A5" s="97" t="n">
         <v>2023</v>
       </c>
-      <c r="B5" s="123" t="n">
+      <c r="B5" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="123" t="n"/>
-      <c r="D5" s="123" t="n"/>
-      <c r="E5" s="118" t="n"/>
-      <c r="F5" s="122" t="n">
+      <c r="C5" s="98" t="n"/>
+      <c r="D5" s="98" t="n"/>
+      <c r="E5" s="93" t="n"/>
+      <c r="F5" s="97" t="n">
         <v>2023</v>
       </c>
-      <c r="G5" s="123" t="n">
+      <c r="G5" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="123" t="n"/>
-      <c r="I5" s="123" t="n"/>
-      <c r="J5" s="120" t="n"/>
-      <c r="K5" s="120" t="n"/>
-      <c r="L5" s="120" t="n"/>
-      <c r="M5" s="120" t="n"/>
+      <c r="H5" s="98" t="n"/>
+      <c r="I5" s="98" t="n"/>
+      <c r="J5" s="95" t="n"/>
+      <c r="K5" s="95" t="n"/>
+      <c r="L5" s="95" t="n"/>
+      <c r="M5" s="95" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1">
-      <c r="A6" s="122" t="n">
+      <c r="A6" s="97" t="n">
         <v>2021</v>
       </c>
-      <c r="B6" s="123" t="n">
+      <c r="B6" s="98" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="123" t="n"/>
-      <c r="D6" s="123" t="n"/>
-      <c r="E6" s="118" t="n"/>
-      <c r="F6" s="122" t="n">
+      <c r="C6" s="98" t="n"/>
+      <c r="D6" s="98" t="n"/>
+      <c r="E6" s="93" t="n"/>
+      <c r="F6" s="97" t="n">
         <v>2021</v>
       </c>
-      <c r="G6" s="123" t="n">
+      <c r="G6" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="123" t="n"/>
-      <c r="I6" s="123" t="n"/>
+      <c r="H6" s="98" t="n"/>
+      <c r="I6" s="98" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1">
-      <c r="A7" s="124" t="n">
+      <c r="A7" s="99" t="n">
         <v>2020</v>
       </c>
-      <c r="B7" s="125" t="n">
+      <c r="B7" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="125" t="n"/>
-      <c r="D7" s="125" t="n"/>
-      <c r="E7" s="111" t="n"/>
-      <c r="F7" s="124" t="n">
+      <c r="C7" s="100" t="n"/>
+      <c r="D7" s="100" t="n"/>
+      <c r="E7" s="87" t="n"/>
+      <c r="F7" s="99" t="n">
         <v>2020</v>
       </c>
-      <c r="G7" s="125" t="n">
+      <c r="G7" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="125" t="n"/>
+      <c r="H7" s="100" t="n"/>
+      <c r="I7" s="100" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
-      <c r="A8" s="126" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="127">
+      <c r="B8" s="102">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="127">
+      <c r="C8" s="102">
         <f>SUM(C4:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="127">
+      <c r="D8" s="102">
         <f>SUM(D4:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="128" t="n"/>
-      <c r="F8" s="126" t="inlineStr">
+      <c r="E8" s="103" t="n"/>
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G8" s="127">
+      <c r="G8" s="102">
         <f>SUM(G4:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="127">
+      <c r="H8" s="102">
         <f>SUM(H4:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="127">
+      <c r="I8" s="102">
         <f>SUM(I4:I7)</f>
         <v/>
       </c>
-      <c r="J8" s="129" t="n"/>
+      <c r="J8" s="104" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" thickTop="1"/>
   </sheetData>
@@ -7483,738 +7379,739 @@
   <dimension ref="B1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.75" defaultRowHeight="15.6" customHeight="1"/>
   <cols>
-    <col width="1.375" customWidth="1" style="114" min="1" max="1"/>
-    <col width="18.25" bestFit="1" customWidth="1" style="114" min="2" max="2"/>
-    <col width="5.75" customWidth="1" style="114" min="3" max="11"/>
-    <col width="18" customWidth="1" style="95" min="12" max="12"/>
-    <col width="1.375" customWidth="1" style="114" min="13" max="13"/>
-    <col width="8.75" customWidth="1" style="114" min="14" max="16384"/>
+    <col width="1.375" customWidth="1" style="89" min="1" max="1"/>
+    <col width="18.25" bestFit="1" customWidth="1" style="89" min="2" max="2"/>
+    <col width="5.75" customWidth="1" style="89" min="3" max="11"/>
+    <col width="18" customWidth="1" style="75" min="12" max="12"/>
+    <col width="1.375" customWidth="1" style="89" min="13" max="13"/>
+    <col width="8.75" customWidth="1" style="89" min="14" max="14"/>
+    <col width="8.75" customWidth="1" style="89" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B1" s="246" t="inlineStr">
+      <c r="B1" s="198" t="inlineStr">
         <is>
           <t>HAL (THBKK)</t>
         </is>
       </c>
-      <c r="C1" s="247" t="n"/>
-      <c r="D1" s="247" t="n"/>
-      <c r="E1" s="247" t="n"/>
-      <c r="F1" s="247" t="n"/>
-      <c r="G1" s="247" t="n"/>
-      <c r="H1" s="247" t="n"/>
-      <c r="I1" s="247" t="n"/>
-      <c r="J1" s="247" t="n"/>
-      <c r="K1" s="248" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+      <c r="J1" s="196" t="n"/>
+      <c r="K1" s="197" t="n"/>
     </row>
     <row r="2" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B2" s="97" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="78" t="inlineStr">
         <is>
           <t>22GP</t>
         </is>
       </c>
-      <c r="D2" s="99" t="inlineStr">
+      <c r="D2" s="79" t="inlineStr">
         <is>
           <t>42GP</t>
         </is>
       </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="E2" s="78" t="inlineStr">
         <is>
           <t>45GP</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
+      <c r="F2" s="78" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="G2" s="98" t="inlineStr">
+      <c r="G2" s="78" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="H2" s="98" t="inlineStr">
+      <c r="H2" s="78" t="inlineStr">
         <is>
           <t>22UT</t>
         </is>
       </c>
-      <c r="I2" s="98" t="inlineStr">
+      <c r="I2" s="78" t="inlineStr">
         <is>
           <t>42UT</t>
         </is>
       </c>
-      <c r="J2" s="98" t="inlineStr">
+      <c r="J2" s="78" t="inlineStr">
         <is>
           <t>22PC</t>
         </is>
       </c>
-      <c r="K2" s="98" t="inlineStr">
+      <c r="K2" s="78" t="inlineStr">
         <is>
           <t>42PC</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B3" s="100" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>Current Stock</t>
         </is>
       </c>
-      <c r="C3" s="101">
+      <c r="C3" s="81">
         <f>Daily!L15</f>
         <v/>
       </c>
-      <c r="D3" s="101">
+      <c r="D3" s="81">
         <f>Daily!M15</f>
         <v/>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="81">
         <f>Daily!N15</f>
         <v/>
       </c>
-      <c r="F3" s="101">
+      <c r="F3" s="81">
         <f>Daily!O15</f>
         <v/>
       </c>
-      <c r="G3" s="101">
+      <c r="G3" s="81">
         <f>Daily!P15</f>
         <v/>
       </c>
-      <c r="H3" s="101">
+      <c r="H3" s="81">
         <f>Daily!Q15</f>
         <v/>
       </c>
-      <c r="I3" s="101">
+      <c r="I3" s="81">
         <f>Daily!R15</f>
         <v/>
       </c>
-      <c r="J3" s="101">
+      <c r="J3" s="81">
         <f>Daily!S15</f>
         <v/>
       </c>
-      <c r="K3" s="101">
+      <c r="K3" s="81">
         <f>Daily!T15</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B4" s="100" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>E/P In (this week)</t>
         </is>
       </c>
-      <c r="C4" s="249">
+      <c r="C4" s="222">
         <f>Daily!L14</f>
         <v/>
       </c>
-      <c r="D4" s="249">
+      <c r="D4" s="222">
         <f>Daily!M14</f>
         <v/>
       </c>
-      <c r="E4" s="249">
+      <c r="E4" s="222">
         <f>Daily!N14</f>
         <v/>
       </c>
-      <c r="F4" s="249">
+      <c r="F4" s="222">
         <f>Daily!O14</f>
         <v/>
       </c>
-      <c r="G4" s="249">
+      <c r="G4" s="222">
         <f>Daily!P14</f>
         <v/>
       </c>
-      <c r="H4" s="249">
+      <c r="H4" s="222">
         <f>Daily!Q14</f>
         <v/>
       </c>
-      <c r="I4" s="249">
+      <c r="I4" s="222">
         <f>Daily!R14</f>
         <v/>
       </c>
-      <c r="J4" s="249">
+      <c r="J4" s="222">
         <f>Daily!S14</f>
         <v/>
       </c>
-      <c r="K4" s="249">
+      <c r="K4" s="222">
         <f>Daily!T14</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B5" s="102" t="n"/>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="103" t="n"/>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="103" t="n"/>
-      <c r="H5" s="103" t="n"/>
-      <c r="I5" s="103" t="n"/>
-      <c r="J5" s="103" t="n"/>
-      <c r="K5" s="103" t="n"/>
+      <c r="B5" s="82" t="n"/>
+      <c r="C5" s="83" t="n"/>
+      <c r="D5" s="83" t="n"/>
+      <c r="E5" s="83" t="n"/>
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="83" t="n"/>
+      <c r="H5" s="83" t="n"/>
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="83" t="n"/>
+      <c r="K5" s="83" t="n"/>
     </row>
     <row r="6" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B6" s="102" t="n"/>
-      <c r="C6" s="103" t="n"/>
-      <c r="D6" s="103" t="n"/>
-      <c r="E6" s="103" t="n"/>
-      <c r="F6" s="103" t="n"/>
-      <c r="G6" s="103" t="n"/>
-      <c r="H6" s="103" t="n"/>
-      <c r="I6" s="103" t="n"/>
-      <c r="J6" s="103" t="n"/>
-      <c r="K6" s="103" t="n"/>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="83" t="n"/>
+      <c r="D6" s="83" t="n"/>
+      <c r="E6" s="83" t="n"/>
+      <c r="F6" s="83" t="n"/>
+      <c r="G6" s="83" t="n"/>
+      <c r="H6" s="83" t="n"/>
+      <c r="I6" s="83" t="n"/>
+      <c r="J6" s="83" t="n"/>
+      <c r="K6" s="83" t="n"/>
     </row>
     <row r="7" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="104" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>INBOUND MT RETURN</t>
         </is>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="223">
         <f>Daily!C15</f>
         <v/>
       </c>
-      <c r="D7" s="250">
+      <c r="D7" s="223">
         <f>Daily!D15</f>
         <v/>
       </c>
-      <c r="E7" s="250">
+      <c r="E7" s="223">
         <f>Daily!E15</f>
         <v/>
       </c>
-      <c r="F7" s="250">
+      <c r="F7" s="223">
         <f>Daily!F15</f>
         <v/>
       </c>
-      <c r="G7" s="250">
+      <c r="G7" s="223">
         <f>Daily!G15</f>
         <v/>
       </c>
-      <c r="H7" s="250">
+      <c r="H7" s="223">
         <f>Daily!H15</f>
         <v/>
       </c>
-      <c r="I7" s="250">
+      <c r="I7" s="223">
         <f>Daily!I15</f>
         <v/>
       </c>
-      <c r="J7" s="250">
+      <c r="J7" s="223">
         <f>Daily!J15</f>
         <v/>
       </c>
-      <c r="K7" s="250">
+      <c r="K7" s="223">
         <f>Daily!K15</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B8" s="100" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>Booking(This week)</t>
         </is>
       </c>
-      <c r="C8" s="249">
+      <c r="C8" s="222">
         <f>Daily!C41</f>
         <v/>
       </c>
-      <c r="D8" s="249">
+      <c r="D8" s="222">
         <f>Daily!D41</f>
         <v/>
       </c>
-      <c r="E8" s="249">
+      <c r="E8" s="222">
         <f>Daily!E41</f>
         <v/>
       </c>
-      <c r="F8" s="249">
+      <c r="F8" s="222">
         <f>Daily!F41</f>
         <v/>
       </c>
-      <c r="G8" s="249">
+      <c r="G8" s="222">
         <f>Daily!G41</f>
         <v/>
       </c>
-      <c r="H8" s="249">
+      <c r="H8" s="222">
         <f>Daily!H41</f>
         <v/>
       </c>
-      <c r="I8" s="249">
+      <c r="I8" s="222">
         <f>Daily!I41</f>
         <v/>
       </c>
-      <c r="J8" s="249">
+      <c r="J8" s="222">
         <f>Daily!J41</f>
         <v/>
       </c>
-      <c r="K8" s="249">
+      <c r="K8" s="222">
         <f>Daily!K41</f>
         <v/>
       </c>
-      <c r="L8" s="95">
+      <c r="L8" s="75">
         <f>Daily!I29</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B9" s="100" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>Booking(Next week)</t>
         </is>
       </c>
-      <c r="C9" s="251">
+      <c r="C9" s="224">
         <f>Daily!C55</f>
         <v/>
       </c>
-      <c r="D9" s="251">
+      <c r="D9" s="224">
         <f>Daily!D55</f>
         <v/>
       </c>
-      <c r="E9" s="251">
+      <c r="E9" s="224">
         <f>Daily!E55</f>
         <v/>
       </c>
-      <c r="F9" s="251">
+      <c r="F9" s="224">
         <f>Daily!F55</f>
         <v/>
       </c>
-      <c r="G9" s="251">
+      <c r="G9" s="224">
         <f>Daily!G55</f>
         <v/>
       </c>
-      <c r="H9" s="251">
+      <c r="H9" s="224">
         <f>Daily!H55</f>
         <v/>
       </c>
-      <c r="I9" s="251">
+      <c r="I9" s="224">
         <f>Daily!I55</f>
         <v/>
       </c>
-      <c r="J9" s="251">
+      <c r="J9" s="224">
         <f>Daily!J55</f>
         <v/>
       </c>
-      <c r="K9" s="251">
+      <c r="K9" s="224">
         <f>Daily!K55</f>
         <v/>
       </c>
-      <c r="L9" s="107">
+      <c r="L9" s="85">
         <f>Daily!I43</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B10" s="108" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="C10" s="252">
+      <c r="C10" s="161">
         <f>SUM(C3+C4+C5+C6+C7-C8-C9)</f>
         <v/>
       </c>
-      <c r="D10" s="252">
+      <c r="D10" s="161">
         <f>SUM(D3+D4+D5+D6+D7-D8-D9)</f>
         <v/>
       </c>
-      <c r="E10" s="252">
+      <c r="E10" s="161">
         <f>SUM(E3+E4+E5+E6+E7-E8-E9)</f>
         <v/>
       </c>
-      <c r="F10" s="252">
+      <c r="F10" s="161">
         <f>SUM(F3+F4+F5+F6+F7-F8-F9)</f>
         <v/>
       </c>
-      <c r="G10" s="253">
+      <c r="G10" s="162">
         <f>SUM(G3+G4+G5+G6+G7-G8-G9)</f>
         <v/>
       </c>
-      <c r="H10" s="252">
+      <c r="H10" s="161">
         <f>SUM(H3+H4+H5+H6+H7-H8-H9)</f>
         <v/>
       </c>
-      <c r="I10" s="252">
+      <c r="I10" s="161">
         <f>SUM(I3+I4+I5+I6+I7-I8-I9)</f>
         <v/>
       </c>
-      <c r="J10" s="252">
+      <c r="J10" s="161">
         <f>SUM(J3+J4+J5+J6+J7-J8-J9)</f>
         <v/>
       </c>
-      <c r="K10" s="252">
+      <c r="K10" s="161">
         <f>SUM(K3+K4+K5+K6+K7-K8-K9)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="9.6" customHeight="1" thickBot="1">
-      <c r="B11" s="111" t="n"/>
-      <c r="C11" s="111" t="n"/>
-      <c r="D11" s="111" t="n"/>
-      <c r="E11" s="111" t="n"/>
-      <c r="F11" s="111" t="n"/>
-      <c r="G11" s="111" t="n"/>
-      <c r="H11" s="111" t="n"/>
-      <c r="I11" s="111" t="n"/>
-      <c r="J11" s="111" t="n"/>
-      <c r="K11" s="111" t="n"/>
+      <c r="B11" s="87" t="n"/>
+      <c r="C11" s="87" t="n"/>
+      <c r="D11" s="87" t="n"/>
+      <c r="E11" s="87" t="n"/>
+      <c r="F11" s="87" t="n"/>
+      <c r="G11" s="87" t="n"/>
+      <c r="H11" s="87" t="n"/>
+      <c r="I11" s="87" t="n"/>
+      <c r="J11" s="87" t="n"/>
+      <c r="K11" s="87" t="n"/>
     </row>
     <row r="12" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B12" s="254" t="inlineStr">
+      <c r="B12" s="195" t="inlineStr">
         <is>
           <t>HAL (THLCH)</t>
         </is>
       </c>
-      <c r="C12" s="247" t="n"/>
-      <c r="D12" s="247" t="n"/>
-      <c r="E12" s="247" t="n"/>
-      <c r="F12" s="247" t="n"/>
-      <c r="G12" s="247" t="n"/>
-      <c r="H12" s="247" t="n"/>
-      <c r="I12" s="247" t="n"/>
-      <c r="J12" s="247" t="n"/>
-      <c r="K12" s="248" t="n"/>
+      <c r="C12" s="196" t="n"/>
+      <c r="D12" s="196" t="n"/>
+      <c r="E12" s="196" t="n"/>
+      <c r="F12" s="196" t="n"/>
+      <c r="G12" s="196" t="n"/>
+      <c r="H12" s="196" t="n"/>
+      <c r="I12" s="196" t="n"/>
+      <c r="J12" s="196" t="n"/>
+      <c r="K12" s="197" t="n"/>
     </row>
     <row r="13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B13" s="97" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C13" s="98" t="inlineStr">
+      <c r="C13" s="78" t="inlineStr">
         <is>
           <t>22GP</t>
         </is>
       </c>
-      <c r="D13" s="98" t="inlineStr">
+      <c r="D13" s="78" t="inlineStr">
         <is>
           <t>42GP</t>
         </is>
       </c>
-      <c r="E13" s="98" t="inlineStr">
+      <c r="E13" s="78" t="inlineStr">
         <is>
           <t>45GP</t>
         </is>
       </c>
-      <c r="F13" s="98" t="inlineStr">
+      <c r="F13" s="78" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="G13" s="98" t="inlineStr">
+      <c r="G13" s="78" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
       </c>
-      <c r="H13" s="98" t="inlineStr">
+      <c r="H13" s="78" t="inlineStr">
         <is>
           <t>22UT</t>
         </is>
       </c>
-      <c r="I13" s="98" t="inlineStr">
+      <c r="I13" s="78" t="inlineStr">
         <is>
           <t>42UT</t>
         </is>
       </c>
-      <c r="J13" s="98" t="inlineStr">
+      <c r="J13" s="78" t="inlineStr">
         <is>
           <t>22PC</t>
         </is>
       </c>
-      <c r="K13" s="98" t="inlineStr">
+      <c r="K13" s="78" t="inlineStr">
         <is>
           <t>42PC</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B14" s="100" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>Current Stock</t>
         </is>
       </c>
-      <c r="C14" s="101">
+      <c r="C14" s="81">
         <f>Daily!AG15</f>
         <v/>
       </c>
-      <c r="D14" s="101">
+      <c r="D14" s="81">
         <f>Daily!AH15</f>
         <v/>
       </c>
-      <c r="E14" s="101">
+      <c r="E14" s="81">
         <f>Daily!AI15</f>
         <v/>
       </c>
-      <c r="F14" s="101">
+      <c r="F14" s="81">
         <f>Daily!AJ15</f>
         <v/>
       </c>
-      <c r="G14" s="101">
+      <c r="G14" s="81">
         <f>Daily!AK15</f>
         <v/>
       </c>
-      <c r="H14" s="101">
+      <c r="H14" s="81">
         <f>Daily!AL15</f>
         <v/>
       </c>
-      <c r="I14" s="101">
+      <c r="I14" s="81">
         <f>Daily!AM15</f>
         <v/>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="81">
         <f>Daily!AN15</f>
         <v/>
       </c>
-      <c r="K14" s="101">
+      <c r="K14" s="81">
         <f>Daily!AO15</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B15" s="100" t="inlineStr">
+      <c r="B15" s="80" t="inlineStr">
         <is>
           <t>E/P In (this week)</t>
         </is>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="222">
         <f>Daily!AG14</f>
         <v/>
       </c>
-      <c r="D15" s="249">
+      <c r="D15" s="222">
         <f>Daily!AH14</f>
         <v/>
       </c>
-      <c r="E15" s="249">
+      <c r="E15" s="222">
         <f>Daily!AI14</f>
         <v/>
       </c>
-      <c r="F15" s="249">
+      <c r="F15" s="222">
         <f>Daily!AJ14</f>
         <v/>
       </c>
-      <c r="G15" s="249">
+      <c r="G15" s="222">
         <f>Daily!AK14</f>
         <v/>
       </c>
-      <c r="H15" s="249">
+      <c r="H15" s="222">
         <f>Daily!AL14</f>
         <v/>
       </c>
-      <c r="I15" s="249">
+      <c r="I15" s="222">
         <f>Daily!AM14</f>
         <v/>
       </c>
-      <c r="J15" s="249">
+      <c r="J15" s="222">
         <f>Daily!AN14</f>
         <v/>
       </c>
-      <c r="K15" s="249">
+      <c r="K15" s="222">
         <f>Daily!AO14</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B16" s="102" t="n"/>
-      <c r="C16" s="103" t="n"/>
-      <c r="D16" s="103" t="n"/>
-      <c r="E16" s="103" t="n"/>
-      <c r="F16" s="103" t="n"/>
-      <c r="G16" s="103" t="n"/>
-      <c r="H16" s="103" t="n"/>
-      <c r="I16" s="103" t="n"/>
-      <c r="J16" s="103" t="n"/>
-      <c r="K16" s="103" t="n"/>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="83" t="n"/>
+      <c r="D16" s="83" t="n"/>
+      <c r="E16" s="83" t="n"/>
+      <c r="F16" s="83" t="n"/>
+      <c r="G16" s="83" t="n"/>
+      <c r="H16" s="83" t="n"/>
+      <c r="I16" s="83" t="n"/>
+      <c r="J16" s="83" t="n"/>
+      <c r="K16" s="83" t="n"/>
     </row>
     <row r="17" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B17" s="102" t="n"/>
-      <c r="C17" s="103" t="n"/>
-      <c r="D17" s="103" t="n"/>
-      <c r="E17" s="103" t="n"/>
-      <c r="F17" s="103" t="n"/>
-      <c r="G17" s="103" t="n"/>
-      <c r="H17" s="103" t="n"/>
-      <c r="I17" s="103" t="n"/>
-      <c r="J17" s="103" t="n"/>
-      <c r="K17" s="103" t="n"/>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="83" t="n"/>
+      <c r="D17" s="83" t="n"/>
+      <c r="E17" s="83" t="n"/>
+      <c r="F17" s="83" t="n"/>
+      <c r="G17" s="83" t="n"/>
+      <c r="H17" s="83" t="n"/>
+      <c r="I17" s="83" t="n"/>
+      <c r="J17" s="83" t="n"/>
+      <c r="K17" s="83" t="n"/>
     </row>
     <row r="18" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B18" s="104" t="inlineStr">
+      <c r="B18" s="84" t="inlineStr">
         <is>
           <t>INBOUND MT RETURN</t>
         </is>
       </c>
-      <c r="C18" s="250">
+      <c r="C18" s="223">
         <f>Daily!X15</f>
         <v/>
       </c>
-      <c r="D18" s="250">
+      <c r="D18" s="223">
         <f>Daily!Y15</f>
         <v/>
       </c>
-      <c r="E18" s="250">
+      <c r="E18" s="223">
         <f>Daily!Z15</f>
         <v/>
       </c>
-      <c r="F18" s="250">
+      <c r="F18" s="223">
         <f>Daily!AA15</f>
         <v/>
       </c>
-      <c r="G18" s="250">
+      <c r="G18" s="223">
         <f>Daily!AB15</f>
         <v/>
       </c>
-      <c r="H18" s="250">
+      <c r="H18" s="223">
         <f>Daily!AC15</f>
         <v/>
       </c>
-      <c r="I18" s="250">
+      <c r="I18" s="223">
         <f>Daily!AD15</f>
         <v/>
       </c>
-      <c r="J18" s="250">
+      <c r="J18" s="223">
         <f>Daily!AE15</f>
         <v/>
       </c>
-      <c r="K18" s="250">
+      <c r="K18" s="223">
         <f>Daily!AF15</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B19" s="112" t="inlineStr">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>Booking(This week)</t>
         </is>
       </c>
-      <c r="C19" s="251">
+      <c r="C19" s="224">
         <f>Daily!X41</f>
         <v/>
       </c>
-      <c r="D19" s="251">
+      <c r="D19" s="224">
         <f>Daily!Y41</f>
         <v/>
       </c>
-      <c r="E19" s="251">
+      <c r="E19" s="224">
         <f>Daily!Z41</f>
         <v/>
       </c>
-      <c r="F19" s="251">
+      <c r="F19" s="224">
         <f>Daily!AA41</f>
         <v/>
       </c>
-      <c r="G19" s="251">
+      <c r="G19" s="224">
         <f>Daily!AB41</f>
         <v/>
       </c>
-      <c r="H19" s="251">
+      <c r="H19" s="224">
         <f>Daily!AC41</f>
         <v/>
       </c>
-      <c r="I19" s="255">
+      <c r="I19" s="225">
         <f>Daily!AD41</f>
         <v/>
       </c>
-      <c r="J19" s="255">
+      <c r="J19" s="225">
         <f>Daily!AE41</f>
         <v/>
       </c>
-      <c r="K19" s="251">
+      <c r="K19" s="224">
         <f>Daily!AF41</f>
         <v/>
       </c>
-      <c r="L19" s="95">
+      <c r="L19" s="75">
         <f>Daily!AD29</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B20" s="112" t="inlineStr">
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t>Booking(Next week)</t>
         </is>
       </c>
-      <c r="C20" s="251">
+      <c r="C20" s="224">
         <f>Daily!X55</f>
         <v/>
       </c>
-      <c r="D20" s="251">
+      <c r="D20" s="224">
         <f>Daily!Y55</f>
         <v/>
       </c>
-      <c r="E20" s="251">
+      <c r="E20" s="224">
         <f>Daily!Z55</f>
         <v/>
       </c>
-      <c r="F20" s="251">
+      <c r="F20" s="224">
         <f>Daily!AA55</f>
         <v/>
       </c>
-      <c r="G20" s="251">
+      <c r="G20" s="224">
         <f>Daily!AB55</f>
         <v/>
       </c>
-      <c r="H20" s="251">
+      <c r="H20" s="224">
         <f>Daily!AC55</f>
         <v/>
       </c>
-      <c r="I20" s="251">
+      <c r="I20" s="224">
         <f>Daily!AD55</f>
         <v/>
       </c>
-      <c r="J20" s="251">
+      <c r="J20" s="224">
         <f>Daily!AE55</f>
         <v/>
       </c>
-      <c r="K20" s="251">
+      <c r="K20" s="224">
         <f>Daily!AF55</f>
         <v/>
       </c>
-      <c r="L20" s="95">
+      <c r="L20" s="75">
         <f>Daily!AD43</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B21" s="108" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="161">
         <f>SUM(C14+C15+C16+C17+C18-C19-C20)</f>
         <v/>
       </c>
-      <c r="D21" s="252">
+      <c r="D21" s="161">
         <f>SUM(D14+D15+D16+D17+D18-D19-D20)</f>
         <v/>
       </c>
-      <c r="E21" s="252">
+      <c r="E21" s="161">
         <f>SUM(E14+E15+E16+E17+E18-E19-E20)</f>
         <v/>
       </c>
-      <c r="F21" s="252">
+      <c r="F21" s="161">
         <f>SUM(F14+F15+F16+F17+F18-F19-F20)</f>
         <v/>
       </c>
-      <c r="G21" s="252">
+      <c r="G21" s="161">
         <f>SUM(G14+G15+G16+G17+G18-G19-G20)</f>
         <v/>
       </c>
-      <c r="H21" s="252">
+      <c r="H21" s="161">
         <f>SUM(H14+H15+H16+H17+H18-H19-H20)</f>
         <v/>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="161">
         <f>SUM(I14+I15+I16+I17+I18-I19-I20)</f>
         <v/>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="161">
         <f>SUM(J14+J15+J16+J17+J18-J19-J20)</f>
         <v/>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="161">
         <f>SUM(K14+K15+K16+K17+K18-K19-K20)</f>
         <v/>
       </c>
